--- a/frontend/public/content/stitchfix-home.xlsx
+++ b/frontend/public/content/stitchfix-home.xlsx
@@ -8461,7 +8461,7 @@
         <v>Structured Wool Twill</v>
       </c>
       <c r="AJ44" t="str">
-        <v>Sharper outerwear line pulled into the womenâs edit for contrast. Curated into the All Archive rail for a fuller workbook seed.</v>
+        <v>Sharper outerwear line pulled into the womenÃ¢ÂÂs edit for contrast. Curated into the All Archive rail for a fuller workbook seed.</v>
       </c>
       <c r="AK44" t="str">
         <v/>
@@ -8646,7 +8646,7 @@
         <v>Pure Cashmere</v>
       </c>
       <c r="AJ45" t="str">
-        <v>A softer knit layer that keeps the womenâs tab calm and tactile. Curated into the All Archive rail for a fuller workbook seed.</v>
+        <v>A softer knit layer that keeps the womenÃ¢ÂÂs tab calm and tactile. Curated into the All Archive rail for a fuller workbook seed.</v>
       </c>
       <c r="AK45" t="str">
         <v/>
@@ -12716,7 +12716,7 @@
         <v>Structured Wool Twill</v>
       </c>
       <c r="AJ67" t="str">
-        <v>Sharper outerwear line pulled into the womenâs edit for contrast.</v>
+        <v>Sharper outerwear line pulled into the womenÃ¢ÂÂs edit for contrast.</v>
       </c>
       <c r="AK67" t="str">
         <v/>
@@ -12901,7 +12901,7 @@
         <v>Pure Cashmere</v>
       </c>
       <c r="AJ68" t="str">
-        <v>A softer knit layer that keeps the womenâs tab calm and tactile.</v>
+        <v>A softer knit layer that keeps the womenÃ¢ÂÂs tab calm and tactile.</v>
       </c>
       <c r="AK68" t="str">
         <v/>
@@ -13271,7 +13271,7 @@
         <v>Brushed Wool Blend</v>
       </c>
       <c r="AJ70" t="str">
-        <v>A tapered trouser used to ground the softer tops in the womenâs rail.</v>
+        <v>A tapered trouser used to ground the softer tops in the womenÃ¢ÂÂs rail.</v>
       </c>
       <c r="AK70" t="str">
         <v/>
@@ -13641,7 +13641,7 @@
         <v>Washed Silk Blend</v>
       </c>
       <c r="AJ72" t="str">
-        <v>A wrapped silhouette that keeps the womenâs page light and fluid.</v>
+        <v>A wrapped silhouette that keeps the womenÃ¢ÂÂs page light and fluid.</v>
       </c>
       <c r="AK72" t="str">
         <v/>

--- a/frontend/public/content/stitchfix-home.xlsx
+++ b/frontend/public/content/stitchfix-home.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI160"/>
+  <dimension ref="A1:BI158"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8425,13 +8425,13 @@
         <v/>
       </c>
       <c r="X44" t="str">
-        <v>Limited</v>
+        <v>New Arrival</v>
       </c>
       <c r="Y44" t="str">
         <v/>
       </c>
       <c r="Z44" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</v>
       </c>
       <c r="AA44" t="str">
         <v/>
@@ -8446,22 +8446,22 @@
         <v/>
       </c>
       <c r="AE44" t="str">
-        <v>women-002</v>
+        <v>footwear-001</v>
       </c>
       <c r="AF44" t="str">
         <v>ND Shop</v>
       </c>
       <c r="AG44" t="str">
-        <v>Architectural Overcoat</v>
+        <v>Atelier Low Sneaker</v>
       </c>
       <c r="AH44" t="str">
-        <v>1250</v>
+        <v>340</v>
       </c>
       <c r="AI44" t="str">
-        <v>Structured Wool Twill</v>
+        <v>Smooth Italian Calfskin</v>
       </c>
       <c r="AJ44" t="str">
-        <v>Sharper outerwear line pulled into the womenÃ¢ÂÂs edit for contrast. Curated into the All Archive rail for a fuller workbook seed.</v>
+        <v>Minimal sneaker profile designed to keep the footwear story clean and modern. Curated into the All Archive rail for a fuller workbook seed.</v>
       </c>
       <c r="AK44" t="str">
         <v/>
@@ -8610,13 +8610,13 @@
         <v/>
       </c>
       <c r="X45" t="str">
-        <v>Knitwear</v>
+        <v>Handcrafted</v>
       </c>
       <c r="Y45" t="str">
         <v/>
       </c>
       <c r="Z45" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBEKFEZ7Xk7Fyqc9Uf8Rr7JfhPIghhY7j0HO6bqSglckdRAUU1XFK1Vy_uPXAbpLqczXmCH41FFfT4QIgBtt7oBHhaEojRqYoMhEeW0zN9yDlgFxnnAhZfa_FjmfnZNakXUp-HAT6D2gb_BUeHA5TXBmMVsObd_AHQfOwPuMZTKrAqSkXnJe60KUnlOWajJ6btQ5zyNadwls33tVZNcDlHyJ8_EUlUAhHRtQ90ZhEzMNN5Mzjf_Hr7Onn7MZF-hkz45XkPrdm6pngSw</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</v>
       </c>
       <c r="AA45" t="str">
         <v/>
@@ -8631,22 +8631,22 @@
         <v/>
       </c>
       <c r="AE45" t="str">
-        <v>women-003</v>
+        <v>footwear-002</v>
       </c>
       <c r="AF45" t="str">
         <v>ND Shop</v>
       </c>
       <c r="AG45" t="str">
-        <v>Cloud Cashmere Crew</v>
+        <v>Chelsea Field Boot</v>
       </c>
       <c r="AH45" t="str">
-        <v>280</v>
+        <v>495</v>
       </c>
       <c r="AI45" t="str">
-        <v>Pure Cashmere</v>
+        <v>Waxed Roughout Leather</v>
       </c>
       <c r="AJ45" t="str">
-        <v>A softer knit layer that keeps the womenÃ¢ÂÂs tab calm and tactile. Curated into the All Archive rail for a fuller workbook seed.</v>
+        <v>A field boot with a quieter shaft and stronger welt presence. Curated into the All Archive rail for a fuller workbook seed.</v>
       </c>
       <c r="AK45" t="str">
         <v/>
@@ -8795,13 +8795,13 @@
         <v/>
       </c>
       <c r="X46" t="str">
-        <v>New Arrival</v>
+        <v>Studio Classic</v>
       </c>
       <c r="Y46" t="str">
         <v/>
       </c>
       <c r="Z46" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</v>
       </c>
       <c r="AA46" t="str">
         <v/>
@@ -8816,22 +8816,22 @@
         <v/>
       </c>
       <c r="AE46" t="str">
-        <v>footwear-001</v>
+        <v>footwear-003</v>
       </c>
       <c r="AF46" t="str">
         <v>ND Shop</v>
       </c>
       <c r="AG46" t="str">
-        <v>Atelier Low Sneaker</v>
+        <v>Classic Penny Loafer</v>
       </c>
       <c r="AH46" t="str">
-        <v>340</v>
+        <v>420</v>
       </c>
       <c r="AI46" t="str">
-        <v>Smooth Italian Calfskin</v>
+        <v>Pebbled Grain Leather</v>
       </c>
       <c r="AJ46" t="str">
-        <v>Minimal sneaker profile designed to keep the footwear story clean and modern. Curated into the All Archive rail for a fuller workbook seed.</v>
+        <v>A classic loafer shape refined for the workshop-led footwear rail. Curated into the All Archive rail for a fuller workbook seed.</v>
       </c>
       <c r="AK46" t="str">
         <v/>
@@ -8980,13 +8980,13 @@
         <v/>
       </c>
       <c r="X47" t="str">
-        <v>Handcrafted</v>
+        <v>Limited Edition</v>
       </c>
       <c r="Y47" t="str">
         <v/>
       </c>
       <c r="Z47" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
       </c>
       <c r="AA47" t="str">
         <v/>
@@ -9001,22 +9001,22 @@
         <v/>
       </c>
       <c r="AE47" t="str">
-        <v>footwear-002</v>
+        <v>accessories-001</v>
       </c>
       <c r="AF47" t="str">
         <v>ND Shop</v>
       </c>
       <c r="AG47" t="str">
-        <v>Chelsea Field Boot</v>
+        <v>Atelier Tote</v>
       </c>
       <c r="AH47" t="str">
-        <v>495</v>
+        <v>840</v>
       </c>
       <c r="AI47" t="str">
-        <v>Waxed Roughout Leather</v>
+        <v>Vegetable Tanned Leather</v>
       </c>
       <c r="AJ47" t="str">
-        <v>A field boot with a quieter shaft and stronger welt presence. Curated into the All Archive rail for a fuller workbook seed.</v>
+        <v>A structured tote that leads the accessory story with more presence. Curated into the All Archive rail for a fuller workbook seed.</v>
       </c>
       <c r="AK47" t="str">
         <v/>
@@ -9165,13 +9165,13 @@
         <v/>
       </c>
       <c r="X48" t="str">
-        <v>Studio Classic</v>
+        <v>Essential</v>
       </c>
       <c r="Y48" t="str">
         <v/>
       </c>
       <c r="Z48" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
       </c>
       <c r="AA48" t="str">
         <v/>
@@ -9186,22 +9186,22 @@
         <v/>
       </c>
       <c r="AE48" t="str">
-        <v>footwear-003</v>
+        <v>accessories-002</v>
       </c>
       <c r="AF48" t="str">
         <v>ND Shop</v>
       </c>
       <c r="AG48" t="str">
-        <v>Classic Penny Loafer</v>
+        <v>Aurora Wrap</v>
       </c>
       <c r="AH48" t="str">
-        <v>420</v>
+        <v>215</v>
       </c>
       <c r="AI48" t="str">
-        <v>Pebbled Grain Leather</v>
+        <v>Organic Raw Silk</v>
       </c>
       <c r="AJ48" t="str">
-        <v>A classic loafer shape refined for the workshop-led footwear rail. Curated into the All Archive rail for a fuller workbook seed.</v>
+        <v>A lighter textile accent to soften the accessory rail. Curated into the All Archive rail for a fuller workbook seed.</v>
       </c>
       <c r="AK48" t="str">
         <v/>
@@ -9350,13 +9350,13 @@
         <v/>
       </c>
       <c r="X49" t="str">
-        <v>Limited Edition</v>
+        <v>Leather Detail</v>
       </c>
       <c r="Y49" t="str">
         <v/>
       </c>
       <c r="Z49" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDclyoI7lW_Aez2lBayMz4ES5BVdH-wo43IL4ZwpD4HLQkaJqfV3eDM-qMUs4V8Uyl6BTZ9FSNg7ExFisE6J-TMxcflCy5mFritcP54bDT49eqwGnwGnsOeheOgbCmpdtfGvnHaqpfmRpU4zQvBD7B4tmigGgv7hCDEHWLojIzOlAfe5p-0cCnzLjktClPIw5lG6h2qfT0buVNcsY57FFriSrjdMpV_jPcwn3Dwsz1C-8IS20dhOYE1-Kak6Hi0R-OiEeULdIqMBj2c</v>
       </c>
       <c r="AA49" t="str">
         <v/>
@@ -9371,22 +9371,22 @@
         <v/>
       </c>
       <c r="AE49" t="str">
-        <v>accessories-001</v>
+        <v>accessories-003</v>
       </c>
       <c r="AF49" t="str">
         <v>ND Shop</v>
       </c>
       <c r="AG49" t="str">
-        <v>Atelier Tote</v>
+        <v>Cintura Belt</v>
       </c>
       <c r="AH49" t="str">
-        <v>840</v>
+        <v>165</v>
       </c>
       <c r="AI49" t="str">
-        <v>Vegetable Tanned Leather</v>
+        <v>Full Grain Saddle Leather</v>
       </c>
       <c r="AJ49" t="str">
-        <v>A structured tote that leads the accessory story with more presence. Curated into the All Archive rail for a fuller workbook seed.</v>
+        <v>A structured belt detail pulled into the accessory catalog. Curated into the All Archive rail for a fuller workbook seed.</v>
       </c>
       <c r="AK49" t="str">
         <v/>
@@ -9478,7 +9478,7 @@
         <v/>
       </c>
       <c r="E50" t="str">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F50" t="str">
         <v/>
@@ -9487,13 +9487,13 @@
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>/products</v>
+        <v>/categories/Shop%20Men</v>
       </c>
       <c r="I50" t="str">
         <v/>
       </c>
       <c r="J50" t="str">
-        <v>all-archive</v>
+        <v>nam</v>
       </c>
       <c r="K50" t="str">
         <v/>
@@ -9535,13 +9535,13 @@
         <v/>
       </c>
       <c r="X50" t="str">
-        <v>Essential</v>
+        <v>New Arrival</v>
       </c>
       <c r="Y50" t="str">
         <v/>
       </c>
       <c r="Z50" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</v>
       </c>
       <c r="AA50" t="str">
         <v/>
@@ -9556,22 +9556,22 @@
         <v/>
       </c>
       <c r="AE50" t="str">
-        <v>accessories-002</v>
+        <v>men-001</v>
       </c>
       <c r="AF50" t="str">
-        <v>ND Shop</v>
+        <v>ND Atelier</v>
       </c>
       <c r="AG50" t="str">
-        <v>Aurora Wrap</v>
+        <v>Sculpted Linen Shirt</v>
       </c>
       <c r="AH50" t="str">
-        <v>215</v>
+        <v>420</v>
       </c>
       <c r="AI50" t="str">
-        <v>Organic Raw Silk</v>
+        <v>Italian Linen Blend</v>
       </c>
       <c r="AJ50" t="str">
-        <v>A lighter textile accent to soften the accessory rail. Curated into the All Archive rail for a fuller workbook seed.</v>
+        <v>Lightweight structure and a cleaner vertical line for spring layering.</v>
       </c>
       <c r="AK50" t="str">
         <v/>
@@ -9663,7 +9663,7 @@
         <v/>
       </c>
       <c r="E51" t="str">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F51" t="str">
         <v/>
@@ -9672,13 +9672,13 @@
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>/products</v>
+        <v>/categories/Shop%20Men</v>
       </c>
       <c r="I51" t="str">
         <v/>
       </c>
       <c r="J51" t="str">
-        <v>all-archive</v>
+        <v>nam</v>
       </c>
       <c r="K51" t="str">
         <v/>
@@ -9720,13 +9720,13 @@
         <v/>
       </c>
       <c r="X51" t="str">
-        <v>Leather Detail</v>
+        <v>Limited Edition</v>
       </c>
       <c r="Y51" t="str">
         <v/>
       </c>
       <c r="Z51" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDclyoI7lW_Aez2lBayMz4ES5BVdH-wo43IL4ZwpD4HLQkaJqfV3eDM-qMUs4V8Uyl6BTZ9FSNg7ExFisE6J-TMxcflCy5mFritcP54bDT49eqwGnwGnsOeheOgbCmpdtfGvnHaqpfmRpU4zQvBD7B4tmigGgv7hCDEHWLojIzOlAfe5p-0cCnzLjktClPIw5lG6h2qfT0buVNcsY57FFriSrjdMpV_jPcwn3Dwsz1C-8IS20dhOYE1-Kak6Hi0R-OiEeULdIqMBj2c</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</v>
       </c>
       <c r="AA51" t="str">
         <v/>
@@ -9741,22 +9741,22 @@
         <v/>
       </c>
       <c r="AE51" t="str">
-        <v>accessories-003</v>
+        <v>men-002</v>
       </c>
       <c r="AF51" t="str">
-        <v>ND Shop</v>
+        <v>ND Atelier</v>
       </c>
       <c r="AG51" t="str">
-        <v>Cintura Belt</v>
+        <v>Structured Atelier Jacket</v>
       </c>
       <c r="AH51" t="str">
-        <v>165</v>
+        <v>1250</v>
       </c>
       <c r="AI51" t="str">
-        <v>Full Grain Saddle Leather</v>
+        <v>100% Merino Wool</v>
       </c>
       <c r="AJ51" t="str">
-        <v>A structured belt detail pulled into the accessory catalog. Curated into the All Archive rail for a fuller workbook seed.</v>
+        <v>The anchor outerwear piece for the men's editorial story.</v>
       </c>
       <c r="AK51" t="str">
         <v/>
@@ -9848,7 +9848,7 @@
         <v/>
       </c>
       <c r="E52" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F52" t="str">
         <v/>
@@ -9905,13 +9905,13 @@
         <v/>
       </c>
       <c r="X52" t="str">
-        <v>New Arrival</v>
+        <v>Tailoring</v>
       </c>
       <c r="Y52" t="str">
         <v/>
       </c>
       <c r="Z52" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBXRSWOWcHtCNyaMDYLCJzvRD_aYObkVBkIHPoz_HZOOuihWxPKo82MAX7anUmfBqHwOgx_6YthGokOn-aqEtAkMya3di9RNTlqqA2-zqT6x85Yh0CGWy5_gOTjOOMYxnRJ7B8A9ihZaMR-PzIAILb7T5rSMUCiZ-3CZRTX_u3XxJpOlXlYjWEZj4aFLaV_mamuWkKjkhTxSRpw7LyICx9lPITcKUuGOxJ0NkpKweDI4rMjqFkSSGZJssErigmmpbKq5Z6kLPVUehXg</v>
       </c>
       <c r="AA52" t="str">
         <v/>
@@ -9926,22 +9926,22 @@
         <v/>
       </c>
       <c r="AE52" t="str">
-        <v>men-001</v>
+        <v>men-003</v>
       </c>
       <c r="AF52" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG52" t="str">
-        <v>Sculpted Linen Shirt</v>
+        <v>Modern Drape Trousers</v>
       </c>
       <c r="AH52" t="str">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="AI52" t="str">
-        <v>Italian Linen Blend</v>
+        <v>Fine Serge Cotton</v>
       </c>
       <c r="AJ52" t="str">
-        <v>Lightweight structure and a cleaner vertical line for spring layering.</v>
+        <v>A softer trouser line that balances the stronger jacket shapes.</v>
       </c>
       <c r="AK52" t="str">
         <v/>
@@ -10033,7 +10033,7 @@
         <v/>
       </c>
       <c r="E53" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F53" t="str">
         <v/>
@@ -10090,13 +10090,13 @@
         <v/>
       </c>
       <c r="X53" t="str">
-        <v>Limited Edition</v>
+        <v>Knitwear</v>
       </c>
       <c r="Y53" t="str">
         <v/>
       </c>
       <c r="Z53" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDBowt2AR0QGkZ_teHLK0qG2iUl8fGSUuNTrZHreU_s95xtmrbnCTB8LYOShnHaraaNDqoUnziBnVe2Rh6OAlJpU9ZSpF84L0-k23aokXc6aJdWswRdyGowycFswnENPgO9tfnUyUaMa2VjW8lGJYkmhPbnJhSE0zC0BdoSTdae8pmGnQwaAXzVlJJRhWYysiO1yf2n_lREj8nVxarkGub1OLnfLI4QrhAiAGV-AZTWnZg1MCqdpNi1pBSjb6RIPFAzXw0h_iTQCqrp</v>
       </c>
       <c r="AA53" t="str">
         <v/>
@@ -10111,22 +10111,22 @@
         <v/>
       </c>
       <c r="AE53" t="str">
-        <v>men-002</v>
+        <v>men-004</v>
       </c>
       <c r="AF53" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG53" t="str">
-        <v>Structured Atelier Jacket</v>
+        <v>Atelier Knit Polo</v>
       </c>
       <c r="AH53" t="str">
-        <v>1250</v>
+        <v>290</v>
       </c>
       <c r="AI53" t="str">
-        <v>100% Merino Wool</v>
+        <v>Sea Island Cotton</v>
       </c>
       <c r="AJ53" t="str">
-        <v>The anchor outerwear piece for the men's editorial story.</v>
+        <v>A quiet knit that keeps the rail tactile without losing structure.</v>
       </c>
       <c r="AK53" t="str">
         <v/>
@@ -10218,7 +10218,7 @@
         <v/>
       </c>
       <c r="E54" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F54" t="str">
         <v/>
@@ -10275,13 +10275,13 @@
         <v/>
       </c>
       <c r="X54" t="str">
-        <v>Tailoring</v>
+        <v>Editorial Pick</v>
       </c>
       <c r="Y54" t="str">
         <v/>
       </c>
       <c r="Z54" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBXRSWOWcHtCNyaMDYLCJzvRD_aYObkVBkIHPoz_HZOOuihWxPKo82MAX7anUmfBqHwOgx_6YthGokOn-aqEtAkMya3di9RNTlqqA2-zqT6x85Yh0CGWy5_gOTjOOMYxnRJ7B8A9ihZaMR-PzIAILb7T5rSMUCiZ-3CZRTX_u3XxJpOlXlYjWEZj4aFLaV_mamuWkKjkhTxSRpw7LyICx9lPITcKUuGOxJ0NkpKweDI4rMjqFkSSGZJssErigmmpbKq5Z6kLPVUehXg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</v>
       </c>
       <c r="AA54" t="str">
         <v/>
@@ -10296,22 +10296,22 @@
         <v/>
       </c>
       <c r="AE54" t="str">
-        <v>men-003</v>
+        <v>men-005</v>
       </c>
       <c r="AF54" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG54" t="str">
-        <v>Modern Drape Trousers</v>
+        <v>The Obsidian Overcoat</v>
       </c>
       <c r="AH54" t="str">
-        <v>380</v>
+        <v>1890</v>
       </c>
       <c r="AI54" t="str">
-        <v>Fine Serge Cotton</v>
+        <v>Cashmere Blend</v>
       </c>
       <c r="AJ54" t="str">
-        <v>A softer trouser line that balances the stronger jacket shapes.</v>
+        <v>Longline outerwear built as the hero silhouette for colder drops.</v>
       </c>
       <c r="AK54" t="str">
         <v/>
@@ -10403,7 +10403,7 @@
         <v/>
       </c>
       <c r="E55" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F55" t="str">
         <v/>
@@ -10460,13 +10460,13 @@
         <v/>
       </c>
       <c r="X55" t="str">
-        <v>Knitwear</v>
+        <v>Studio Essential</v>
       </c>
       <c r="Y55" t="str">
         <v/>
       </c>
       <c r="Z55" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDBowt2AR0QGkZ_teHLK0qG2iUl8fGSUuNTrZHreU_s95xtmrbnCTB8LYOShnHaraaNDqoUnziBnVe2Rh6OAlJpU9ZSpF84L0-k23aokXc6aJdWswRdyGowycFswnENPgO9tfnUyUaMa2VjW8lGJYkmhPbnJhSE0zC0BdoSTdae8pmGnQwaAXzVlJJRhWYysiO1yf2n_lREj8nVxarkGub1OLnfLI4QrhAiAGV-AZTWnZg1MCqdpNi1pBSjb6RIPFAzXw0h_iTQCqrp</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</v>
       </c>
       <c r="AA55" t="str">
         <v/>
@@ -10481,22 +10481,22 @@
         <v/>
       </c>
       <c r="AE55" t="str">
-        <v>men-004</v>
+        <v>men-006</v>
       </c>
       <c r="AF55" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG55" t="str">
-        <v>Atelier Knit Polo</v>
+        <v>Relaxed Cargo Trouser</v>
       </c>
       <c r="AH55" t="str">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="AI55" t="str">
-        <v>Sea Island Cotton</v>
+        <v>Brushed Twill</v>
       </c>
       <c r="AJ55" t="str">
-        <v>A quiet knit that keeps the rail tactile without losing structure.</v>
+        <v>Utility detail softened into a more editorial everyday trouser.</v>
       </c>
       <c r="AK55" t="str">
         <v/>
@@ -10588,7 +10588,7 @@
         <v/>
       </c>
       <c r="E56" t="str">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F56" t="str">
         <v/>
@@ -10645,13 +10645,13 @@
         <v/>
       </c>
       <c r="X56" t="str">
-        <v>Editorial Pick</v>
+        <v>Workshop Layer</v>
       </c>
       <c r="Y56" t="str">
         <v/>
       </c>
       <c r="Z56" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</v>
       </c>
       <c r="AA56" t="str">
         <v/>
@@ -10666,22 +10666,22 @@
         <v/>
       </c>
       <c r="AE56" t="str">
-        <v>men-005</v>
+        <v>men-007</v>
       </c>
       <c r="AF56" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG56" t="str">
-        <v>The Obsidian Overcoat</v>
+        <v>Stonewashed Utility Overshirt</v>
       </c>
       <c r="AH56" t="str">
-        <v>1890</v>
+        <v>360</v>
       </c>
       <c r="AI56" t="str">
-        <v>Cashmere Blend</v>
+        <v>Washed Cotton Drill</v>
       </c>
       <c r="AJ56" t="str">
-        <v>Longline outerwear built as the hero silhouette for colder drops.</v>
+        <v>A practical overshirt cut to sit between shirting and outerwear.</v>
       </c>
       <c r="AK56" t="str">
         <v/>
@@ -10773,7 +10773,7 @@
         <v/>
       </c>
       <c r="E57" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F57" t="str">
         <v/>
@@ -10830,13 +10830,13 @@
         <v/>
       </c>
       <c r="X57" t="str">
-        <v>Studio Essential</v>
+        <v>Soft Structure</v>
       </c>
       <c r="Y57" t="str">
         <v/>
       </c>
       <c r="Z57" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBXRSWOWcHtCNyaMDYLCJzvRD_aYObkVBkIHPoz_HZOOuihWxPKo82MAX7anUmfBqHwOgx_6YthGokOn-aqEtAkMya3di9RNTlqqA2-zqT6x85Yh0CGWy5_gOTjOOMYxnRJ7B8A9ihZaMR-PzIAILb7T5rSMUCiZ-3CZRTX_u3XxJpOlXlYjWEZj4aFLaV_mamuWkKjkhTxSRpw7LyICx9lPITcKUuGOxJ0NkpKweDI4rMjqFkSSGZJssErigmmpbKq5Z6kLPVUehXg</v>
       </c>
       <c r="AA57" t="str">
         <v/>
@@ -10851,22 +10851,22 @@
         <v/>
       </c>
       <c r="AE57" t="str">
-        <v>men-006</v>
+        <v>men-008</v>
       </c>
       <c r="AF57" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG57" t="str">
-        <v>Relaxed Cargo Trouser</v>
+        <v>Meridian Wool Cardigan</v>
       </c>
       <c r="AH57" t="str">
-        <v>340</v>
+        <v>410</v>
       </c>
       <c r="AI57" t="str">
-        <v>Brushed Twill</v>
+        <v>Merino Wool</v>
       </c>
       <c r="AJ57" t="str">
-        <v>Utility detail softened into a more editorial everyday trouser.</v>
+        <v>Midweight knitwear that layers easily under coats and chore jackets.</v>
       </c>
       <c r="AK57" t="str">
         <v/>
@@ -10958,7 +10958,7 @@
         <v/>
       </c>
       <c r="E58" t="str">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F58" t="str">
         <v/>
@@ -11015,13 +11015,13 @@
         <v/>
       </c>
       <c r="X58" t="str">
-        <v>Workshop Layer</v>
+        <v>Warm Weather</v>
       </c>
       <c r="Y58" t="str">
         <v/>
       </c>
       <c r="Z58" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDBowt2AR0QGkZ_teHLK0qG2iUl8fGSUuNTrZHreU_s95xtmrbnCTB8LYOShnHaraaNDqoUnziBnVe2Rh6OAlJpU9ZSpF84L0-k23aokXc6aJdWswRdyGowycFswnENPgO9tfnUyUaMa2VjW8lGJYkmhPbnJhSE0zC0BdoSTdae8pmGnQwaAXzVlJJRhWYysiO1yf2n_lREj8nVxarkGub1OLnfLI4QrhAiAGV-AZTWnZg1MCqdpNi1pBSjb6RIPFAzXw0h_iTQCqrp</v>
       </c>
       <c r="AA58" t="str">
         <v/>
@@ -11036,22 +11036,22 @@
         <v/>
       </c>
       <c r="AE58" t="str">
-        <v>men-007</v>
+        <v>men-009</v>
       </c>
       <c r="AF58" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG58" t="str">
-        <v>Stonewashed Utility Overshirt</v>
+        <v>Foundry Pleat Short</v>
       </c>
       <c r="AH58" t="str">
-        <v>360</v>
+        <v>250</v>
       </c>
       <c r="AI58" t="str">
-        <v>Washed Cotton Drill</v>
+        <v>Tumbled Cotton Poplin</v>
       </c>
       <c r="AJ58" t="str">
-        <v>A practical overshirt cut to sit between shirting and outerwear.</v>
+        <v>A pleated short that keeps the men's edit crisp in lighter weather.</v>
       </c>
       <c r="AK58" t="str">
         <v/>
@@ -11143,7 +11143,7 @@
         <v/>
       </c>
       <c r="E59" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F59" t="str">
         <v/>
@@ -11200,13 +11200,13 @@
         <v/>
       </c>
       <c r="X59" t="str">
-        <v>Soft Structure</v>
+        <v>Shirting</v>
       </c>
       <c r="Y59" t="str">
         <v/>
       </c>
       <c r="Z59" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBXRSWOWcHtCNyaMDYLCJzvRD_aYObkVBkIHPoz_HZOOuihWxPKo82MAX7anUmfBqHwOgx_6YthGokOn-aqEtAkMya3di9RNTlqqA2-zqT6x85Yh0CGWy5_gOTjOOMYxnRJ7B8A9ihZaMR-PzIAILb7T5rSMUCiZ-3CZRTX_u3XxJpOlXlYjWEZj4aFLaV_mamuWkKjkhTxSRpw7LyICx9lPITcKUuGOxJ0NkpKweDI4rMjqFkSSGZJssErigmmpbKq5Z6kLPVUehXg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</v>
       </c>
       <c r="AA59" t="str">
         <v/>
@@ -11221,22 +11221,22 @@
         <v/>
       </c>
       <c r="AE59" t="str">
-        <v>men-008</v>
+        <v>men-010</v>
       </c>
       <c r="AF59" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG59" t="str">
-        <v>Meridian Wool Cardigan</v>
+        <v>Tailored Poplin Bandshirt</v>
       </c>
       <c r="AH59" t="str">
-        <v>410</v>
+        <v>280</v>
       </c>
       <c r="AI59" t="str">
-        <v>Merino Wool</v>
+        <v>Compact Cotton Poplin</v>
       </c>
       <c r="AJ59" t="str">
-        <v>Midweight knitwear that layers easily under coats and chore jackets.</v>
+        <v>Band-collar shirting with a sharper placket and longer line.</v>
       </c>
       <c r="AK59" t="str">
         <v/>
@@ -11328,7 +11328,7 @@
         <v/>
       </c>
       <c r="E60" t="str">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F60" t="str">
         <v/>
@@ -11385,13 +11385,13 @@
         <v/>
       </c>
       <c r="X60" t="str">
-        <v>Warm Weather</v>
+        <v>Outerwear</v>
       </c>
       <c r="Y60" t="str">
         <v/>
       </c>
       <c r="Z60" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDBowt2AR0QGkZ_teHLK0qG2iUl8fGSUuNTrZHreU_s95xtmrbnCTB8LYOShnHaraaNDqoUnziBnVe2Rh6OAlJpU9ZSpF84L0-k23aokXc6aJdWswRdyGowycFswnENPgO9tfnUyUaMa2VjW8lGJYkmhPbnJhSE0zC0BdoSTdae8pmGnQwaAXzVlJJRhWYysiO1yf2n_lREj8nVxarkGub1OLnfLI4QrhAiAGV-AZTWnZg1MCqdpNi1pBSjb6RIPFAzXw0h_iTQCqrp</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</v>
       </c>
       <c r="AA60" t="str">
         <v/>
@@ -11406,22 +11406,22 @@
         <v/>
       </c>
       <c r="AE60" t="str">
-        <v>men-009</v>
+        <v>men-011</v>
       </c>
       <c r="AF60" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG60" t="str">
-        <v>Foundry Pleat Short</v>
+        <v>Alpine Field Parka</v>
       </c>
       <c r="AH60" t="str">
-        <v>250</v>
+        <v>980</v>
       </c>
       <c r="AI60" t="str">
-        <v>Tumbled Cotton Poplin</v>
+        <v>Technical Cotton Shell</v>
       </c>
       <c r="AJ60" t="str">
-        <v>A pleated short that keeps the men's edit crisp in lighter weather.</v>
+        <v>A weather-ready parka tuned for the same quiet palette as the men's rail.</v>
       </c>
       <c r="AK60" t="str">
         <v/>
@@ -11513,7 +11513,7 @@
         <v/>
       </c>
       <c r="E61" t="str">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F61" t="str">
         <v/>
@@ -11570,13 +11570,13 @@
         <v/>
       </c>
       <c r="X61" t="str">
-        <v>Shirting</v>
+        <v>Tailoring</v>
       </c>
       <c r="Y61" t="str">
         <v/>
       </c>
       <c r="Z61" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</v>
       </c>
       <c r="AA61" t="str">
         <v/>
@@ -11591,22 +11591,22 @@
         <v/>
       </c>
       <c r="AE61" t="str">
-        <v>men-010</v>
+        <v>men-012</v>
       </c>
       <c r="AF61" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG61" t="str">
-        <v>Tailored Poplin Bandshirt</v>
+        <v>Slate Double Pleat Trouser</v>
       </c>
       <c r="AH61" t="str">
-        <v>280</v>
+        <v>390</v>
       </c>
       <c r="AI61" t="str">
-        <v>Compact Cotton Poplin</v>
+        <v>Worsted Wool Blend</v>
       </c>
       <c r="AJ61" t="str">
-        <v>Band-collar shirting with a sharper placket and longer line.</v>
+        <v>Double pleats and a longer rise make this trouser sit with more authority.</v>
       </c>
       <c r="AK61" t="str">
         <v/>
@@ -11698,7 +11698,7 @@
         <v/>
       </c>
       <c r="E62" t="str">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F62" t="str">
         <v/>
@@ -11707,7 +11707,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>/categories/Shop%20Men</v>
+        <v>/products/550e8400-e29b-41d4-a716-446655440001</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -11755,13 +11755,13 @@
         <v/>
       </c>
       <c r="X62" t="str">
-        <v>Outerwear</v>
+        <v>Men</v>
       </c>
       <c r="Y62" t="str">
         <v/>
       </c>
       <c r="Z62" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</v>
+        <v>https://example.com/images/sm002-s.jpg</v>
       </c>
       <c r="AA62" t="str">
         <v/>
@@ -11776,22 +11776,22 @@
         <v/>
       </c>
       <c r="AE62" t="str">
-        <v>men-011</v>
+        <v>550e8400-e29b-41d4-a716-446655440001</v>
       </c>
       <c r="AF62" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG62" t="str">
-        <v>Alpine Field Parka</v>
+        <v>Cotton Tee</v>
       </c>
       <c r="AH62" t="str">
-        <v>980</v>
+        <v>49.99</v>
       </c>
       <c r="AI62" t="str">
-        <v>Technical Cotton Shell</v>
+        <v>S / Navy</v>
       </c>
       <c r="AJ62" t="str">
-        <v>A weather-ready parka tuned for the same quiet palette as the men's rail.</v>
+        <v/>
       </c>
       <c r="AK62" t="str">
         <v/>
@@ -11883,7 +11883,7 @@
         <v/>
       </c>
       <c r="E63" t="str">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F63" t="str">
         <v/>
@@ -11892,7 +11892,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>/categories/Shop%20Men</v>
+        <v>/products/550e8400-e29b-41d4-a716-446655440000</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -11940,13 +11940,13 @@
         <v/>
       </c>
       <c r="X63" t="str">
-        <v>Tailoring</v>
+        <v>Men</v>
       </c>
       <c r="Y63" t="str">
         <v/>
       </c>
       <c r="Z63" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</v>
+        <v>https://example.com/images/sm001-m.jpg</v>
       </c>
       <c r="AA63" t="str">
         <v/>
@@ -11961,22 +11961,22 @@
         <v/>
       </c>
       <c r="AE63" t="str">
-        <v>men-012</v>
+        <v>550e8400-e29b-41d4-a716-446655440000</v>
       </c>
       <c r="AF63" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG63" t="str">
-        <v>Slate Double Pleat Trouser</v>
+        <v>Linen Shirt</v>
       </c>
       <c r="AH63" t="str">
-        <v>390</v>
+        <v>129.99</v>
       </c>
       <c r="AI63" t="str">
-        <v>Worsted Wool Blend</v>
+        <v>M / White</v>
       </c>
       <c r="AJ63" t="str">
-        <v>Double pleats and a longer rise make this trouser sit with more authority.</v>
+        <v/>
       </c>
       <c r="AK63" t="str">
         <v/>
@@ -12068,7 +12068,7 @@
         <v/>
       </c>
       <c r="E64" t="str">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F64" t="str">
         <v/>
@@ -12077,13 +12077,13 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>/products/550e8400-e29b-41d4-a716-446655440001</v>
+        <v>/categories/Shop%20Women</v>
       </c>
       <c r="I64" t="str">
         <v/>
       </c>
       <c r="J64" t="str">
-        <v>nam</v>
+        <v>nu</v>
       </c>
       <c r="K64" t="str">
         <v/>
@@ -12125,13 +12125,13 @@
         <v/>
       </c>
       <c r="X64" t="str">
-        <v>Men</v>
+        <v>New Arrival</v>
       </c>
       <c r="Y64" t="str">
         <v/>
       </c>
       <c r="Z64" t="str">
-        <v>https://example.com/images/sm002-s.jpg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</v>
       </c>
       <c r="AA64" t="str">
         <v/>
@@ -12146,22 +12146,22 @@
         <v/>
       </c>
       <c r="AE64" t="str">
-        <v>550e8400-e29b-41d4-a716-446655440001</v>
+        <v>women-001</v>
       </c>
       <c r="AF64" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG64" t="str">
-        <v>Cotton Tee</v>
+        <v>Ethereal Silk Slip</v>
       </c>
       <c r="AH64" t="str">
-        <v>49.99</v>
+        <v>340</v>
       </c>
       <c r="AI64" t="str">
-        <v>S / Navy</v>
+        <v>Mulberry Silk</v>
       </c>
       <c r="AJ64" t="str">
-        <v/>
+        <v>A fluid dress that opens the women's story with a lighter touch.</v>
       </c>
       <c r="AK64" t="str">
         <v/>
@@ -12253,7 +12253,7 @@
         <v/>
       </c>
       <c r="E65" t="str">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F65" t="str">
         <v/>
@@ -12262,13 +12262,13 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>/products/550e8400-e29b-41d4-a716-446655440000</v>
+        <v>/categories/Shop%20Women</v>
       </c>
       <c r="I65" t="str">
         <v/>
       </c>
       <c r="J65" t="str">
-        <v>nam</v>
+        <v>nu</v>
       </c>
       <c r="K65" t="str">
         <v/>
@@ -12310,13 +12310,13 @@
         <v/>
       </c>
       <c r="X65" t="str">
-        <v>Men</v>
+        <v>Bottoms</v>
       </c>
       <c r="Y65" t="str">
         <v/>
       </c>
       <c r="Z65" t="str">
-        <v>https://example.com/images/sm001-m.jpg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAULIeOGtZd7vXZH0gSJHWiv3w1w4d6Tz7E7Y55Pp0wpbrudgRPkQEUxLNJ7z1iX2ofjNS4KSwbIFdzRgJR2rZEzslEi02TskRTUycOtweLNiBcTRv0RAiCUncTPXaXvHGzovAfwglQIxRlDavgkG0kp9z1__77ZtFulQa4AVlvR_muVhFSILTRpDDYMIgzrzsCEPjKJNyVc0k_NtV_qrK021aTU5RlI_Mg4TBu8JIzJLGkLHTEGfvWBezAYGbi6wNp_bgFRdeYEwST</v>
       </c>
       <c r="AA65" t="str">
         <v/>
@@ -12331,22 +12331,22 @@
         <v/>
       </c>
       <c r="AE65" t="str">
-        <v>550e8400-e29b-41d4-a716-446655440000</v>
+        <v>women-004</v>
       </c>
       <c r="AF65" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG65" t="str">
-        <v>Linen Shirt</v>
+        <v>Sculptural Pleated Skirt</v>
       </c>
       <c r="AH65" t="str">
-        <v>129.99</v>
+        <v>490</v>
       </c>
       <c r="AI65" t="str">
-        <v>M / White</v>
+        <v>Pleated Wool Crepe</v>
       </c>
       <c r="AJ65" t="str">
-        <v/>
+        <v>Pleated movement with a cleaner, more architectural waistline.</v>
       </c>
       <c r="AK65" t="str">
         <v/>
@@ -12438,7 +12438,7 @@
         <v/>
       </c>
       <c r="E66" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66" t="str">
         <v/>
@@ -12495,13 +12495,13 @@
         <v/>
       </c>
       <c r="X66" t="str">
-        <v>New Arrival</v>
+        <v>Bottoms</v>
       </c>
       <c r="Y66" t="str">
         <v/>
       </c>
       <c r="Z66" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</v>
       </c>
       <c r="AA66" t="str">
         <v/>
@@ -12516,22 +12516,22 @@
         <v/>
       </c>
       <c r="AE66" t="str">
-        <v>women-001</v>
+        <v>women-005</v>
       </c>
       <c r="AF66" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG66" t="str">
-        <v>Ethereal Silk Slip</v>
+        <v>Hearth Tapered Pant</v>
       </c>
       <c r="AH66" t="str">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AI66" t="str">
-        <v>Mulberry Silk</v>
+        <v>Brushed Wool Blend</v>
       </c>
       <c r="AJ66" t="str">
-        <v>A fluid dress that opens the women's story with a lighter touch.</v>
+        <v>A tapered trouser used to ground the softer tops in the womenÃÂÃÂ¢ÃÂÃÂÃÂÃÂs rail.</v>
       </c>
       <c r="AK66" t="str">
         <v/>
@@ -12623,7 +12623,7 @@
         <v/>
       </c>
       <c r="E67" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F67" t="str">
         <v/>
@@ -12680,13 +12680,13 @@
         <v/>
       </c>
       <c r="X67" t="str">
-        <v>Limited</v>
+        <v>Outerwear</v>
       </c>
       <c r="Y67" t="str">
         <v/>
       </c>
       <c r="Z67" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</v>
       </c>
       <c r="AA67" t="str">
         <v/>
@@ -12701,22 +12701,22 @@
         <v/>
       </c>
       <c r="AE67" t="str">
-        <v>women-002</v>
+        <v>women-006</v>
       </c>
       <c r="AF67" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG67" t="str">
-        <v>Architectural Overcoat</v>
+        <v>Atelier Formal Blazer</v>
       </c>
       <c r="AH67" t="str">
-        <v>1250</v>
+        <v>850</v>
       </c>
       <c r="AI67" t="str">
-        <v>Structured Wool Twill</v>
+        <v>Tailored Wool Blend</v>
       </c>
       <c r="AJ67" t="str">
-        <v>Sharper outerwear line pulled into the womenÃ¢ÂÂs edit for contrast.</v>
+        <v>A cleaner blazer silhouette that adds structure without crowding the rail.</v>
       </c>
       <c r="AK67" t="str">
         <v/>
@@ -12808,7 +12808,7 @@
         <v/>
       </c>
       <c r="E68" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F68" t="str">
         <v/>
@@ -12865,13 +12865,13 @@
         <v/>
       </c>
       <c r="X68" t="str">
-        <v>Knitwear</v>
+        <v>Draped</v>
       </c>
       <c r="Y68" t="str">
         <v/>
       </c>
       <c r="Z68" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBEKFEZ7Xk7Fyqc9Uf8Rr7JfhPIghhY7j0HO6bqSglckdRAUU1XFK1Vy_uPXAbpLqczXmCH41FFfT4QIgBtt7oBHhaEojRqYoMhEeW0zN9yDlgFxnnAhZfa_FjmfnZNakXUp-HAT6D2gb_BUeHA5TXBmMVsObd_AHQfOwPuMZTKrAqSkXnJe60KUnlOWajJ6btQ5zyNadwls33tVZNcDlHyJ8_EUlUAhHRtQ90ZhEzMNN5Mzjf_Hr7Onn7MZF-hkz45XkPrdm6pngSw</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</v>
       </c>
       <c r="AA68" t="str">
         <v/>
@@ -12886,22 +12886,22 @@
         <v/>
       </c>
       <c r="AE68" t="str">
-        <v>women-003</v>
+        <v>women-007</v>
       </c>
       <c r="AF68" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG68" t="str">
-        <v>Cloud Cashmere Crew</v>
+        <v>Botanical Wrap Dress</v>
       </c>
       <c r="AH68" t="str">
-        <v>280</v>
+        <v>410</v>
       </c>
       <c r="AI68" t="str">
-        <v>Pure Cashmere</v>
+        <v>Washed Silk Blend</v>
       </c>
       <c r="AJ68" t="str">
-        <v>A softer knit layer that keeps the womenÃ¢ÂÂs tab calm and tactile.</v>
+        <v>A wrapped silhouette that keeps the womenÃÂÃÂ¢ÃÂÃÂÃÂÃÂs page light and fluid.</v>
       </c>
       <c r="AK68" t="str">
         <v/>
@@ -12993,7 +12993,7 @@
         <v/>
       </c>
       <c r="E69" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F69" t="str">
         <v/>
@@ -13050,13 +13050,13 @@
         <v/>
       </c>
       <c r="X69" t="str">
-        <v>Bottoms</v>
+        <v>Studio Essential</v>
       </c>
       <c r="Y69" t="str">
         <v/>
       </c>
       <c r="Z69" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAULIeOGtZd7vXZH0gSJHWiv3w1w4d6Tz7E7Y55Pp0wpbrudgRPkQEUxLNJ7z1iX2ofjNS4KSwbIFdzRgJR2rZEzslEi02TskRTUycOtweLNiBcTRv0RAiCUncTPXaXvHGzovAfwglQIxRlDavgkG0kp9z1__77ZtFulQa4AVlvR_muVhFSILTRpDDYMIgzrzsCEPjKJNyVc0k_NtV_qrK021aTU5RlI_Mg4TBu8JIzJLGkLHTEGfvWBezAYGbi6wNp_bgFRdeYEwST</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBEKFEZ7Xk7Fyqc9Uf8Rr7JfhPIghhY7j0HO6bqSglckdRAUU1XFK1Vy_uPXAbpLqczXmCH41FFfT4QIgBtt7oBHhaEojRqYoMhEeW0zN9yDlgFxnnAhZfa_FjmfnZNakXUp-HAT6D2gb_BUeHA5TXBmMVsObd_AHQfOwPuMZTKrAqSkXnJe60KUnlOWajJ6btQ5zyNadwls33tVZNcDlHyJ8_EUlUAhHRtQ90ZhEzMNN5Mzjf_Hr7Onn7MZF-hkz45XkPrdm6pngSw</v>
       </c>
       <c r="AA69" t="str">
         <v/>
@@ -13071,22 +13071,22 @@
         <v/>
       </c>
       <c r="AE69" t="str">
-        <v>women-004</v>
+        <v>women-008</v>
       </c>
       <c r="AF69" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG69" t="str">
-        <v>Sculptural Pleated Skirt</v>
+        <v>Gallery Satin Blouse</v>
       </c>
       <c r="AH69" t="str">
-        <v>490</v>
+        <v>295</v>
       </c>
       <c r="AI69" t="str">
-        <v>Pleated Wool Crepe</v>
+        <v>Liquid Satin</v>
       </c>
       <c r="AJ69" t="str">
-        <v>Pleated movement with a cleaner, more architectural waistline.</v>
+        <v>A polished blouse designed to pair with skirts and tailored trousers alike.</v>
       </c>
       <c r="AK69" t="str">
         <v/>
@@ -13178,7 +13178,7 @@
         <v/>
       </c>
       <c r="E70" t="str">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F70" t="str">
         <v/>
@@ -13235,13 +13235,13 @@
         <v/>
       </c>
       <c r="X70" t="str">
-        <v>Bottoms</v>
+        <v>Editorial Pick</v>
       </c>
       <c r="Y70" t="str">
         <v/>
       </c>
       <c r="Z70" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAULIeOGtZd7vXZH0gSJHWiv3w1w4d6Tz7E7Y55Pp0wpbrudgRPkQEUxLNJ7z1iX2ofjNS4KSwbIFdzRgJR2rZEzslEi02TskRTUycOtweLNiBcTRv0RAiCUncTPXaXvHGzovAfwglQIxRlDavgkG0kp9z1__77ZtFulQa4AVlvR_muVhFSILTRpDDYMIgzrzsCEPjKJNyVc0k_NtV_qrK021aTU5RlI_Mg4TBu8JIzJLGkLHTEGfvWBezAYGbi6wNp_bgFRdeYEwST</v>
       </c>
       <c r="AA70" t="str">
         <v/>
@@ -13256,22 +13256,22 @@
         <v/>
       </c>
       <c r="AE70" t="str">
-        <v>women-005</v>
+        <v>women-009</v>
       </c>
       <c r="AF70" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG70" t="str">
-        <v>Hearth Tapered Pant</v>
+        <v>Quiet Wool Column Coat</v>
       </c>
       <c r="AH70" t="str">
-        <v>320</v>
+        <v>1180</v>
       </c>
       <c r="AI70" t="str">
-        <v>Brushed Wool Blend</v>
+        <v>Double-Faced Wool</v>
       </c>
       <c r="AJ70" t="str">
-        <v>A tapered trouser used to ground the softer tops in the womenÃ¢ÂÂs rail.</v>
+        <v>A longline column coat used to deepen the winter story of the page.</v>
       </c>
       <c r="AK70" t="str">
         <v/>
@@ -13363,7 +13363,7 @@
         <v/>
       </c>
       <c r="E71" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F71" t="str">
         <v/>
@@ -13420,13 +13420,13 @@
         <v/>
       </c>
       <c r="X71" t="str">
-        <v>Outerwear</v>
+        <v>Tailored Bottoms</v>
       </c>
       <c r="Y71" t="str">
         <v/>
       </c>
       <c r="Z71" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</v>
       </c>
       <c r="AA71" t="str">
         <v/>
@@ -13441,22 +13441,22 @@
         <v/>
       </c>
       <c r="AE71" t="str">
-        <v>women-006</v>
+        <v>women-010</v>
       </c>
       <c r="AF71" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG71" t="str">
-        <v>Atelier Formal Blazer</v>
+        <v>Soft Structure Trouser</v>
       </c>
       <c r="AH71" t="str">
-        <v>850</v>
+        <v>365</v>
       </c>
       <c r="AI71" t="str">
-        <v>Tailored Wool Blend</v>
+        <v>Compact Viscose Twill</v>
       </c>
       <c r="AJ71" t="str">
-        <v>A cleaner blazer silhouette that adds structure without crowding the rail.</v>
+        <v>A clean trouser designed to bring sharper rhythm to fluid tops.</v>
       </c>
       <c r="AK71" t="str">
         <v/>
@@ -13548,7 +13548,7 @@
         <v/>
       </c>
       <c r="E72" t="str">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F72" t="str">
         <v/>
@@ -13605,13 +13605,13 @@
         <v/>
       </c>
       <c r="X72" t="str">
-        <v>Draped</v>
+        <v>Layering</v>
       </c>
       <c r="Y72" t="str">
         <v/>
       </c>
       <c r="Z72" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</v>
       </c>
       <c r="AA72" t="str">
         <v/>
@@ -13626,22 +13626,22 @@
         <v/>
       </c>
       <c r="AE72" t="str">
-        <v>women-007</v>
+        <v>women-011</v>
       </c>
       <c r="AF72" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG72" t="str">
-        <v>Botanical Wrap Dress</v>
+        <v>Moonstone Rib Tank</v>
       </c>
       <c r="AH72" t="str">
-        <v>410</v>
+        <v>180</v>
       </c>
       <c r="AI72" t="str">
-        <v>Washed Silk Blend</v>
+        <v>Fine Rib Cotton</v>
       </c>
       <c r="AJ72" t="str">
-        <v>A wrapped silhouette that keeps the womenÃ¢ÂÂs page light and fluid.</v>
+        <v>A minimal base layer for pairing beneath blazers and coats.</v>
       </c>
       <c r="AK72" t="str">
         <v/>
@@ -13733,7 +13733,7 @@
         <v/>
       </c>
       <c r="E73" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F73" t="str">
         <v/>
@@ -13790,13 +13790,13 @@
         <v/>
       </c>
       <c r="X73" t="str">
-        <v>Studio Essential</v>
+        <v>Fluid Line</v>
       </c>
       <c r="Y73" t="str">
         <v/>
       </c>
       <c r="Z73" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBEKFEZ7Xk7Fyqc9Uf8Rr7JfhPIghhY7j0HO6bqSglckdRAUU1XFK1Vy_uPXAbpLqczXmCH41FFfT4QIgBtt7oBHhaEojRqYoMhEeW0zN9yDlgFxnnAhZfa_FjmfnZNakXUp-HAT6D2gb_BUeHA5TXBmMVsObd_AHQfOwPuMZTKrAqSkXnJe60KUnlOWajJ6btQ5zyNadwls33tVZNcDlHyJ8_EUlUAhHRtQ90ZhEzMNN5Mzjf_Hr7Onn7MZF-hkz45XkPrdm6pngSw</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</v>
       </c>
       <c r="AA73" t="str">
         <v/>
@@ -13811,22 +13811,22 @@
         <v/>
       </c>
       <c r="AE73" t="str">
-        <v>women-008</v>
+        <v>women-012</v>
       </c>
       <c r="AF73" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG73" t="str">
-        <v>Gallery Satin Blouse</v>
+        <v>Atelier Bias Midi Skirt</v>
       </c>
       <c r="AH73" t="str">
-        <v>295</v>
+        <v>430</v>
       </c>
       <c r="AI73" t="str">
-        <v>Liquid Satin</v>
+        <v>Washed Satin</v>
       </c>
       <c r="AJ73" t="str">
-        <v>A polished blouse designed to pair with skirts and tailored trousers alike.</v>
+        <v>A bias-cut skirt that keeps the lower half of the page moving softly.</v>
       </c>
       <c r="AK73" t="str">
         <v/>
@@ -13918,7 +13918,7 @@
         <v/>
       </c>
       <c r="E74" t="str">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F74" t="str">
         <v/>
@@ -13927,7 +13927,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>/categories/Shop%20Women</v>
+        <v>/products/550e8400-e29b-41d4-a716-446655440002</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -13975,13 +13975,13 @@
         <v/>
       </c>
       <c r="X74" t="str">
-        <v>Editorial Pick</v>
+        <v>Women</v>
       </c>
       <c r="Y74" t="str">
         <v/>
       </c>
       <c r="Z74" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAULIeOGtZd7vXZH0gSJHWiv3w1w4d6Tz7E7Y55Pp0wpbrudgRPkQEUxLNJ7z1iX2ofjNS4KSwbIFdzRgJR2rZEzslEi02TskRTUycOtweLNiBcTRv0RAiCUncTPXaXvHGzovAfwglQIxRlDavgkG0kp9z1__77ZtFulQa4AVlvR_muVhFSILTRpDDYMIgzrzsCEPjKJNyVc0k_NtV_qrK021aTU5RlI_Mg4TBu8JIzJLGkLHTEGfvWBezAYGbi6wNp_bgFRdeYEwST</v>
+        <v/>
       </c>
       <c r="AA74" t="str">
         <v/>
@@ -13996,22 +13996,22 @@
         <v/>
       </c>
       <c r="AE74" t="str">
-        <v>women-009</v>
+        <v>550e8400-e29b-41d4-a716-446655440002</v>
       </c>
       <c r="AF74" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG74" t="str">
-        <v>Quiet Wool Column Coat</v>
+        <v>Silk Dress</v>
       </c>
       <c r="AH74" t="str">
-        <v>1180</v>
+        <v>229</v>
       </c>
       <c r="AI74" t="str">
-        <v>Double-Faced Wool</v>
+        <v>Women</v>
       </c>
       <c r="AJ74" t="str">
-        <v>A longline column coat used to deepen the winter story of the page.</v>
+        <v/>
       </c>
       <c r="AK74" t="str">
         <v/>
@@ -14103,7 +14103,7 @@
         <v/>
       </c>
       <c r="E75" t="str">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F75" t="str">
         <v/>
@@ -14112,7 +14112,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>/categories/Shop%20Women</v>
+        <v>/products/10000000-0000-4000-8000-000000000014</v>
       </c>
       <c r="I75" t="str">
         <v/>
@@ -14160,13 +14160,13 @@
         <v/>
       </c>
       <c r="X75" t="str">
-        <v>Tailored Bottoms</v>
+        <v>Limited</v>
       </c>
       <c r="Y75" t="str">
         <v/>
       </c>
       <c r="Z75" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</v>
       </c>
       <c r="AA75" t="str">
         <v/>
@@ -14181,22 +14181,22 @@
         <v/>
       </c>
       <c r="AE75" t="str">
-        <v>women-010</v>
+        <v>10000000-0000-4000-8000-000000000014</v>
       </c>
       <c r="AF75" t="str">
-        <v>ND Atelier</v>
+        <v>ND Shop</v>
       </c>
       <c r="AG75" t="str">
-        <v>Soft Structure Trouser</v>
+        <v>Architectural Overcoat</v>
       </c>
       <c r="AH75" t="str">
-        <v>365</v>
+        <v>1250</v>
       </c>
       <c r="AI75" t="str">
-        <v>Compact Viscose Twill</v>
+        <v>M / Forest</v>
       </c>
       <c r="AJ75" t="str">
-        <v>A clean trouser designed to bring sharper rhythm to fluid tops.</v>
+        <v>Sharper outerwear line pulled into the womenÃÂÃÂ¢ÃÂÃÂÃÂÃÂs edit for contrast. Curated into the All Archive rail for a fuller workbook seed.</v>
       </c>
       <c r="AK75" t="str">
         <v/>
@@ -14288,7 +14288,7 @@
         <v/>
       </c>
       <c r="E76" t="str">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F76" t="str">
         <v/>
@@ -14297,7 +14297,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>/categories/Shop%20Women</v>
+        <v>/products/10000000-0000-4000-8000-000000000015</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -14345,13 +14345,13 @@
         <v/>
       </c>
       <c r="X76" t="str">
-        <v>Layering</v>
+        <v>Knitwear</v>
       </c>
       <c r="Y76" t="str">
         <v/>
       </c>
       <c r="Z76" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBEKFEZ7Xk7Fyqc9Uf8Rr7JfhPIghhY7j0HO6bqSglckdRAUU1XFK1Vy_uPXAbpLqczXmCH41FFfT4QIgBtt7oBHhaEojRqYoMhEeW0zN9yDlgFxnnAhZfa_FjmfnZNakXUp-HAT6D2gb_BUeHA5TXBmMVsObd_AHQfOwPuMZTKrAqSkXnJe60KUnlOWajJ6btQ5zyNadwls33tVZNcDlHyJ8_EUlUAhHRtQ90ZhEzMNN5Mzjf_Hr7Onn7MZF-hkz45XkPrdm6pngSw</v>
       </c>
       <c r="AA76" t="str">
         <v/>
@@ -14366,22 +14366,22 @@
         <v/>
       </c>
       <c r="AE76" t="str">
-        <v>women-011</v>
+        <v>10000000-0000-4000-8000-000000000015</v>
       </c>
       <c r="AF76" t="str">
-        <v>ND Atelier</v>
+        <v>ND Shop</v>
       </c>
       <c r="AG76" t="str">
-        <v>Moonstone Rib Tank</v>
+        <v>Cloud Cashmere Crew</v>
       </c>
       <c r="AH76" t="str">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="AI76" t="str">
-        <v>Fine Rib Cotton</v>
+        <v>M / Stone</v>
       </c>
       <c r="AJ76" t="str">
-        <v>A minimal base layer for pairing beneath blazers and coats.</v>
+        <v>A softer knit layer that keeps the womenÃÂÃÂ¢ÃÂÃÂÃÂÃÂs tab calm and tactile. Curated into the All Archive rail for a fuller workbook seed.</v>
       </c>
       <c r="AK76" t="str">
         <v/>
@@ -14473,7 +14473,7 @@
         <v/>
       </c>
       <c r="E77" t="str">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F77" t="str">
         <v/>
@@ -14482,13 +14482,13 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>/categories/Shop%20Women</v>
+        <v>/categories/Accessories</v>
       </c>
       <c r="I77" t="str">
         <v/>
       </c>
       <c r="J77" t="str">
-        <v>nu</v>
+        <v>accessories</v>
       </c>
       <c r="K77" t="str">
         <v/>
@@ -14530,13 +14530,13 @@
         <v/>
       </c>
       <c r="X77" t="str">
-        <v>Fluid Line</v>
+        <v>Limited Edition</v>
       </c>
       <c r="Y77" t="str">
         <v/>
       </c>
       <c r="Z77" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
       </c>
       <c r="AA77" t="str">
         <v/>
@@ -14551,22 +14551,22 @@
         <v/>
       </c>
       <c r="AE77" t="str">
-        <v>women-012</v>
+        <v>accessories-001</v>
       </c>
       <c r="AF77" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG77" t="str">
-        <v>Atelier Bias Midi Skirt</v>
+        <v>Atelier Tote</v>
       </c>
       <c r="AH77" t="str">
-        <v>430</v>
+        <v>840</v>
       </c>
       <c r="AI77" t="str">
-        <v>Washed Satin</v>
+        <v>Vegetable Tanned Leather</v>
       </c>
       <c r="AJ77" t="str">
-        <v>A bias-cut skirt that keeps the lower half of the page moving softly.</v>
+        <v>A structured tote that leads the accessory story with more presence.</v>
       </c>
       <c r="AK77" t="str">
         <v/>
@@ -14658,7 +14658,7 @@
         <v/>
       </c>
       <c r="E78" t="str">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F78" t="str">
         <v/>
@@ -14667,13 +14667,13 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>/products/550e8400-e29b-41d4-a716-446655440002</v>
+        <v>/categories/Accessories</v>
       </c>
       <c r="I78" t="str">
         <v/>
       </c>
       <c r="J78" t="str">
-        <v>nu</v>
+        <v>accessories</v>
       </c>
       <c r="K78" t="str">
         <v/>
@@ -14715,13 +14715,13 @@
         <v/>
       </c>
       <c r="X78" t="str">
-        <v>Women</v>
+        <v>Essential</v>
       </c>
       <c r="Y78" t="str">
         <v/>
       </c>
       <c r="Z78" t="str">
-        <v/>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
       </c>
       <c r="AA78" t="str">
         <v/>
@@ -14736,22 +14736,22 @@
         <v/>
       </c>
       <c r="AE78" t="str">
-        <v>550e8400-e29b-41d4-a716-446655440002</v>
+        <v>accessories-002</v>
       </c>
       <c r="AF78" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG78" t="str">
-        <v>Silk Dress</v>
+        <v>Aurora Wrap</v>
       </c>
       <c r="AH78" t="str">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="AI78" t="str">
-        <v>Women</v>
+        <v>Organic Raw Silk</v>
       </c>
       <c r="AJ78" t="str">
-        <v/>
+        <v>A lighter textile accent to soften the accessory rail.</v>
       </c>
       <c r="AK78" t="str">
         <v/>
@@ -14843,7 +14843,7 @@
         <v/>
       </c>
       <c r="E79" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F79" t="str">
         <v/>
@@ -14900,13 +14900,13 @@
         <v/>
       </c>
       <c r="X79" t="str">
-        <v>Limited Edition</v>
+        <v>Leather Detail</v>
       </c>
       <c r="Y79" t="str">
         <v/>
       </c>
       <c r="Z79" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDclyoI7lW_Aez2lBayMz4ES5BVdH-wo43IL4ZwpD4HLQkaJqfV3eDM-qMUs4V8Uyl6BTZ9FSNg7ExFisE6J-TMxcflCy5mFritcP54bDT49eqwGnwGnsOeheOgbCmpdtfGvnHaqpfmRpU4zQvBD7B4tmigGgv7hCDEHWLojIzOlAfe5p-0cCnzLjktClPIw5lG6h2qfT0buVNcsY57FFriSrjdMpV_jPcwn3Dwsz1C-8IS20dhOYE1-Kak6Hi0R-OiEeULdIqMBj2c</v>
       </c>
       <c r="AA79" t="str">
         <v/>
@@ -14921,22 +14921,22 @@
         <v/>
       </c>
       <c r="AE79" t="str">
-        <v>accessories-001</v>
+        <v>accessories-003</v>
       </c>
       <c r="AF79" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG79" t="str">
-        <v>Atelier Tote</v>
+        <v>Cintura Belt</v>
       </c>
       <c r="AH79" t="str">
-        <v>840</v>
+        <v>165</v>
       </c>
       <c r="AI79" t="str">
-        <v>Vegetable Tanned Leather</v>
+        <v>Full Grain Saddle Leather</v>
       </c>
       <c r="AJ79" t="str">
-        <v>A structured tote that leads the accessory story with more presence.</v>
+        <v>A structured belt detail pulled into the accessory catalog.</v>
       </c>
       <c r="AK79" t="str">
         <v/>
@@ -15028,7 +15028,7 @@
         <v/>
       </c>
       <c r="E80" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F80" t="str">
         <v/>
@@ -15085,13 +15085,13 @@
         <v/>
       </c>
       <c r="X80" t="str">
-        <v>Essential</v>
+        <v>Leather Detail</v>
       </c>
       <c r="Y80" t="str">
         <v/>
       </c>
       <c r="Z80" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAc-xgefZmjRHW4tYawNPs3ljWfgQ66YMBuFgX39XflOo-rQyjbJ2Ju2V0nLkyj2SVuz2BKsp1ucM74P4Gg2Q-TiJKsqrjsQRpxYORvaVExN0KFMkAU9KQFmWEmtNZHK5dm7iBBb1zYMTsluHO4Em5IwIi3lS3JGSUeU_unqmYgh-Fw65tcUaH2Ywxl8ag7h1znu1rGefQrkuDTARLHNwtQdpiGPKWCCp8JpO_yLO4kKGzLmwj8g3VfRzxs02GzkmBt2St6l1zyFYZU</v>
       </c>
       <c r="AA80" t="str">
         <v/>
@@ -15106,22 +15106,22 @@
         <v/>
       </c>
       <c r="AE80" t="str">
-        <v>accessories-002</v>
+        <v>accessories-004</v>
       </c>
       <c r="AF80" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG80" t="str">
-        <v>Aurora Wrap</v>
+        <v>Vault Clutch</v>
       </c>
       <c r="AH80" t="str">
-        <v>215</v>
+        <v>420</v>
       </c>
       <c r="AI80" t="str">
-        <v>Organic Raw Silk</v>
+        <v>Nappa Leather</v>
       </c>
       <c r="AJ80" t="str">
-        <v>A lighter textile accent to soften the accessory rail.</v>
+        <v>Compact Nappa leather shape used to finish the accessory story.</v>
       </c>
       <c r="AK80" t="str">
         <v/>
@@ -15213,7 +15213,7 @@
         <v/>
       </c>
       <c r="E81" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F81" t="str">
         <v/>
@@ -15270,13 +15270,13 @@
         <v/>
       </c>
       <c r="X81" t="str">
-        <v>Leather Detail</v>
+        <v>Limited Edition</v>
       </c>
       <c r="Y81" t="str">
         <v/>
       </c>
       <c r="Z81" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDclyoI7lW_Aez2lBayMz4ES5BVdH-wo43IL4ZwpD4HLQkaJqfV3eDM-qMUs4V8Uyl6BTZ9FSNg7ExFisE6J-TMxcflCy5mFritcP54bDT49eqwGnwGnsOeheOgbCmpdtfGvnHaqpfmRpU4zQvBD7B4tmigGgv7hCDEHWLojIzOlAfe5p-0cCnzLjktClPIw5lG6h2qfT0buVNcsY57FFriSrjdMpV_jPcwn3Dwsz1C-8IS20dhOYE1-Kak6Hi0R-OiEeULdIqMBj2c</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDwib-yVKWuTMsi4heheiLMLuw3Aukcrj4t8F5TLsWcUDULrkliTF_b5hFcyekqcaoBOrRCOob6yU3tV5aJCQChHBAggBedojt1THWZ_F-1GiBclBPJw389BrO0MvSA5xrOo1ssievm9rXO2UiIT0Ix_tHvr6rnGAPSAVNt1DYmLJVg_7vuvdan2zI6d3Z7JsuFwAqcipqjdi0FbCpFwqD4d7bZrq5JeL4i4aGx5NsOkOBZScx3UPHkR_rmJldHJi3Cb4MoiZaIoNsN</v>
       </c>
       <c r="AA81" t="str">
         <v/>
@@ -15291,22 +15291,22 @@
         <v/>
       </c>
       <c r="AE81" t="str">
-        <v>accessories-003</v>
+        <v>accessories-005</v>
       </c>
       <c r="AF81" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG81" t="str">
-        <v>Cintura Belt</v>
+        <v>Obsidian Band</v>
       </c>
       <c r="AH81" t="str">
-        <v>165</v>
+        <v>310</v>
       </c>
       <c r="AI81" t="str">
-        <v>Full Grain Saddle Leather</v>
+        <v>925 Sterling Silver</v>
       </c>
       <c r="AJ81" t="str">
-        <v>A structured belt detail pulled into the accessory catalog.</v>
+        <v>A hand-finished ring that gives the accessories page more jewelry depth.</v>
       </c>
       <c r="AK81" t="str">
         <v/>
@@ -15398,7 +15398,7 @@
         <v/>
       </c>
       <c r="E82" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F82" t="str">
         <v/>
@@ -15455,13 +15455,13 @@
         <v/>
       </c>
       <c r="X82" t="str">
-        <v>Leather Detail</v>
+        <v>Soft Finish</v>
       </c>
       <c r="Y82" t="str">
         <v/>
       </c>
       <c r="Z82" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAc-xgefZmjRHW4tYawNPs3ljWfgQ66YMBuFgX39XflOo-rQyjbJ2Ju2V0nLkyj2SVuz2BKsp1ucM74P4Gg2Q-TiJKsqrjsQRpxYORvaVExN0KFMkAU9KQFmWEmtNZHK5dm7iBBb1zYMTsluHO4Em5IwIi3lS3JGSUeU_unqmYgh-Fw65tcUaH2Ywxl8ag7h1znu1rGefQrkuDTARLHNwtQdpiGPKWCCp8JpO_yLO4kKGzLmwj8g3VfRzxs02GzkmBt2St6l1zyFYZU</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
       </c>
       <c r="AA82" t="str">
         <v/>
@@ -15476,22 +15476,22 @@
         <v/>
       </c>
       <c r="AE82" t="str">
-        <v>accessories-004</v>
+        <v>accessories-006</v>
       </c>
       <c r="AF82" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG82" t="str">
-        <v>Vault Clutch</v>
+        <v>Mist Scarf</v>
       </c>
       <c r="AH82" t="str">
-        <v>420</v>
+        <v>190</v>
       </c>
       <c r="AI82" t="str">
-        <v>Nappa Leather</v>
+        <v>Cashmere Blend</v>
       </c>
       <c r="AJ82" t="str">
-        <v>Compact Nappa leather shape used to finish the accessory story.</v>
+        <v>A softer scarf that keeps the object rail warm and tactile.</v>
       </c>
       <c r="AK82" t="str">
         <v/>
@@ -15583,7 +15583,7 @@
         <v/>
       </c>
       <c r="E83" t="str">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F83" t="str">
         <v/>
@@ -15640,13 +15640,13 @@
         <v/>
       </c>
       <c r="X83" t="str">
-        <v>Limited Edition</v>
+        <v>Travel Object</v>
       </c>
       <c r="Y83" t="str">
         <v/>
       </c>
       <c r="Z83" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDwib-yVKWuTMsi4heheiLMLuw3Aukcrj4t8F5TLsWcUDULrkliTF_b5hFcyekqcaoBOrRCOob6yU3tV5aJCQChHBAggBedojt1THWZ_F-1GiBclBPJw389BrO0MvSA5xrOo1ssievm9rXO2UiIT0Ix_tHvr6rnGAPSAVNt1DYmLJVg_7vuvdan2zI6d3Z7JsuFwAqcipqjdi0FbCpFwqD4d7bZrq5JeL4i4aGx5NsOkOBZScx3UPHkR_rmJldHJi3Cb4MoiZaIoNsN</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
       </c>
       <c r="AA83" t="str">
         <v/>
@@ -15661,22 +15661,22 @@
         <v/>
       </c>
       <c r="AE83" t="str">
-        <v>accessories-005</v>
+        <v>accessories-007</v>
       </c>
       <c r="AF83" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG83" t="str">
-        <v>Obsidian Band</v>
+        <v>Meridian Weekender</v>
       </c>
       <c r="AH83" t="str">
-        <v>310</v>
+        <v>980</v>
       </c>
       <c r="AI83" t="str">
-        <v>925 Sterling Silver</v>
+        <v>Vachetta Leather</v>
       </c>
       <c r="AJ83" t="str">
-        <v>A hand-finished ring that gives the accessories page more jewelry depth.</v>
+        <v>A larger travel bag built to extend the accessory set beyond everyday pieces.</v>
       </c>
       <c r="AK83" t="str">
         <v/>
@@ -15768,7 +15768,7 @@
         <v/>
       </c>
       <c r="E84" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F84" t="str">
         <v/>
@@ -15825,13 +15825,13 @@
         <v/>
       </c>
       <c r="X84" t="str">
-        <v>Soft Finish</v>
+        <v>Daily Carry</v>
       </c>
       <c r="Y84" t="str">
         <v/>
       </c>
       <c r="Z84" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDclyoI7lW_Aez2lBayMz4ES5BVdH-wo43IL4ZwpD4HLQkaJqfV3eDM-qMUs4V8Uyl6BTZ9FSNg7ExFisE6J-TMxcflCy5mFritcP54bDT49eqwGnwGnsOeheOgbCmpdtfGvnHaqpfmRpU4zQvBD7B4tmigGgv7hCDEHWLojIzOlAfe5p-0cCnzLjktClPIw5lG6h2qfT0buVNcsY57FFriSrjdMpV_jPcwn3Dwsz1C-8IS20dhOYE1-Kak6Hi0R-OiEeULdIqMBj2c</v>
       </c>
       <c r="AA84" t="str">
         <v/>
@@ -15846,22 +15846,22 @@
         <v/>
       </c>
       <c r="AE84" t="str">
-        <v>accessories-006</v>
+        <v>accessories-008</v>
       </c>
       <c r="AF84" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG84" t="str">
-        <v>Mist Scarf</v>
+        <v>Sculptor Card Holder</v>
       </c>
       <c r="AH84" t="str">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="AI84" t="str">
-        <v>Cashmere Blend</v>
+        <v>Vachetta Leather</v>
       </c>
       <c r="AJ84" t="str">
-        <v>A softer scarf that keeps the object rail warm and tactile.</v>
+        <v>A slim card holder that adds a smaller-scale object to the grid.</v>
       </c>
       <c r="AK84" t="str">
         <v/>
@@ -15953,7 +15953,7 @@
         <v/>
       </c>
       <c r="E85" t="str">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F85" t="str">
         <v/>
@@ -16010,13 +16010,13 @@
         <v/>
       </c>
       <c r="X85" t="str">
-        <v>Travel Object</v>
+        <v>Utility Detail</v>
       </c>
       <c r="Y85" t="str">
         <v/>
       </c>
       <c r="Z85" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAc-xgefZmjRHW4tYawNPs3ljWfgQ66YMBuFgX39XflOo-rQyjbJ2Ju2V0nLkyj2SVuz2BKsp1ucM74P4Gg2Q-TiJKsqrjsQRpxYORvaVExN0KFMkAU9KQFmWEmtNZHK5dm7iBBb1zYMTsluHO4Em5IwIi3lS3JGSUeU_unqmYgh-Fw65tcUaH2Ywxl8ag7h1znu1rGefQrkuDTARLHNwtQdpiGPKWCCp8JpO_yLO4kKGzLmwj8g3VfRzxs02GzkmBt2St6l1zyFYZU</v>
       </c>
       <c r="AA85" t="str">
         <v/>
@@ -16031,22 +16031,22 @@
         <v/>
       </c>
       <c r="AE85" t="str">
-        <v>accessories-007</v>
+        <v>accessories-009</v>
       </c>
       <c r="AF85" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG85" t="str">
-        <v>Meridian Weekender</v>
+        <v>Studio Key Lanyard</v>
       </c>
       <c r="AH85" t="str">
-        <v>980</v>
+        <v>110</v>
       </c>
       <c r="AI85" t="str">
-        <v>Vachetta Leather</v>
+        <v>Bridle Leather</v>
       </c>
       <c r="AJ85" t="str">
-        <v>A larger travel bag built to extend the accessory set beyond everyday pieces.</v>
+        <v>A small leather object that rounds out the more functional side of the page.</v>
       </c>
       <c r="AK85" t="str">
         <v/>
@@ -16138,7 +16138,7 @@
         <v/>
       </c>
       <c r="E86" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F86" t="str">
         <v/>
@@ -16195,13 +16195,13 @@
         <v/>
       </c>
       <c r="X86" t="str">
-        <v>Daily Carry</v>
+        <v>Silk Accent</v>
       </c>
       <c r="Y86" t="str">
         <v/>
       </c>
       <c r="Z86" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDclyoI7lW_Aez2lBayMz4ES5BVdH-wo43IL4ZwpD4HLQkaJqfV3eDM-qMUs4V8Uyl6BTZ9FSNg7ExFisE6J-TMxcflCy5mFritcP54bDT49eqwGnwGnsOeheOgbCmpdtfGvnHaqpfmRpU4zQvBD7B4tmigGgv7hCDEHWLojIzOlAfe5p-0cCnzLjktClPIw5lG6h2qfT0buVNcsY57FFriSrjdMpV_jPcwn3Dwsz1C-8IS20dhOYE1-Kak6Hi0R-OiEeULdIqMBj2c</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDwib-yVKWuTMsi4heheiLMLuw3Aukcrj4t8F5TLsWcUDULrkliTF_b5hFcyekqcaoBOrRCOob6yU3tV5aJCQChHBAggBedojt1THWZ_F-1GiBclBPJw389BrO0MvSA5xrOo1ssievm9rXO2UiIT0Ix_tHvr6rnGAPSAVNt1DYmLJVg_7vuvdan2zI6d3Z7JsuFwAqcipqjdi0FbCpFwqD4d7bZrq5JeL4i4aGx5NsOkOBZScx3UPHkR_rmJldHJi3Cb4MoiZaIoNsN</v>
       </c>
       <c r="AA86" t="str">
         <v/>
@@ -16216,22 +16216,22 @@
         <v/>
       </c>
       <c r="AE86" t="str">
-        <v>accessories-008</v>
+        <v>accessories-010</v>
       </c>
       <c r="AF86" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG86" t="str">
-        <v>Sculptor Card Holder</v>
+        <v>Veil Silk Neckerchief</v>
       </c>
       <c r="AH86" t="str">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="AI86" t="str">
-        <v>Vachetta Leather</v>
+        <v>Printed Raw Silk</v>
       </c>
       <c r="AJ86" t="str">
-        <v>A slim card holder that adds a smaller-scale object to the grid.</v>
+        <v>A smaller silk accent piece for layering around the neck or bag handle.</v>
       </c>
       <c r="AK86" t="str">
         <v/>
@@ -16323,7 +16323,7 @@
         <v/>
       </c>
       <c r="E87" t="str">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F87" t="str">
         <v/>
@@ -16380,13 +16380,13 @@
         <v/>
       </c>
       <c r="X87" t="str">
-        <v>Utility Detail</v>
+        <v>Metal Form</v>
       </c>
       <c r="Y87" t="str">
         <v/>
       </c>
       <c r="Z87" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAc-xgefZmjRHW4tYawNPs3ljWfgQ66YMBuFgX39XflOo-rQyjbJ2Ju2V0nLkyj2SVuz2BKsp1ucM74P4Gg2Q-TiJKsqrjsQRpxYORvaVExN0KFMkAU9KQFmWEmtNZHK5dm7iBBb1zYMTsluHO4Em5IwIi3lS3JGSUeU_unqmYgh-Fw65tcUaH2Ywxl8ag7h1znu1rGefQrkuDTARLHNwtQdpiGPKWCCp8JpO_yLO4kKGzLmwj8g3VfRzxs02GzkmBt2St6l1zyFYZU</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
       </c>
       <c r="AA87" t="str">
         <v/>
@@ -16401,22 +16401,22 @@
         <v/>
       </c>
       <c r="AE87" t="str">
-        <v>accessories-009</v>
+        <v>accessories-011</v>
       </c>
       <c r="AF87" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG87" t="str">
-        <v>Studio Key Lanyard</v>
+        <v>Hinge Cuff</v>
       </c>
       <c r="AH87" t="str">
-        <v>110</v>
+        <v>265</v>
       </c>
       <c r="AI87" t="str">
-        <v>Bridle Leather</v>
+        <v>Sterling Silver</v>
       </c>
       <c r="AJ87" t="str">
-        <v>A small leather object that rounds out the more functional side of the page.</v>
+        <v>A cuff silhouette that expands the jewelry edit without overpowering it.</v>
       </c>
       <c r="AK87" t="str">
         <v/>
@@ -16508,7 +16508,7 @@
         <v/>
       </c>
       <c r="E88" t="str">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F88" t="str">
         <v/>
@@ -16565,13 +16565,13 @@
         <v/>
       </c>
       <c r="X88" t="str">
-        <v>Silk Accent</v>
+        <v>Compact Bag</v>
       </c>
       <c r="Y88" t="str">
         <v/>
       </c>
       <c r="Z88" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDwib-yVKWuTMsi4heheiLMLuw3Aukcrj4t8F5TLsWcUDULrkliTF_b5hFcyekqcaoBOrRCOob6yU3tV5aJCQChHBAggBedojt1THWZ_F-1GiBclBPJw389BrO0MvSA5xrOo1ssievm9rXO2UiIT0Ix_tHvr6rnGAPSAVNt1DYmLJVg_7vuvdan2zI6d3Z7JsuFwAqcipqjdi0FbCpFwqD4d7bZrq5JeL4i4aGx5NsOkOBZScx3UPHkR_rmJldHJi3Cb4MoiZaIoNsN</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
       </c>
       <c r="AA88" t="str">
         <v/>
@@ -16586,22 +16586,22 @@
         <v/>
       </c>
       <c r="AE88" t="str">
-        <v>accessories-010</v>
+        <v>accessories-012</v>
       </c>
       <c r="AF88" t="str">
         <v>ND Atelier</v>
       </c>
       <c r="AG88" t="str">
-        <v>Veil Silk Neckerchief</v>
+        <v>Atelier Bucket Pouch</v>
       </c>
       <c r="AH88" t="str">
-        <v>175</v>
+        <v>390</v>
       </c>
       <c r="AI88" t="str">
-        <v>Printed Raw Silk</v>
+        <v>Nappa Leather</v>
       </c>
       <c r="AJ88" t="str">
-        <v>A smaller silk accent piece for layering around the neck or bag handle.</v>
+        <v>A compact drawstring bag used to finish the accessories rail with a softer silhouette.</v>
       </c>
       <c r="AK88" t="str">
         <v/>
@@ -16681,7 +16681,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>product</v>
+        <v>footer_link</v>
       </c>
       <c r="B89" t="str">
         <v/>
@@ -16693,22 +16693,22 @@
         <v/>
       </c>
       <c r="E89" t="str">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F89" t="str">
         <v/>
       </c>
       <c r="G89" t="str">
-        <v/>
+        <v>Sustainability</v>
       </c>
       <c r="H89" t="str">
-        <v>/categories/Accessories</v>
+        <v>/products</v>
       </c>
       <c r="I89" t="str">
         <v/>
       </c>
       <c r="J89" t="str">
-        <v>accessories</v>
+        <v/>
       </c>
       <c r="K89" t="str">
         <v/>
@@ -16750,13 +16750,13 @@
         <v/>
       </c>
       <c r="X89" t="str">
-        <v>Metal Form</v>
+        <v/>
       </c>
       <c r="Y89" t="str">
         <v/>
       </c>
       <c r="Z89" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
+        <v/>
       </c>
       <c r="AA89" t="str">
         <v/>
@@ -16771,22 +16771,22 @@
         <v/>
       </c>
       <c r="AE89" t="str">
-        <v>accessories-011</v>
+        <v/>
       </c>
       <c r="AF89" t="str">
-        <v>ND Atelier</v>
+        <v/>
       </c>
       <c r="AG89" t="str">
-        <v>Hinge Cuff</v>
+        <v/>
       </c>
       <c r="AH89" t="str">
-        <v>265</v>
+        <v/>
       </c>
       <c r="AI89" t="str">
-        <v>Sterling Silver</v>
+        <v/>
       </c>
       <c r="AJ89" t="str">
-        <v>A cuff silhouette that expands the jewelry edit without overpowering it.</v>
+        <v/>
       </c>
       <c r="AK89" t="str">
         <v/>
@@ -16866,7 +16866,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>product</v>
+        <v>footer_link</v>
       </c>
       <c r="B90" t="str">
         <v/>
@@ -16878,22 +16878,22 @@
         <v/>
       </c>
       <c r="E90" t="str">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F90" t="str">
         <v/>
       </c>
       <c r="G90" t="str">
-        <v/>
+        <v>Atelier Services</v>
       </c>
       <c r="H90" t="str">
-        <v>/categories/Accessories</v>
+        <v>/products</v>
       </c>
       <c r="I90" t="str">
         <v/>
       </c>
       <c r="J90" t="str">
-        <v>accessories</v>
+        <v/>
       </c>
       <c r="K90" t="str">
         <v/>
@@ -16935,13 +16935,13 @@
         <v/>
       </c>
       <c r="X90" t="str">
-        <v>Compact Bag</v>
+        <v/>
       </c>
       <c r="Y90" t="str">
         <v/>
       </c>
       <c r="Z90" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
+        <v/>
       </c>
       <c r="AA90" t="str">
         <v/>
@@ -16956,22 +16956,22 @@
         <v/>
       </c>
       <c r="AE90" t="str">
-        <v>accessories-012</v>
+        <v/>
       </c>
       <c r="AF90" t="str">
-        <v>ND Atelier</v>
+        <v/>
       </c>
       <c r="AG90" t="str">
-        <v>Atelier Bucket Pouch</v>
+        <v/>
       </c>
       <c r="AH90" t="str">
-        <v>390</v>
+        <v/>
       </c>
       <c r="AI90" t="str">
-        <v>Nappa Leather</v>
+        <v/>
       </c>
       <c r="AJ90" t="str">
-        <v>A compact drawstring bag used to finish the accessories rail with a softer silhouette.</v>
+        <v/>
       </c>
       <c r="AK90" t="str">
         <v/>
@@ -17063,13 +17063,13 @@
         <v/>
       </c>
       <c r="E91" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F91" t="str">
         <v/>
       </c>
       <c r="G91" t="str">
-        <v>Sustainability</v>
+        <v>Privacy</v>
       </c>
       <c r="H91" t="str">
         <v>/products</v>
@@ -17248,13 +17248,13 @@
         <v/>
       </c>
       <c r="E92" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F92" t="str">
         <v/>
       </c>
       <c r="G92" t="str">
-        <v>Atelier Services</v>
+        <v>Terms</v>
       </c>
       <c r="H92" t="str">
         <v>/products</v>
@@ -17421,7 +17421,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>footer_link</v>
+        <v>category_page</v>
       </c>
       <c r="B93" t="str">
         <v/>
@@ -17430,19 +17430,19 @@
         <v/>
       </c>
       <c r="D93" t="str">
-        <v/>
+        <v>Workbook-driven category page aligned to the Men's Atelier screen in Stitch.</v>
       </c>
       <c r="E93" t="str">
-        <v>3</v>
+        <v/>
       </c>
       <c r="F93" t="str">
-        <v/>
+        <v>men-atelier</v>
       </c>
       <c r="G93" t="str">
-        <v>Privacy</v>
+        <v/>
       </c>
       <c r="H93" t="str">
-        <v>/products</v>
+        <v/>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -17478,7 +17478,7 @@
         <v/>
       </c>
       <c r="T93" t="str">
-        <v/>
+        <v>Structure, restraint, and material depth staged with a quieter editorial rhythm.</v>
       </c>
       <c r="U93" t="str">
         <v/>
@@ -17529,55 +17529,55 @@
         <v/>
       </c>
       <c r="AK93" t="str">
-        <v/>
+        <v>Men</v>
       </c>
       <c r="AL93" t="str">
-        <v/>
+        <v>Shop Men|shop-men|Men|men</v>
       </c>
       <c r="AM93" t="str">
-        <v/>
+        <v>The Men's</v>
       </c>
       <c r="AN93" t="str">
-        <v/>
+        <v>Men's Atelier</v>
       </c>
       <c r="AO93" t="str">
-        <v/>
+        <v>An architectural study in silhouette and structure. Crafted for the modern artisan with a steadier, darker editorial tone.</v>
       </c>
       <c r="AP93" t="str">
-        <v/>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuACWMir-mH0L8UXbUXQWypp-pFR6ldBwMeB_P57xJ4h6lF91JgCYYyEJ27pPIbRuST3wzOd8tibscQ-NbIurAXAyGOUWfZstI5mdT9d5_jh6VLXet-x-y-OPWmMV69qNvZALg2WhY1PVY_SFZnR1pxtNpFxR9lsyyLR7XmqRbJ_dhy0WQE2rK_YiUzI2TXstgAkQ537sWLyCCgyHe5Z2QW16TODc2jAY392leqTD0jFdmPyw689W_PhHTFoOURRakfD2ODeVuxVtb-u</v>
       </c>
       <c r="AQ93" t="str">
-        <v/>
+        <v>Close-up of dark wool fabric and tailored structure in the Men's Atelier</v>
       </c>
       <c r="AR93" t="str">
-        <v/>
+        <v>ND Atelier</v>
       </c>
       <c r="AS93" t="str">
-        <v/>
+        <v>Material Study</v>
       </c>
       <c r="AT93" t="str">
-        <v/>
+        <v>The Obsidian Overcoat</v>
       </c>
       <c r="AU93" t="str">
-        <v/>
+        <v>Outerwear anchors the men's edit with denser texture, stronger shoulders, and a cleaner break through the full silhouette.</v>
       </c>
       <c r="AV93" t="str">
-        <v/>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</v>
       </c>
       <c r="AW93" t="str">
-        <v/>
+        <v>Black luxury overcoat silhouette on a dark moody background</v>
       </c>
       <c r="AX93" t="str">
-        <v/>
+        <v>View Outerwear</v>
       </c>
       <c r="AY93" t="str">
-        <v/>
+        <v>/categories/Shop%20Men</v>
       </c>
       <c r="AZ93" t="str">
-        <v/>
+        <v>Showing %count% results</v>
       </c>
       <c r="BA93" t="str">
-        <v/>
+        <v>Sort by: Relevance</v>
       </c>
       <c r="BB93" t="str">
         <v/>
@@ -17606,7 +17606,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>footer_link</v>
+        <v>category_page</v>
       </c>
       <c r="B94" t="str">
         <v/>
@@ -17615,19 +17615,19 @@
         <v/>
       </c>
       <c r="D94" t="str">
-        <v/>
+        <v>Workbook-driven category page aligned to the Women's Atelier screen in Stitch.</v>
       </c>
       <c r="E94" t="str">
-        <v>4</v>
+        <v/>
       </c>
       <c r="F94" t="str">
-        <v/>
+        <v>women-atelier</v>
       </c>
       <c r="G94" t="str">
-        <v>Terms</v>
+        <v/>
       </c>
       <c r="H94" t="str">
-        <v>/products</v>
+        <v/>
       </c>
       <c r="I94" t="str">
         <v/>
@@ -17663,7 +17663,7 @@
         <v/>
       </c>
       <c r="T94" t="str">
-        <v/>
+        <v>Quiet luxury, defined by purpose.</v>
       </c>
       <c r="U94" t="str">
         <v/>
@@ -17714,55 +17714,55 @@
         <v/>
       </c>
       <c r="AK94" t="str">
-        <v/>
+        <v>Women</v>
       </c>
       <c r="AL94" t="str">
-        <v/>
+        <v>Shop Women|shop-women|Women|women</v>
       </c>
       <c r="AM94" t="str">
-        <v/>
+        <v>The Women's</v>
       </c>
       <c r="AN94" t="str">
-        <v/>
+        <v>Women's Atelier</v>
       </c>
       <c r="AO94" t="str">
-        <v/>
+        <v>Quiet luxury, sculptural drape, and natural fibers arranged with more room to breathe and a calmer editorial pace.</v>
       </c>
       <c r="AP94" t="str">
-        <v/>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCCHjHHNBD0bZoSfUrXMIUsusvSJpfmxcJRzVyGEWriuKDCynB8NOcLil0MHJfUCfgjmGv_IMPAfbmEm73hz3s6Y6ycMQrKq1qnMzNHz4QbDczvsSfdf8SaL9vw3qoSEt36Xm52OFG4ej1BLs2XxqsJW_tPT1C2xruIyndF6i4KCKATXFKExblf5UqEURDlAYRnWNDYbLXe8GGoCndX4q2IeRKAuk6Etam3vFkW85HI4vZvrHKCLYN63hA-DGdTKTpY9k-VBO3aY4le</v>
       </c>
       <c r="AQ94" t="str">
-        <v/>
+        <v>Close-up of ethereal cream silk fabric draping in a softly lit atelier</v>
       </c>
       <c r="AR94" t="str">
-        <v/>
+        <v>ND Atelier</v>
       </c>
       <c r="AS94" t="str">
-        <v/>
+        <v>The Craftsmanship</v>
       </c>
       <c r="AT94" t="str">
-        <v/>
+        <v>Soft drape, clear line, grounded warmth.</v>
       </c>
       <c r="AU94" t="str">
-        <v/>
+        <v>The women's story holds its softness without losing structure, balancing fluid dresses with sharper outerwear and richer texture.</v>
       </c>
       <c r="AV94" t="str">
-        <v/>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</v>
       </c>
       <c r="AW94" t="str">
-        <v/>
+        <v>Wide atelier scene with natural light and tactile fabric study</v>
       </c>
       <c r="AX94" t="str">
-        <v/>
+        <v>Read the Story</v>
       </c>
       <c r="AY94" t="str">
-        <v/>
+        <v>/categories/Shop%20Women</v>
       </c>
       <c r="AZ94" t="str">
-        <v/>
+        <v>Showing %count% pieces</v>
       </c>
       <c r="BA94" t="str">
-        <v/>
+        <v>Sort By</v>
       </c>
       <c r="BB94" t="str">
         <v/>
@@ -17800,13 +17800,13 @@
         <v/>
       </c>
       <c r="D95" t="str">
-        <v>Workbook-driven category page aligned to the Men's Atelier screen in Stitch.</v>
+        <v>Workbook-driven category page aligned to the Footwear Atelier screen in Stitch.</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>men-atelier</v>
+        <v>footwear-atelier</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -17848,7 +17848,7 @@
         <v/>
       </c>
       <c r="T95" t="str">
-        <v>Structure, restraint, and material depth staged with a quieter editorial rhythm.</v>
+        <v>"Luxury is not the absence of imperfection, but the presence of character."</v>
       </c>
       <c r="U95" t="str">
         <v/>
@@ -17899,49 +17899,49 @@
         <v/>
       </c>
       <c r="AK95" t="str">
-        <v>Men</v>
+        <v>Footwear</v>
       </c>
       <c r="AL95" t="str">
-        <v>Shop Men|shop-men|Men|men</v>
+        <v>Footwear|footwear</v>
       </c>
       <c r="AM95" t="str">
-        <v>The Men's</v>
+        <v>The Digital Atelier</v>
       </c>
       <c r="AN95" t="str">
-        <v>Men's Atelier</v>
+        <v>Footwear Atelier</v>
       </c>
       <c r="AO95" t="str">
-        <v>An architectural study in silhouette and structure. Crafted for the modern artisan with a steadier, darker editorial tone.</v>
+        <v>Handcrafted performance, sculptural form, and material precision for the modern explorer.</v>
       </c>
       <c r="AP95" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuACWMir-mH0L8UXbUXQWypp-pFR6ldBwMeB_P57xJ4h6lF91JgCYYyEJ27pPIbRuST3wzOd8tibscQ-NbIurAXAyGOUWfZstI5mdT9d5_jh6VLXet-x-y-OPWmMV69qNvZALg2WhY1PVY_SFZnR1pxtNpFxR9lsyyLR7XmqRbJ_dhy0WQE2rK_YiUzI2TXstgAkQ537sWLyCCgyHe5Z2QW16TODc2jAY392leqTD0jFdmPyw689W_PhHTFoOURRakfD2ODeVuxVtb-u</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAFXvDME4hl86EBAExrs0TPuPyrDnhtwEb8MCDCvjzu2OS-kjWnUF7XkqwYs0MGf5WGZS6B5xPKLv0OXCG5ZrDjkm-McNkALLC0DCYp5LC9beGhY0SnzFUMFF998AElRWMoxze_NVDcZ1jJ4qerfPiE1xI5Xjc0Euy-lzfbdQzjbDW9gtsemGrCxPBq4MDAxVn_PdqcdHWaZ05cl7EMLinkvr6U9D8RGxe-UFtVaee5Q6n-Ohev-vr9h8DwExyawlWEZa9kUKDqsxlQ</v>
       </c>
       <c r="AQ95" t="str">
-        <v>Close-up of dark wool fabric and tailored structure in the Men's Atelier</v>
+        <v>Premium leather shoemaking tools and footwear materials in a bright artisan workshop</v>
       </c>
       <c r="AR95" t="str">
-        <v>ND Atelier</v>
+        <v>Master Shoemaker, ND Atelier</v>
       </c>
       <c r="AS95" t="str">
-        <v>Material Study</v>
+        <v>The Heritage Series</v>
       </c>
       <c r="AT95" t="str">
-        <v>The Obsidian Overcoat</v>
+        <v>Heritage craft, modern proportion.</v>
       </c>
       <c r="AU95" t="str">
-        <v>Outerwear anchors the men's edit with denser texture, stronger shoulders, and a cleaner break through the full silhouette.</v>
+        <v>Leather, edge finishing, and hardware carry the footwear story with a more tactile, workshop-led tone throughout the page.</v>
       </c>
       <c r="AV95" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</v>
       </c>
       <c r="AW95" t="str">
-        <v>Black luxury overcoat silhouette on a dark moody background</v>
+        <v>Abstract editorial shot of leather boots and workshop detail</v>
       </c>
       <c r="AX95" t="str">
-        <v>View Outerwear</v>
+        <v>Discover Craft</v>
       </c>
       <c r="AY95" t="str">
-        <v>/categories/Shop%20Men</v>
+        <v>/categories/Footwear</v>
       </c>
       <c r="AZ95" t="str">
         <v>Showing %count% results</v>
@@ -17985,13 +17985,13 @@
         <v/>
       </c>
       <c r="D96" t="str">
-        <v>Workbook-driven category page aligned to the Women's Atelier screen in Stitch.</v>
+        <v>Workbook-driven category page aligned to the Accessories Atelier screen in Stitch.</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>women-atelier</v>
+        <v>accessories-atelier</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -18033,7 +18033,7 @@
         <v/>
       </c>
       <c r="T96" t="str">
-        <v>Quiet luxury, defined by purpose.</v>
+        <v>True luxury is found in the hidden details of the stitch.</v>
       </c>
       <c r="U96" t="str">
         <v/>
@@ -18084,55 +18084,55 @@
         <v/>
       </c>
       <c r="AK96" t="str">
-        <v>Women</v>
+        <v>Accessories</v>
       </c>
       <c r="AL96" t="str">
-        <v>Shop Women|shop-women|Women|women</v>
+        <v>Accessories|accessories</v>
       </c>
       <c r="AM96" t="str">
-        <v>The Women's</v>
+        <v>Accessories</v>
       </c>
       <c r="AN96" t="str">
-        <v>Women's Atelier</v>
+        <v>Accessories Atelier</v>
       </c>
       <c r="AO96" t="str">
-        <v>Quiet luxury, sculptural drape, and natural fibers arranged with more room to breathe and a calmer editorial pace.</v>
+        <v>Objects, bags, and finishing pieces shaped by material integrity and quieter architectural form.</v>
       </c>
       <c r="AP96" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCCHjHHNBD0bZoSfUrXMIUsusvSJpfmxcJRzVyGEWriuKDCynB8NOcLil0MHJfUCfgjmGv_IMPAfbmEm73hz3s6Y6ycMQrKq1qnMzNHz4QbDczvsSfdf8SaL9vw3qoSEt36Xm52OFG4ej1BLs2XxqsJW_tPT1C2xruIyndF6i4KCKATXFKExblf5UqEURDlAYRnWNDYbLXe8GGoCndX4q2IeRKAuk6Etam3vFkW85HI4vZvrHKCLYN63hA-DGdTKTpY9k-VBO3aY4le</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBlb713Ad1ZqSwci4xtZudIi3pLSP2LntjrYOZbjlMC3NLKbFllzQBjpelA2EcNqh24qXtAEpJDAyVB3yIDQIFXvkmKD86_5kVoAVPrMjID1bCAWG7fccKmwcS9kJ41ohvAPtYZJCMl2fOWYpy8JLZLlE7ksjMmFK7UnFdxUeGvbhsRltWVAsAFxPv7hkz1uizaDdvr0s5HWGulhxwsX6bDRakqRxoA2bYrvMeQA0Nta95LkdO9PMTmAYDvvqhCUeQTFYjDd4sXr9q0</v>
       </c>
       <c r="AQ96" t="str">
-        <v>Close-up of ethereal cream silk fabric draping in a softly lit atelier</v>
+        <v>Close-up of vegetable tanned leather and fine stitching tools in warm light</v>
       </c>
       <c r="AR96" t="str">
-        <v>ND Atelier</v>
+        <v>The Master Artisan</v>
       </c>
       <c r="AS96" t="str">
-        <v>The Craftsmanship</v>
+        <v>Material Focus</v>
       </c>
       <c r="AT96" t="str">
-        <v>Soft drape, clear line, grounded warmth.</v>
+        <v>Objects designed to finish the silhouette.</v>
       </c>
       <c r="AU96" t="str">
-        <v>The women's story holds its softness without losing structure, balancing fluid dresses with sharper outerwear and richer texture.</v>
+        <v>From vegetable tanned leather to raw silk, the accessory page keeps the same airy composition while every object stays editable in the workbook.</v>
       </c>
       <c r="AV96" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDwib-yVKWuTMsi4heheiLMLuw3Aukcrj4t8F5TLsWcUDULrkliTF_b5hFcyekqcaoBOrRCOob6yU3tV5aJCQChHBAggBedojt1THWZ_F-1GiBclBPJw389BrO0MvSA5xrOo1ssievm9rXO2UiIT0Ix_tHvr6rnGAPSAVNt1DYmLJVg_7vuvdan2zI6d3Z7JsuFwAqcipqjdi0FbCpFwqD4d7bZrq5JeL4i4aGx5NsOkOBZScx3UPHkR_rmJldHJi3Cb4MoiZaIoNsN</v>
       </c>
       <c r="AW96" t="str">
-        <v>Wide atelier scene with natural light and tactile fabric study</v>
+        <v>Monochromatic scarf and accessory study in a cream-toned set</v>
       </c>
       <c r="AX96" t="str">
-        <v>Read the Story</v>
+        <v>Discover Objects</v>
       </c>
       <c r="AY96" t="str">
-        <v>/categories/Shop%20Women</v>
+        <v>/categories/Accessories</v>
       </c>
       <c r="AZ96" t="str">
-        <v>Showing %count% pieces</v>
+        <v>Showing %count% results</v>
       </c>
       <c r="BA96" t="str">
-        <v>Sort By</v>
+        <v>Sort by: Relevance</v>
       </c>
       <c r="BB96" t="str">
         <v/>
@@ -18161,7 +18161,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>category_page</v>
+        <v>category_filter</v>
       </c>
       <c r="B97" t="str">
         <v/>
@@ -18170,16 +18170,16 @@
         <v/>
       </c>
       <c r="D97" t="str">
-        <v>Workbook-driven category page aligned to the Footwear Atelier screen in Stitch.</v>
+        <v/>
       </c>
       <c r="E97" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F97" t="str">
-        <v>footwear-atelier</v>
+        <v/>
       </c>
       <c r="G97" t="str">
-        <v/>
+        <v>Category</v>
       </c>
       <c r="H97" t="str">
         <v/>
@@ -18218,7 +18218,7 @@
         <v/>
       </c>
       <c r="T97" t="str">
-        <v>"Luxury is not the absence of imperfection, but the presence of character."</v>
+        <v/>
       </c>
       <c r="U97" t="str">
         <v/>
@@ -18269,64 +18269,64 @@
         <v/>
       </c>
       <c r="AK97" t="str">
-        <v>Footwear</v>
+        <v/>
       </c>
       <c r="AL97" t="str">
-        <v>Footwear|footwear</v>
+        <v/>
       </c>
       <c r="AM97" t="str">
-        <v>The Digital Atelier</v>
+        <v/>
       </c>
       <c r="AN97" t="str">
-        <v>Footwear Atelier</v>
+        <v/>
       </c>
       <c r="AO97" t="str">
-        <v>Handcrafted performance, sculptural form, and material precision for the modern explorer.</v>
+        <v/>
       </c>
       <c r="AP97" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAFXvDME4hl86EBAExrs0TPuPyrDnhtwEb8MCDCvjzu2OS-kjWnUF7XkqwYs0MGf5WGZS6B5xPKLv0OXCG5ZrDjkm-McNkALLC0DCYp5LC9beGhY0SnzFUMFF998AElRWMoxze_NVDcZ1jJ4qerfPiE1xI5Xjc0Euy-lzfbdQzjbDW9gtsemGrCxPBq4MDAxVn_PdqcdHWaZ05cl7EMLinkvr6U9D8RGxe-UFtVaee5Q6n-Ohev-vr9h8DwExyawlWEZa9kUKDqsxlQ</v>
+        <v/>
       </c>
       <c r="AQ97" t="str">
-        <v>Premium leather shoemaking tools and footwear materials in a bright artisan workshop</v>
+        <v/>
       </c>
       <c r="AR97" t="str">
-        <v>Master Shoemaker, ND Atelier</v>
+        <v/>
       </c>
       <c r="AS97" t="str">
-        <v>The Heritage Series</v>
+        <v/>
       </c>
       <c r="AT97" t="str">
-        <v>Heritage craft, modern proportion.</v>
+        <v/>
       </c>
       <c r="AU97" t="str">
-        <v>Leather, edge finishing, and hardware carry the footwear story with a more tactile, workshop-led tone throughout the page.</v>
+        <v/>
       </c>
       <c r="AV97" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</v>
+        <v/>
       </c>
       <c r="AW97" t="str">
-        <v>Abstract editorial shot of leather boots and workshop detail</v>
+        <v/>
       </c>
       <c r="AX97" t="str">
-        <v>Discover Craft</v>
+        <v/>
       </c>
       <c r="AY97" t="str">
-        <v>/categories/Footwear</v>
+        <v/>
       </c>
       <c r="AZ97" t="str">
-        <v>Showing %count% results</v>
+        <v/>
       </c>
       <c r="BA97" t="str">
-        <v>Sort by: Relevance</v>
+        <v/>
       </c>
       <c r="BB97" t="str">
-        <v/>
+        <v>men-atelier</v>
       </c>
       <c r="BC97" t="str">
-        <v/>
+        <v>category</v>
       </c>
       <c r="BD97" t="str">
-        <v/>
+        <v>Shirts|Outerwear|Trousers|Knitwear</v>
       </c>
       <c r="BE97" t="str">
         <v/>
@@ -18346,7 +18346,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>category_page</v>
+        <v>category_filter</v>
       </c>
       <c r="B98" t="str">
         <v/>
@@ -18355,16 +18355,16 @@
         <v/>
       </c>
       <c r="D98" t="str">
-        <v>Workbook-driven category page aligned to the Accessories Atelier screen in Stitch.</v>
+        <v/>
       </c>
       <c r="E98" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="F98" t="str">
-        <v>accessories-atelier</v>
+        <v/>
       </c>
       <c r="G98" t="str">
-        <v/>
+        <v>Size</v>
       </c>
       <c r="H98" t="str">
         <v/>
@@ -18403,7 +18403,7 @@
         <v/>
       </c>
       <c r="T98" t="str">
-        <v>True luxury is found in the hidden details of the stitch.</v>
+        <v/>
       </c>
       <c r="U98" t="str">
         <v/>
@@ -18454,64 +18454,64 @@
         <v/>
       </c>
       <c r="AK98" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="AL98" t="str">
-        <v>Accessories|accessories</v>
+        <v/>
       </c>
       <c r="AM98" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="AN98" t="str">
-        <v>Accessories Atelier</v>
+        <v/>
       </c>
       <c r="AO98" t="str">
-        <v>Objects, bags, and finishing pieces shaped by material integrity and quieter architectural form.</v>
+        <v/>
       </c>
       <c r="AP98" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBlb713Ad1ZqSwci4xtZudIi3pLSP2LntjrYOZbjlMC3NLKbFllzQBjpelA2EcNqh24qXtAEpJDAyVB3yIDQIFXvkmKD86_5kVoAVPrMjID1bCAWG7fccKmwcS9kJ41ohvAPtYZJCMl2fOWYpy8JLZLlE7ksjMmFK7UnFdxUeGvbhsRltWVAsAFxPv7hkz1uizaDdvr0s5HWGulhxwsX6bDRakqRxoA2bYrvMeQA0Nta95LkdO9PMTmAYDvvqhCUeQTFYjDd4sXr9q0</v>
+        <v/>
       </c>
       <c r="AQ98" t="str">
-        <v>Close-up of vegetable tanned leather and fine stitching tools in warm light</v>
+        <v/>
       </c>
       <c r="AR98" t="str">
-        <v>The Master Artisan</v>
+        <v/>
       </c>
       <c r="AS98" t="str">
-        <v>Material Focus</v>
+        <v/>
       </c>
       <c r="AT98" t="str">
-        <v>Objects designed to finish the silhouette.</v>
+        <v/>
       </c>
       <c r="AU98" t="str">
-        <v>From vegetable tanned leather to raw silk, the accessory page keeps the same airy composition while every object stays editable in the workbook.</v>
+        <v/>
       </c>
       <c r="AV98" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDwib-yVKWuTMsi4heheiLMLuw3Aukcrj4t8F5TLsWcUDULrkliTF_b5hFcyekqcaoBOrRCOob6yU3tV5aJCQChHBAggBedojt1THWZ_F-1GiBclBPJw389BrO0MvSA5xrOo1ssievm9rXO2UiIT0Ix_tHvr6rnGAPSAVNt1DYmLJVg_7vuvdan2zI6d3Z7JsuFwAqcipqjdi0FbCpFwqD4d7bZrq5JeL4i4aGx5NsOkOBZScx3UPHkR_rmJldHJi3Cb4MoiZaIoNsN</v>
+        <v/>
       </c>
       <c r="AW98" t="str">
-        <v>Monochromatic scarf and accessory study in a cream-toned set</v>
+        <v/>
       </c>
       <c r="AX98" t="str">
-        <v>Discover Objects</v>
+        <v/>
       </c>
       <c r="AY98" t="str">
-        <v>/categories/Accessories</v>
+        <v/>
       </c>
       <c r="AZ98" t="str">
-        <v>Showing %count% results</v>
+        <v/>
       </c>
       <c r="BA98" t="str">
-        <v>Sort by: Relevance</v>
+        <v/>
       </c>
       <c r="BB98" t="str">
-        <v/>
+        <v>men-atelier</v>
       </c>
       <c r="BC98" t="str">
-        <v/>
+        <v>size</v>
       </c>
       <c r="BD98" t="str">
-        <v/>
+        <v>S|M|L|XL</v>
       </c>
       <c r="BE98" t="str">
         <v/>
@@ -18543,13 +18543,13 @@
         <v/>
       </c>
       <c r="E99" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F99" t="str">
         <v/>
       </c>
       <c r="G99" t="str">
-        <v>Category</v>
+        <v>Price Range</v>
       </c>
       <c r="H99" t="str">
         <v/>
@@ -18693,10 +18693,10 @@
         <v>men-atelier</v>
       </c>
       <c r="BC99" t="str">
-        <v>category</v>
+        <v>price</v>
       </c>
       <c r="BD99" t="str">
-        <v>Shirts|Outerwear|Trousers|Knitwear</v>
+        <v>$150-$500|$500-$1000|$1000+</v>
       </c>
       <c r="BE99" t="str">
         <v/>
@@ -18728,13 +18728,13 @@
         <v/>
       </c>
       <c r="E100" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F100" t="str">
         <v/>
       </c>
       <c r="G100" t="str">
-        <v>Size</v>
+        <v>Categories</v>
       </c>
       <c r="H100" t="str">
         <v/>
@@ -18875,13 +18875,13 @@
         <v/>
       </c>
       <c r="BB100" t="str">
-        <v>men-atelier</v>
+        <v>women-atelier</v>
       </c>
       <c r="BC100" t="str">
-        <v>size</v>
+        <v>category</v>
       </c>
       <c r="BD100" t="str">
-        <v>S|M|L|XL</v>
+        <v>Dresses|Tops|Bottoms|Outerwear</v>
       </c>
       <c r="BE100" t="str">
         <v/>
@@ -18913,13 +18913,13 @@
         <v/>
       </c>
       <c r="E101" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F101" t="str">
         <v/>
       </c>
       <c r="G101" t="str">
-        <v>Price Range</v>
+        <v>Size</v>
       </c>
       <c r="H101" t="str">
         <v/>
@@ -19060,13 +19060,13 @@
         <v/>
       </c>
       <c r="BB101" t="str">
-        <v>men-atelier</v>
+        <v>women-atelier</v>
       </c>
       <c r="BC101" t="str">
-        <v>price</v>
+        <v>size</v>
       </c>
       <c r="BD101" t="str">
-        <v>$150-$500|$500-$1000|$1000+</v>
+        <v>XS|S|M|L|XL</v>
       </c>
       <c r="BE101" t="str">
         <v/>
@@ -19098,13 +19098,13 @@
         <v/>
       </c>
       <c r="E102" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F102" t="str">
         <v/>
       </c>
       <c r="G102" t="str">
-        <v>Categories</v>
+        <v>Palette</v>
       </c>
       <c r="H102" t="str">
         <v/>
@@ -19248,10 +19248,10 @@
         <v>women-atelier</v>
       </c>
       <c r="BC102" t="str">
-        <v>category</v>
+        <v>palette</v>
       </c>
       <c r="BD102" t="str">
-        <v>Dresses|Tops|Bottoms|Outerwear</v>
+        <v>Cream|Forest|Stone|Charcoal</v>
       </c>
       <c r="BE102" t="str">
         <v/>
@@ -19283,13 +19283,13 @@
         <v/>
       </c>
       <c r="E103" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" t="str">
         <v/>
       </c>
       <c r="G103" t="str">
-        <v>Size</v>
+        <v>Type</v>
       </c>
       <c r="H103" t="str">
         <v/>
@@ -19430,13 +19430,13 @@
         <v/>
       </c>
       <c r="BB103" t="str">
-        <v>women-atelier</v>
+        <v>footwear-atelier</v>
       </c>
       <c r="BC103" t="str">
-        <v>size</v>
+        <v>type</v>
       </c>
       <c r="BD103" t="str">
-        <v>XS|S|M|L|XL</v>
+        <v>Boots|Sneakers|Loafers|Sandals</v>
       </c>
       <c r="BE103" t="str">
         <v/>
@@ -19468,13 +19468,13 @@
         <v/>
       </c>
       <c r="E104" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F104" t="str">
         <v/>
       </c>
       <c r="G104" t="str">
-        <v>Palette</v>
+        <v>Size</v>
       </c>
       <c r="H104" t="str">
         <v/>
@@ -19615,13 +19615,13 @@
         <v/>
       </c>
       <c r="BB104" t="str">
-        <v>women-atelier</v>
+        <v>footwear-atelier</v>
       </c>
       <c r="BC104" t="str">
-        <v>palette</v>
+        <v>size</v>
       </c>
       <c r="BD104" t="str">
-        <v>Cream|Forest|Stone|Charcoal</v>
+        <v>39|40|41|42|43</v>
       </c>
       <c r="BE104" t="str">
         <v/>
@@ -19653,13 +19653,13 @@
         <v/>
       </c>
       <c r="E105" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F105" t="str">
         <v/>
       </c>
       <c r="G105" t="str">
-        <v>Type</v>
+        <v>Material</v>
       </c>
       <c r="H105" t="str">
         <v/>
@@ -19803,10 +19803,10 @@
         <v>footwear-atelier</v>
       </c>
       <c r="BC105" t="str">
-        <v>type</v>
+        <v>material</v>
       </c>
       <c r="BD105" t="str">
-        <v>Boots|Sneakers|Loafers|Sandals</v>
+        <v>Calfskin|Suede|Grain Leather|Bridle Leather</v>
       </c>
       <c r="BE105" t="str">
         <v/>
@@ -19838,13 +19838,13 @@
         <v/>
       </c>
       <c r="E106" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F106" t="str">
         <v/>
       </c>
       <c r="G106" t="str">
-        <v>Size</v>
+        <v>Category</v>
       </c>
       <c r="H106" t="str">
         <v/>
@@ -19985,13 +19985,13 @@
         <v/>
       </c>
       <c r="BB106" t="str">
-        <v>footwear-atelier</v>
+        <v>accessories-atelier</v>
       </c>
       <c r="BC106" t="str">
-        <v>size</v>
+        <v>category</v>
       </c>
       <c r="BD106" t="str">
-        <v>39|40|41|42|43</v>
+        <v>All Objects|Bags|Belts|Jewelry|Scarves</v>
       </c>
       <c r="BE106" t="str">
         <v/>
@@ -20023,7 +20023,7 @@
         <v/>
       </c>
       <c r="E107" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F107" t="str">
         <v/>
@@ -20170,13 +20170,13 @@
         <v/>
       </c>
       <c r="BB107" t="str">
-        <v>footwear-atelier</v>
+        <v>accessories-atelier</v>
       </c>
       <c r="BC107" t="str">
         <v>material</v>
       </c>
       <c r="BD107" t="str">
-        <v>Calfskin|Suede|Grain Leather|Bridle Leather</v>
+        <v>Raw Silk|Vachetta|Sterling Silver|Cashmere|Nappa Leather</v>
       </c>
       <c r="BE107" t="str">
         <v/>
@@ -20196,7 +20196,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>category_filter</v>
+        <v>category_page_product</v>
       </c>
       <c r="B108" t="str">
         <v/>
@@ -20214,10 +20214,10 @@
         <v/>
       </c>
       <c r="G108" t="str">
-        <v>Category</v>
+        <v/>
       </c>
       <c r="H108" t="str">
-        <v/>
+        <v>/categories/Shop%20Men</v>
       </c>
       <c r="I108" t="str">
         <v/>
@@ -20271,7 +20271,7 @@
         <v/>
       </c>
       <c r="Z108" t="str">
-        <v/>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</v>
       </c>
       <c r="AA108" t="str">
         <v/>
@@ -20286,16 +20286,16 @@
         <v/>
       </c>
       <c r="AE108" t="str">
-        <v/>
+        <v>men-001</v>
       </c>
       <c r="AF108" t="str">
         <v/>
       </c>
       <c r="AG108" t="str">
-        <v/>
+        <v>Sculpted Linen Shirt</v>
       </c>
       <c r="AH108" t="str">
-        <v/>
+        <v>420</v>
       </c>
       <c r="AI108" t="str">
         <v/>
@@ -20355,33 +20355,33 @@
         <v/>
       </c>
       <c r="BB108" t="str">
-        <v>accessories-atelier</v>
+        <v>men-atelier</v>
       </c>
       <c r="BC108" t="str">
-        <v>category</v>
+        <v/>
       </c>
       <c r="BD108" t="str">
-        <v>All Objects|Bags|Belts|Jewelry|Scarves</v>
+        <v/>
       </c>
       <c r="BE108" t="str">
         <v/>
       </c>
       <c r="BF108" t="str">
-        <v/>
+        <v>New Arrival</v>
       </c>
       <c r="BG108" t="str">
-        <v/>
+        <v>Italian Linen Blend</v>
       </c>
       <c r="BH108" t="str">
-        <v/>
+        <v>Cream tailored linen shirt in morning light</v>
       </c>
       <c r="BI108" t="str">
-        <v/>
+        <v>category:shirts|size:M|price:$150-$500</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>category_filter</v>
+        <v>category_page_product</v>
       </c>
       <c r="B109" t="str">
         <v/>
@@ -20399,10 +20399,10 @@
         <v/>
       </c>
       <c r="G109" t="str">
-        <v>Material</v>
+        <v/>
       </c>
       <c r="H109" t="str">
-        <v/>
+        <v>/categories/Shop%20Men</v>
       </c>
       <c r="I109" t="str">
         <v/>
@@ -20456,7 +20456,7 @@
         <v/>
       </c>
       <c r="Z109" t="str">
-        <v/>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</v>
       </c>
       <c r="AA109" t="str">
         <v/>
@@ -20471,16 +20471,16 @@
         <v/>
       </c>
       <c r="AE109" t="str">
-        <v/>
+        <v>men-002</v>
       </c>
       <c r="AF109" t="str">
         <v/>
       </c>
       <c r="AG109" t="str">
-        <v/>
+        <v>Structured Atelier Jacket</v>
       </c>
       <c r="AH109" t="str">
-        <v/>
+        <v>1250</v>
       </c>
       <c r="AI109" t="str">
         <v/>
@@ -20540,28 +20540,28 @@
         <v/>
       </c>
       <c r="BB109" t="str">
-        <v>accessories-atelier</v>
+        <v>men-atelier</v>
       </c>
       <c r="BC109" t="str">
-        <v>material</v>
+        <v/>
       </c>
       <c r="BD109" t="str">
-        <v>Raw Silk|Vachetta|Sterling Silver|Cashmere|Nappa Leather</v>
+        <v/>
       </c>
       <c r="BE109" t="str">
         <v/>
       </c>
       <c r="BF109" t="str">
-        <v/>
+        <v>Limited Edition</v>
       </c>
       <c r="BG109" t="str">
-        <v/>
+        <v>100% Merino Wool</v>
       </c>
       <c r="BH109" t="str">
-        <v/>
+        <v>Structured dark wool jacket with precise lapel detail</v>
       </c>
       <c r="BI109" t="str">
-        <v/>
+        <v>category:outerwear|size:L|price:$1000+</v>
       </c>
     </row>
     <row r="110">
@@ -20578,7 +20578,7 @@
         <v/>
       </c>
       <c r="E110" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F110" t="str">
         <v/>
@@ -20641,7 +20641,7 @@
         <v/>
       </c>
       <c r="Z110" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBXRSWOWcHtCNyaMDYLCJzvRD_aYObkVBkIHPoz_HZOOuihWxPKo82MAX7anUmfBqHwOgx_6YthGokOn-aqEtAkMya3di9RNTlqqA2-zqT6x85Yh0CGWy5_gOTjOOMYxnRJ7B8A9ihZaMR-PzIAILb7T5rSMUCiZ-3CZRTX_u3XxJpOlXlYjWEZj4aFLaV_mamuWkKjkhTxSRpw7LyICx9lPITcKUuGOxJ0NkpKweDI4rMjqFkSSGZJssErigmmpbKq5Z6kLPVUehXg</v>
       </c>
       <c r="AA110" t="str">
         <v/>
@@ -20656,16 +20656,16 @@
         <v/>
       </c>
       <c r="AE110" t="str">
-        <v>men-001</v>
+        <v>men-003</v>
       </c>
       <c r="AF110" t="str">
         <v/>
       </c>
       <c r="AG110" t="str">
-        <v>Sculpted Linen Shirt</v>
+        <v>Modern Drape Trousers</v>
       </c>
       <c r="AH110" t="str">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="AI110" t="str">
         <v/>
@@ -20737,16 +20737,16 @@
         <v/>
       </c>
       <c r="BF110" t="str">
-        <v>New Arrival</v>
+        <v>Tailoring</v>
       </c>
       <c r="BG110" t="str">
-        <v>Italian Linen Blend</v>
+        <v>Fine Serge Cotton</v>
       </c>
       <c r="BH110" t="str">
-        <v>Cream tailored linen shirt in morning light</v>
+        <v>Folded olive trousers with sharp crease</v>
       </c>
       <c r="BI110" t="str">
-        <v>category:shirts|size:M|price:$150-$500</v>
+        <v>category:trousers|size:M|price:$150-$500</v>
       </c>
     </row>
     <row r="111">
@@ -20763,7 +20763,7 @@
         <v/>
       </c>
       <c r="E111" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F111" t="str">
         <v/>
@@ -20826,7 +20826,7 @@
         <v/>
       </c>
       <c r="Z111" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDBowt2AR0QGkZ_teHLK0qG2iUl8fGSUuNTrZHreU_s95xtmrbnCTB8LYOShnHaraaNDqoUnziBnVe2Rh6OAlJpU9ZSpF84L0-k23aokXc6aJdWswRdyGowycFswnENPgO9tfnUyUaMa2VjW8lGJYkmhPbnJhSE0zC0BdoSTdae8pmGnQwaAXzVlJJRhWYysiO1yf2n_lREj8nVxarkGub1OLnfLI4QrhAiAGV-AZTWnZg1MCqdpNi1pBSjb6RIPFAzXw0h_iTQCqrp</v>
       </c>
       <c r="AA111" t="str">
         <v/>
@@ -20841,16 +20841,16 @@
         <v/>
       </c>
       <c r="AE111" t="str">
-        <v>men-002</v>
+        <v>men-004</v>
       </c>
       <c r="AF111" t="str">
         <v/>
       </c>
       <c r="AG111" t="str">
-        <v>Structured Atelier Jacket</v>
+        <v>Atelier Knit Polo</v>
       </c>
       <c r="AH111" t="str">
-        <v>1250</v>
+        <v>290</v>
       </c>
       <c r="AI111" t="str">
         <v/>
@@ -20922,16 +20922,16 @@
         <v/>
       </c>
       <c r="BF111" t="str">
-        <v>Limited Edition</v>
+        <v>Knitwear</v>
       </c>
       <c r="BG111" t="str">
-        <v>100% Merino Wool</v>
+        <v>Sea Island Cotton</v>
       </c>
       <c r="BH111" t="str">
-        <v>Structured dark wool jacket with precise lapel detail</v>
+        <v>Dark green knit polo with horn buttons</v>
       </c>
       <c r="BI111" t="str">
-        <v>category:outerwear|size:L|price:$1000+</v>
+        <v>category:knitwear|size:M|price:$150-$500</v>
       </c>
     </row>
     <row r="112">
@@ -20948,7 +20948,7 @@
         <v/>
       </c>
       <c r="E112" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F112" t="str">
         <v/>
@@ -21011,7 +21011,7 @@
         <v/>
       </c>
       <c r="Z112" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBXRSWOWcHtCNyaMDYLCJzvRD_aYObkVBkIHPoz_HZOOuihWxPKo82MAX7anUmfBqHwOgx_6YthGokOn-aqEtAkMya3di9RNTlqqA2-zqT6x85Yh0CGWy5_gOTjOOMYxnRJ7B8A9ihZaMR-PzIAILb7T5rSMUCiZ-3CZRTX_u3XxJpOlXlYjWEZj4aFLaV_mamuWkKjkhTxSRpw7LyICx9lPITcKUuGOxJ0NkpKweDI4rMjqFkSSGZJssErigmmpbKq5Z6kLPVUehXg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</v>
       </c>
       <c r="AA112" t="str">
         <v/>
@@ -21026,16 +21026,16 @@
         <v/>
       </c>
       <c r="AE112" t="str">
-        <v>men-003</v>
+        <v>men-005</v>
       </c>
       <c r="AF112" t="str">
         <v/>
       </c>
       <c r="AG112" t="str">
-        <v>Modern Drape Trousers</v>
+        <v>The Obsidian Overcoat</v>
       </c>
       <c r="AH112" t="str">
-        <v>380</v>
+        <v>1890</v>
       </c>
       <c r="AI112" t="str">
         <v/>
@@ -21107,16 +21107,16 @@
         <v/>
       </c>
       <c r="BF112" t="str">
-        <v>Tailoring</v>
+        <v>Editorial Pick</v>
       </c>
       <c r="BG112" t="str">
-        <v>Fine Serge Cotton</v>
+        <v>Cashmere Blend</v>
       </c>
       <c r="BH112" t="str">
-        <v>Folded olive trousers with sharp crease</v>
+        <v>Black overcoat silhouette on a dark background</v>
       </c>
       <c r="BI112" t="str">
-        <v>category:trousers|size:M|price:$150-$500</v>
+        <v>category:outerwear|size:L|price:$1000+</v>
       </c>
     </row>
     <row r="113">
@@ -21133,7 +21133,7 @@
         <v/>
       </c>
       <c r="E113" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F113" t="str">
         <v/>
@@ -21196,7 +21196,7 @@
         <v/>
       </c>
       <c r="Z113" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDBowt2AR0QGkZ_teHLK0qG2iUl8fGSUuNTrZHreU_s95xtmrbnCTB8LYOShnHaraaNDqoUnziBnVe2Rh6OAlJpU9ZSpF84L0-k23aokXc6aJdWswRdyGowycFswnENPgO9tfnUyUaMa2VjW8lGJYkmhPbnJhSE0zC0BdoSTdae8pmGnQwaAXzVlJJRhWYysiO1yf2n_lREj8nVxarkGub1OLnfLI4QrhAiAGV-AZTWnZg1MCqdpNi1pBSjb6RIPFAzXw0h_iTQCqrp</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</v>
       </c>
       <c r="AA113" t="str">
         <v/>
@@ -21211,16 +21211,16 @@
         <v/>
       </c>
       <c r="AE113" t="str">
-        <v>men-004</v>
+        <v>men-006</v>
       </c>
       <c r="AF113" t="str">
         <v/>
       </c>
       <c r="AG113" t="str">
-        <v>Atelier Knit Polo</v>
+        <v>Relaxed Cargo Trouser</v>
       </c>
       <c r="AH113" t="str">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="AI113" t="str">
         <v/>
@@ -21292,16 +21292,16 @@
         <v/>
       </c>
       <c r="BF113" t="str">
-        <v>Knitwear</v>
+        <v>Studio Essential</v>
       </c>
       <c r="BG113" t="str">
-        <v>Sea Island Cotton</v>
+        <v>Brushed Twill</v>
       </c>
       <c r="BH113" t="str">
-        <v>Dark green knit polo with horn buttons</v>
+        <v>Khaki trouser texture and pocket detail</v>
       </c>
       <c r="BI113" t="str">
-        <v>category:knitwear|size:M|price:$150-$500</v>
+        <v>category:trousers|size:S|price:$150-$500</v>
       </c>
     </row>
     <row r="114">
@@ -21318,7 +21318,7 @@
         <v/>
       </c>
       <c r="E114" t="str">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F114" t="str">
         <v/>
@@ -21381,7 +21381,7 @@
         <v/>
       </c>
       <c r="Z114" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</v>
       </c>
       <c r="AA114" t="str">
         <v/>
@@ -21396,16 +21396,16 @@
         <v/>
       </c>
       <c r="AE114" t="str">
-        <v>men-005</v>
+        <v>men-007</v>
       </c>
       <c r="AF114" t="str">
         <v/>
       </c>
       <c r="AG114" t="str">
-        <v>The Obsidian Overcoat</v>
+        <v>Stonewashed Utility Overshirt</v>
       </c>
       <c r="AH114" t="str">
-        <v>1890</v>
+        <v>360</v>
       </c>
       <c r="AI114" t="str">
         <v/>
@@ -21477,16 +21477,16 @@
         <v/>
       </c>
       <c r="BF114" t="str">
-        <v>Editorial Pick</v>
+        <v>Workshop Layer</v>
       </c>
       <c r="BG114" t="str">
-        <v>Cashmere Blend</v>
+        <v>Washed Cotton Drill</v>
       </c>
       <c r="BH114" t="str">
-        <v>Black overcoat silhouette on a dark background</v>
+        <v>Stonewashed overshirt on a wooden hanger</v>
       </c>
       <c r="BI114" t="str">
-        <v>category:outerwear|size:L|price:$1000+</v>
+        <v>category:shirts|size:M|price:$150-$500</v>
       </c>
     </row>
     <row r="115">
@@ -21503,7 +21503,7 @@
         <v/>
       </c>
       <c r="E115" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F115" t="str">
         <v/>
@@ -21566,7 +21566,7 @@
         <v/>
       </c>
       <c r="Z115" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBXRSWOWcHtCNyaMDYLCJzvRD_aYObkVBkIHPoz_HZOOuihWxPKo82MAX7anUmfBqHwOgx_6YthGokOn-aqEtAkMya3di9RNTlqqA2-zqT6x85Yh0CGWy5_gOTjOOMYxnRJ7B8A9ihZaMR-PzIAILb7T5rSMUCiZ-3CZRTX_u3XxJpOlXlYjWEZj4aFLaV_mamuWkKjkhTxSRpw7LyICx9lPITcKUuGOxJ0NkpKweDI4rMjqFkSSGZJssErigmmpbKq5Z6kLPVUehXg</v>
       </c>
       <c r="AA115" t="str">
         <v/>
@@ -21581,16 +21581,16 @@
         <v/>
       </c>
       <c r="AE115" t="str">
-        <v>men-006</v>
+        <v>men-008</v>
       </c>
       <c r="AF115" t="str">
         <v/>
       </c>
       <c r="AG115" t="str">
-        <v>Relaxed Cargo Trouser</v>
+        <v>Meridian Wool Cardigan</v>
       </c>
       <c r="AH115" t="str">
-        <v>340</v>
+        <v>410</v>
       </c>
       <c r="AI115" t="str">
         <v/>
@@ -21662,16 +21662,16 @@
         <v/>
       </c>
       <c r="BF115" t="str">
-        <v>Studio Essential</v>
+        <v>Soft Structure</v>
       </c>
       <c r="BG115" t="str">
-        <v>Brushed Twill</v>
+        <v>Merino Wool</v>
       </c>
       <c r="BH115" t="str">
-        <v>Khaki trouser texture and pocket detail</v>
+        <v>Merino cardigan folded on a leather bench</v>
       </c>
       <c r="BI115" t="str">
-        <v>category:trousers|size:S|price:$150-$500</v>
+        <v>category:knitwear|size:M|price:$150-$500</v>
       </c>
     </row>
     <row r="116">
@@ -21688,7 +21688,7 @@
         <v/>
       </c>
       <c r="E116" t="str">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F116" t="str">
         <v/>
@@ -21751,7 +21751,7 @@
         <v/>
       </c>
       <c r="Z116" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDBowt2AR0QGkZ_teHLK0qG2iUl8fGSUuNTrZHreU_s95xtmrbnCTB8LYOShnHaraaNDqoUnziBnVe2Rh6OAlJpU9ZSpF84L0-k23aokXc6aJdWswRdyGowycFswnENPgO9tfnUyUaMa2VjW8lGJYkmhPbnJhSE0zC0BdoSTdae8pmGnQwaAXzVlJJRhWYysiO1yf2n_lREj8nVxarkGub1OLnfLI4QrhAiAGV-AZTWnZg1MCqdpNi1pBSjb6RIPFAzXw0h_iTQCqrp</v>
       </c>
       <c r="AA116" t="str">
         <v/>
@@ -21766,16 +21766,16 @@
         <v/>
       </c>
       <c r="AE116" t="str">
-        <v>men-007</v>
+        <v>men-009</v>
       </c>
       <c r="AF116" t="str">
         <v/>
       </c>
       <c r="AG116" t="str">
-        <v>Stonewashed Utility Overshirt</v>
+        <v>Foundry Pleat Short</v>
       </c>
       <c r="AH116" t="str">
-        <v>360</v>
+        <v>250</v>
       </c>
       <c r="AI116" t="str">
         <v/>
@@ -21847,16 +21847,16 @@
         <v/>
       </c>
       <c r="BF116" t="str">
-        <v>Workshop Layer</v>
+        <v>Warm Weather</v>
       </c>
       <c r="BG116" t="str">
-        <v>Washed Cotton Drill</v>
+        <v>Tumbled Cotton Poplin</v>
       </c>
       <c r="BH116" t="str">
-        <v>Stonewashed overshirt on a wooden hanger</v>
+        <v>Pleated cotton short with a clean hem</v>
       </c>
       <c r="BI116" t="str">
-        <v>category:shirts|size:M|price:$150-$500</v>
+        <v>category:trousers|size:S|price:$150-$500</v>
       </c>
     </row>
     <row r="117">
@@ -21873,7 +21873,7 @@
         <v/>
       </c>
       <c r="E117" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F117" t="str">
         <v/>
@@ -21936,7 +21936,7 @@
         <v/>
       </c>
       <c r="Z117" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBXRSWOWcHtCNyaMDYLCJzvRD_aYObkVBkIHPoz_HZOOuihWxPKo82MAX7anUmfBqHwOgx_6YthGokOn-aqEtAkMya3di9RNTlqqA2-zqT6x85Yh0CGWy5_gOTjOOMYxnRJ7B8A9ihZaMR-PzIAILb7T5rSMUCiZ-3CZRTX_u3XxJpOlXlYjWEZj4aFLaV_mamuWkKjkhTxSRpw7LyICx9lPITcKUuGOxJ0NkpKweDI4rMjqFkSSGZJssErigmmpbKq5Z6kLPVUehXg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</v>
       </c>
       <c r="AA117" t="str">
         <v/>
@@ -21951,16 +21951,16 @@
         <v/>
       </c>
       <c r="AE117" t="str">
-        <v>men-008</v>
+        <v>men-010</v>
       </c>
       <c r="AF117" t="str">
         <v/>
       </c>
       <c r="AG117" t="str">
-        <v>Meridian Wool Cardigan</v>
+        <v>Tailored Poplin Bandshirt</v>
       </c>
       <c r="AH117" t="str">
-        <v>410</v>
+        <v>280</v>
       </c>
       <c r="AI117" t="str">
         <v/>
@@ -22032,16 +22032,16 @@
         <v/>
       </c>
       <c r="BF117" t="str">
-        <v>Soft Structure</v>
+        <v>Shirting</v>
       </c>
       <c r="BG117" t="str">
-        <v>Merino Wool</v>
+        <v>Compact Cotton Poplin</v>
       </c>
       <c r="BH117" t="str">
-        <v>Merino cardigan folded on a leather bench</v>
+        <v>Band-collar shirt hanging in soft daylight</v>
       </c>
       <c r="BI117" t="str">
-        <v>category:knitwear|size:M|price:$150-$500</v>
+        <v>category:shirts|size:M|price:$150-$500</v>
       </c>
     </row>
     <row r="118">
@@ -22058,7 +22058,7 @@
         <v/>
       </c>
       <c r="E118" t="str">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F118" t="str">
         <v/>
@@ -22121,7 +22121,7 @@
         <v/>
       </c>
       <c r="Z118" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDBowt2AR0QGkZ_teHLK0qG2iUl8fGSUuNTrZHreU_s95xtmrbnCTB8LYOShnHaraaNDqoUnziBnVe2Rh6OAlJpU9ZSpF84L0-k23aokXc6aJdWswRdyGowycFswnENPgO9tfnUyUaMa2VjW8lGJYkmhPbnJhSE0zC0BdoSTdae8pmGnQwaAXzVlJJRhWYysiO1yf2n_lREj8nVxarkGub1OLnfLI4QrhAiAGV-AZTWnZg1MCqdpNi1pBSjb6RIPFAzXw0h_iTQCqrp</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</v>
       </c>
       <c r="AA118" t="str">
         <v/>
@@ -22136,16 +22136,16 @@
         <v/>
       </c>
       <c r="AE118" t="str">
-        <v>men-009</v>
+        <v>men-011</v>
       </c>
       <c r="AF118" t="str">
         <v/>
       </c>
       <c r="AG118" t="str">
-        <v>Foundry Pleat Short</v>
+        <v>Alpine Field Parka</v>
       </c>
       <c r="AH118" t="str">
-        <v>250</v>
+        <v>980</v>
       </c>
       <c r="AI118" t="str">
         <v/>
@@ -22217,16 +22217,16 @@
         <v/>
       </c>
       <c r="BF118" t="str">
-        <v>Warm Weather</v>
+        <v>Outerwear</v>
       </c>
       <c r="BG118" t="str">
-        <v>Tumbled Cotton Poplin</v>
+        <v>Technical Cotton Shell</v>
       </c>
       <c r="BH118" t="str">
-        <v>Pleated cotton short with a clean hem</v>
+        <v>Moss field parka styled against stone walls</v>
       </c>
       <c r="BI118" t="str">
-        <v>category:trousers|size:S|price:$150-$500</v>
+        <v>category:outerwear|size:L|price:$500-$1000</v>
       </c>
     </row>
     <row r="119">
@@ -22243,7 +22243,7 @@
         <v/>
       </c>
       <c r="E119" t="str">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F119" t="str">
         <v/>
@@ -22306,7 +22306,7 @@
         <v/>
       </c>
       <c r="Z119" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</v>
       </c>
       <c r="AA119" t="str">
         <v/>
@@ -22321,16 +22321,16 @@
         <v/>
       </c>
       <c r="AE119" t="str">
-        <v>men-010</v>
+        <v>men-012</v>
       </c>
       <c r="AF119" t="str">
         <v/>
       </c>
       <c r="AG119" t="str">
-        <v>Tailored Poplin Bandshirt</v>
+        <v>Slate Double Pleat Trouser</v>
       </c>
       <c r="AH119" t="str">
-        <v>280</v>
+        <v>390</v>
       </c>
       <c r="AI119" t="str">
         <v/>
@@ -22402,16 +22402,16 @@
         <v/>
       </c>
       <c r="BF119" t="str">
-        <v>Shirting</v>
+        <v>Tailoring</v>
       </c>
       <c r="BG119" t="str">
-        <v>Compact Cotton Poplin</v>
+        <v>Worsted Wool Blend</v>
       </c>
       <c r="BH119" t="str">
-        <v>Band-collar shirt hanging in soft daylight</v>
+        <v>Slate trouser with double pleat and pressed finish</v>
       </c>
       <c r="BI119" t="str">
-        <v>category:shirts|size:M|price:$150-$500</v>
+        <v>category:trousers|size:M|price:$150-$500</v>
       </c>
     </row>
     <row r="120">
@@ -22428,7 +22428,7 @@
         <v/>
       </c>
       <c r="E120" t="str">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F120" t="str">
         <v/>
@@ -22437,7 +22437,7 @@
         <v/>
       </c>
       <c r="H120" t="str">
-        <v>/categories/Shop%20Men</v>
+        <v>/products/550e8400-e29b-41d4-a716-446655440001</v>
       </c>
       <c r="I120" t="str">
         <v/>
@@ -22491,7 +22491,7 @@
         <v/>
       </c>
       <c r="Z120" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</v>
+        <v>https://example.com/images/sm002-s.jpg</v>
       </c>
       <c r="AA120" t="str">
         <v/>
@@ -22506,16 +22506,16 @@
         <v/>
       </c>
       <c r="AE120" t="str">
-        <v>men-011</v>
+        <v>550e8400-e29b-41d4-a716-446655440001</v>
       </c>
       <c r="AF120" t="str">
         <v/>
       </c>
       <c r="AG120" t="str">
-        <v>Alpine Field Parka</v>
+        <v>Cotton Tee</v>
       </c>
       <c r="AH120" t="str">
-        <v>980</v>
+        <v>49.99</v>
       </c>
       <c r="AI120" t="str">
         <v/>
@@ -22587,16 +22587,16 @@
         <v/>
       </c>
       <c r="BF120" t="str">
-        <v>Outerwear</v>
+        <v>Men</v>
       </c>
       <c r="BG120" t="str">
-        <v>Technical Cotton Shell</v>
+        <v>S / Navy</v>
       </c>
       <c r="BH120" t="str">
-        <v>Moss field parka styled against stone walls</v>
+        <v>Cotton Tee</v>
       </c>
       <c r="BI120" t="str">
-        <v>category:outerwear|size:L|price:$500-$1000</v>
+        <v>category:Men|size:S|color:Navy|price:$0-$150</v>
       </c>
     </row>
     <row r="121">
@@ -22613,7 +22613,7 @@
         <v/>
       </c>
       <c r="E121" t="str">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F121" t="str">
         <v/>
@@ -22622,7 +22622,7 @@
         <v/>
       </c>
       <c r="H121" t="str">
-        <v>/categories/Shop%20Men</v>
+        <v>/products/550e8400-e29b-41d4-a716-446655440000</v>
       </c>
       <c r="I121" t="str">
         <v/>
@@ -22676,7 +22676,7 @@
         <v/>
       </c>
       <c r="Z121" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</v>
+        <v>https://example.com/images/sm001-m.jpg</v>
       </c>
       <c r="AA121" t="str">
         <v/>
@@ -22691,16 +22691,16 @@
         <v/>
       </c>
       <c r="AE121" t="str">
-        <v>men-012</v>
+        <v>550e8400-e29b-41d4-a716-446655440000</v>
       </c>
       <c r="AF121" t="str">
         <v/>
       </c>
       <c r="AG121" t="str">
-        <v>Slate Double Pleat Trouser</v>
+        <v>Linen Shirt</v>
       </c>
       <c r="AH121" t="str">
-        <v>390</v>
+        <v>129.99</v>
       </c>
       <c r="AI121" t="str">
         <v/>
@@ -22772,16 +22772,16 @@
         <v/>
       </c>
       <c r="BF121" t="str">
-        <v>Tailoring</v>
+        <v>Men</v>
       </c>
       <c r="BG121" t="str">
-        <v>Worsted Wool Blend</v>
+        <v>M / White</v>
       </c>
       <c r="BH121" t="str">
-        <v>Slate trouser with double pleat and pressed finish</v>
+        <v>Linen Shirt</v>
       </c>
       <c r="BI121" t="str">
-        <v>category:trousers|size:M|price:$150-$500</v>
+        <v>category:Men|size:M|size:L|color:White|price:$0-$150</v>
       </c>
     </row>
     <row r="122">
@@ -22798,7 +22798,7 @@
         <v/>
       </c>
       <c r="E122" t="str">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F122" t="str">
         <v/>
@@ -22807,7 +22807,7 @@
         <v/>
       </c>
       <c r="H122" t="str">
-        <v>/products/550e8400-e29b-41d4-a716-446655440001</v>
+        <v>/categories/Shop%20Women</v>
       </c>
       <c r="I122" t="str">
         <v/>
@@ -22861,7 +22861,7 @@
         <v/>
       </c>
       <c r="Z122" t="str">
-        <v>https://example.com/images/sm002-s.jpg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</v>
       </c>
       <c r="AA122" t="str">
         <v/>
@@ -22876,16 +22876,16 @@
         <v/>
       </c>
       <c r="AE122" t="str">
-        <v>550e8400-e29b-41d4-a716-446655440001</v>
+        <v>women-001</v>
       </c>
       <c r="AF122" t="str">
         <v/>
       </c>
       <c r="AG122" t="str">
-        <v>Cotton Tee</v>
+        <v>Ethereal Silk Slip</v>
       </c>
       <c r="AH122" t="str">
-        <v>49.99</v>
+        <v>340</v>
       </c>
       <c r="AI122" t="str">
         <v/>
@@ -22945,7 +22945,7 @@
         <v/>
       </c>
       <c r="BB122" t="str">
-        <v>men-atelier</v>
+        <v>women-atelier</v>
       </c>
       <c r="BC122" t="str">
         <v/>
@@ -22957,16 +22957,16 @@
         <v/>
       </c>
       <c r="BF122" t="str">
-        <v>Men</v>
+        <v>New Arrival</v>
       </c>
       <c r="BG122" t="str">
-        <v>S / Navy</v>
+        <v>Mulberry Silk</v>
       </c>
       <c r="BH122" t="str">
-        <v>Cotton Tee</v>
+        <v>Model in a cream silk slip dress</v>
       </c>
       <c r="BI122" t="str">
-        <v>category:Men|size:S|color:Navy|price:$0-$150</v>
+        <v>category:dresses|size:S|palette:Cream</v>
       </c>
     </row>
     <row r="123">
@@ -22983,7 +22983,7 @@
         <v/>
       </c>
       <c r="E123" t="str">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F123" t="str">
         <v/>
@@ -22992,7 +22992,7 @@
         <v/>
       </c>
       <c r="H123" t="str">
-        <v>/products/550e8400-e29b-41d4-a716-446655440000</v>
+        <v>/categories/Shop%20Women</v>
       </c>
       <c r="I123" t="str">
         <v/>
@@ -23046,7 +23046,7 @@
         <v/>
       </c>
       <c r="Z123" t="str">
-        <v>https://example.com/images/sm001-m.jpg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAULIeOGtZd7vXZH0gSJHWiv3w1w4d6Tz7E7Y55Pp0wpbrudgRPkQEUxLNJ7z1iX2ofjNS4KSwbIFdzRgJR2rZEzslEi02TskRTUycOtweLNiBcTRv0RAiCUncTPXaXvHGzovAfwglQIxRlDavgkG0kp9z1__77ZtFulQa4AVlvR_muVhFSILTRpDDYMIgzrzsCEPjKJNyVc0k_NtV_qrK021aTU5RlI_Mg4TBu8JIzJLGkLHTEGfvWBezAYGbi6wNp_bgFRdeYEwST</v>
       </c>
       <c r="AA123" t="str">
         <v/>
@@ -23061,16 +23061,16 @@
         <v/>
       </c>
       <c r="AE123" t="str">
-        <v>550e8400-e29b-41d4-a716-446655440000</v>
+        <v>women-004</v>
       </c>
       <c r="AF123" t="str">
         <v/>
       </c>
       <c r="AG123" t="str">
-        <v>Linen Shirt</v>
+        <v>Sculptural Pleated Skirt</v>
       </c>
       <c r="AH123" t="str">
-        <v>129.99</v>
+        <v>490</v>
       </c>
       <c r="AI123" t="str">
         <v/>
@@ -23130,7 +23130,7 @@
         <v/>
       </c>
       <c r="BB123" t="str">
-        <v>men-atelier</v>
+        <v>women-atelier</v>
       </c>
       <c r="BC123" t="str">
         <v/>
@@ -23142,16 +23142,16 @@
         <v/>
       </c>
       <c r="BF123" t="str">
-        <v>Men</v>
+        <v>Bottoms</v>
       </c>
       <c r="BG123" t="str">
-        <v>M / White</v>
+        <v>Pleated Wool Crepe</v>
       </c>
       <c r="BH123" t="str">
-        <v>Linen Shirt</v>
+        <v>Pleated charcoal skirt in motion through concrete architecture</v>
       </c>
       <c r="BI123" t="str">
-        <v>category:Men|size:M|size:L|color:White|price:$0-$150</v>
+        <v>category:bottoms|size:S|palette:Charcoal</v>
       </c>
     </row>
     <row r="124">
@@ -23168,7 +23168,7 @@
         <v/>
       </c>
       <c r="E124" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F124" t="str">
         <v/>
@@ -23231,7 +23231,7 @@
         <v/>
       </c>
       <c r="Z124" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</v>
       </c>
       <c r="AA124" t="str">
         <v/>
@@ -23246,16 +23246,16 @@
         <v/>
       </c>
       <c r="AE124" t="str">
-        <v>women-001</v>
+        <v>women-005</v>
       </c>
       <c r="AF124" t="str">
         <v/>
       </c>
       <c r="AG124" t="str">
-        <v>Ethereal Silk Slip</v>
+        <v>Hearth Tapered Pant</v>
       </c>
       <c r="AH124" t="str">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AI124" t="str">
         <v/>
@@ -23327,16 +23327,16 @@
         <v/>
       </c>
       <c r="BF124" t="str">
-        <v>New Arrival</v>
+        <v>Bottoms</v>
       </c>
       <c r="BG124" t="str">
-        <v>Mulberry Silk</v>
+        <v>Brushed Wool Blend</v>
       </c>
       <c r="BH124" t="str">
-        <v>Model in a cream silk slip dress</v>
+        <v>High-end trouser detail in soft terracotta</v>
       </c>
       <c r="BI124" t="str">
-        <v>category:dresses|size:S|palette:Cream</v>
+        <v>category:bottoms|size:M|palette:Charcoal</v>
       </c>
     </row>
     <row r="125">
@@ -23353,7 +23353,7 @@
         <v/>
       </c>
       <c r="E125" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F125" t="str">
         <v/>
@@ -23416,7 +23416,7 @@
         <v/>
       </c>
       <c r="Z125" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</v>
       </c>
       <c r="AA125" t="str">
         <v/>
@@ -23431,16 +23431,16 @@
         <v/>
       </c>
       <c r="AE125" t="str">
-        <v>women-002</v>
+        <v>women-006</v>
       </c>
       <c r="AF125" t="str">
         <v/>
       </c>
       <c r="AG125" t="str">
-        <v>Architectural Overcoat</v>
+        <v>Atelier Formal Blazer</v>
       </c>
       <c r="AH125" t="str">
-        <v>1250</v>
+        <v>850</v>
       </c>
       <c r="AI125" t="str">
         <v/>
@@ -23512,16 +23512,16 @@
         <v/>
       </c>
       <c r="BF125" t="str">
-        <v>Limited</v>
+        <v>Outerwear</v>
       </c>
       <c r="BG125" t="str">
-        <v>Structured Wool Twill</v>
+        <v>Tailored Wool Blend</v>
       </c>
       <c r="BH125" t="str">
-        <v>Deep forest tailored overcoat with sharp lines</v>
+        <v>Structured blazer in forest green with atelier styling</v>
       </c>
       <c r="BI125" t="str">
-        <v>category:outerwear|size:M|palette:Forest</v>
+        <v>category:outerwear|size:L|palette:Forest</v>
       </c>
     </row>
     <row r="126">
@@ -23538,7 +23538,7 @@
         <v/>
       </c>
       <c r="E126" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F126" t="str">
         <v/>
@@ -23601,7 +23601,7 @@
         <v/>
       </c>
       <c r="Z126" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBEKFEZ7Xk7Fyqc9Uf8Rr7JfhPIghhY7j0HO6bqSglckdRAUU1XFK1Vy_uPXAbpLqczXmCH41FFfT4QIgBtt7oBHhaEojRqYoMhEeW0zN9yDlgFxnnAhZfa_FjmfnZNakXUp-HAT6D2gb_BUeHA5TXBmMVsObd_AHQfOwPuMZTKrAqSkXnJe60KUnlOWajJ6btQ5zyNadwls33tVZNcDlHyJ8_EUlUAhHRtQ90ZhEzMNN5Mzjf_Hr7Onn7MZF-hkz45XkPrdm6pngSw</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</v>
       </c>
       <c r="AA126" t="str">
         <v/>
@@ -23616,16 +23616,16 @@
         <v/>
       </c>
       <c r="AE126" t="str">
-        <v>women-003</v>
+        <v>women-007</v>
       </c>
       <c r="AF126" t="str">
         <v/>
       </c>
       <c r="AG126" t="str">
-        <v>Cloud Cashmere Crew</v>
+        <v>Botanical Wrap Dress</v>
       </c>
       <c r="AH126" t="str">
-        <v>280</v>
+        <v>410</v>
       </c>
       <c r="AI126" t="str">
         <v/>
@@ -23697,16 +23697,16 @@
         <v/>
       </c>
       <c r="BF126" t="str">
-        <v>Knitwear</v>
+        <v>Draped</v>
       </c>
       <c r="BG126" t="str">
-        <v>Pure Cashmere</v>
+        <v>Washed Silk Blend</v>
       </c>
       <c r="BH126" t="str">
-        <v>Stone grey cashmere crew resting on a wooden chair</v>
+        <v>Wrap dress draped beside a window in soft daylight</v>
       </c>
       <c r="BI126" t="str">
-        <v>category:tops|size:M|palette:Stone</v>
+        <v>category:dresses|size:S|palette:Cream</v>
       </c>
     </row>
     <row r="127">
@@ -23723,7 +23723,7 @@
         <v/>
       </c>
       <c r="E127" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F127" t="str">
         <v/>
@@ -23786,7 +23786,7 @@
         <v/>
       </c>
       <c r="Z127" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAULIeOGtZd7vXZH0gSJHWiv3w1w4d6Tz7E7Y55Pp0wpbrudgRPkQEUxLNJ7z1iX2ofjNS4KSwbIFdzRgJR2rZEzslEi02TskRTUycOtweLNiBcTRv0RAiCUncTPXaXvHGzovAfwglQIxRlDavgkG0kp9z1__77ZtFulQa4AVlvR_muVhFSILTRpDDYMIgzrzsCEPjKJNyVc0k_NtV_qrK021aTU5RlI_Mg4TBu8JIzJLGkLHTEGfvWBezAYGbi6wNp_bgFRdeYEwST</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBEKFEZ7Xk7Fyqc9Uf8Rr7JfhPIghhY7j0HO6bqSglckdRAUU1XFK1Vy_uPXAbpLqczXmCH41FFfT4QIgBtt7oBHhaEojRqYoMhEeW0zN9yDlgFxnnAhZfa_FjmfnZNakXUp-HAT6D2gb_BUeHA5TXBmMVsObd_AHQfOwPuMZTKrAqSkXnJe60KUnlOWajJ6btQ5zyNadwls33tVZNcDlHyJ8_EUlUAhHRtQ90ZhEzMNN5Mzjf_Hr7Onn7MZF-hkz45XkPrdm6pngSw</v>
       </c>
       <c r="AA127" t="str">
         <v/>
@@ -23801,16 +23801,16 @@
         <v/>
       </c>
       <c r="AE127" t="str">
-        <v>women-004</v>
+        <v>women-008</v>
       </c>
       <c r="AF127" t="str">
         <v/>
       </c>
       <c r="AG127" t="str">
-        <v>Sculptural Pleated Skirt</v>
+        <v>Gallery Satin Blouse</v>
       </c>
       <c r="AH127" t="str">
-        <v>490</v>
+        <v>295</v>
       </c>
       <c r="AI127" t="str">
         <v/>
@@ -23882,16 +23882,16 @@
         <v/>
       </c>
       <c r="BF127" t="str">
-        <v>Bottoms</v>
+        <v>Studio Essential</v>
       </c>
       <c r="BG127" t="str">
-        <v>Pleated Wool Crepe</v>
+        <v>Liquid Satin</v>
       </c>
       <c r="BH127" t="str">
-        <v>Pleated charcoal skirt in motion through concrete architecture</v>
+        <v>Stone satin blouse folded on a soft boucle chair</v>
       </c>
       <c r="BI127" t="str">
-        <v>category:bottoms|size:S|palette:Charcoal</v>
+        <v>category:tops|size:S|palette:Stone</v>
       </c>
     </row>
     <row r="128">
@@ -23908,7 +23908,7 @@
         <v/>
       </c>
       <c r="E128" t="str">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F128" t="str">
         <v/>
@@ -23971,7 +23971,7 @@
         <v/>
       </c>
       <c r="Z128" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAULIeOGtZd7vXZH0gSJHWiv3w1w4d6Tz7E7Y55Pp0wpbrudgRPkQEUxLNJ7z1iX2ofjNS4KSwbIFdzRgJR2rZEzslEi02TskRTUycOtweLNiBcTRv0RAiCUncTPXaXvHGzovAfwglQIxRlDavgkG0kp9z1__77ZtFulQa4AVlvR_muVhFSILTRpDDYMIgzrzsCEPjKJNyVc0k_NtV_qrK021aTU5RlI_Mg4TBu8JIzJLGkLHTEGfvWBezAYGbi6wNp_bgFRdeYEwST</v>
       </c>
       <c r="AA128" t="str">
         <v/>
@@ -23986,16 +23986,16 @@
         <v/>
       </c>
       <c r="AE128" t="str">
-        <v>women-005</v>
+        <v>women-009</v>
       </c>
       <c r="AF128" t="str">
         <v/>
       </c>
       <c r="AG128" t="str">
-        <v>Hearth Tapered Pant</v>
+        <v>Quiet Wool Column Coat</v>
       </c>
       <c r="AH128" t="str">
-        <v>320</v>
+        <v>1180</v>
       </c>
       <c r="AI128" t="str">
         <v/>
@@ -24067,16 +24067,16 @@
         <v/>
       </c>
       <c r="BF128" t="str">
-        <v>Bottoms</v>
+        <v>Editorial Pick</v>
       </c>
       <c r="BG128" t="str">
-        <v>Brushed Wool Blend</v>
+        <v>Double-Faced Wool</v>
       </c>
       <c r="BH128" t="str">
-        <v>High-end trouser detail in soft terracotta</v>
+        <v>Long wool column coat against a pale gallery wall</v>
       </c>
       <c r="BI128" t="str">
-        <v>category:bottoms|size:M|palette:Charcoal</v>
+        <v>category:outerwear|size:M|palette:Forest</v>
       </c>
     </row>
     <row r="129">
@@ -24093,7 +24093,7 @@
         <v/>
       </c>
       <c r="E129" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F129" t="str">
         <v/>
@@ -24156,7 +24156,7 @@
         <v/>
       </c>
       <c r="Z129" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</v>
       </c>
       <c r="AA129" t="str">
         <v/>
@@ -24171,16 +24171,16 @@
         <v/>
       </c>
       <c r="AE129" t="str">
-        <v>women-006</v>
+        <v>women-010</v>
       </c>
       <c r="AF129" t="str">
         <v/>
       </c>
       <c r="AG129" t="str">
-        <v>Atelier Formal Blazer</v>
+        <v>Soft Structure Trouser</v>
       </c>
       <c r="AH129" t="str">
-        <v>850</v>
+        <v>365</v>
       </c>
       <c r="AI129" t="str">
         <v/>
@@ -24252,16 +24252,16 @@
         <v/>
       </c>
       <c r="BF129" t="str">
-        <v>Outerwear</v>
+        <v>Tailored Bottoms</v>
       </c>
       <c r="BG129" t="str">
-        <v>Tailored Wool Blend</v>
+        <v>Compact Viscose Twill</v>
       </c>
       <c r="BH129" t="str">
-        <v>Structured blazer in forest green with atelier styling</v>
+        <v>Tailored trouser displayed with a clean crease and sculpted drape</v>
       </c>
       <c r="BI129" t="str">
-        <v>category:outerwear|size:L|palette:Forest</v>
+        <v>category:bottoms|size:M|palette:Charcoal</v>
       </c>
     </row>
     <row r="130">
@@ -24278,7 +24278,7 @@
         <v/>
       </c>
       <c r="E130" t="str">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F130" t="str">
         <v/>
@@ -24341,7 +24341,7 @@
         <v/>
       </c>
       <c r="Z130" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</v>
       </c>
       <c r="AA130" t="str">
         <v/>
@@ -24356,16 +24356,16 @@
         <v/>
       </c>
       <c r="AE130" t="str">
-        <v>women-007</v>
+        <v>women-011</v>
       </c>
       <c r="AF130" t="str">
         <v/>
       </c>
       <c r="AG130" t="str">
-        <v>Botanical Wrap Dress</v>
+        <v>Moonstone Rib Tank</v>
       </c>
       <c r="AH130" t="str">
-        <v>410</v>
+        <v>180</v>
       </c>
       <c r="AI130" t="str">
         <v/>
@@ -24437,16 +24437,16 @@
         <v/>
       </c>
       <c r="BF130" t="str">
-        <v>Draped</v>
+        <v>Layering</v>
       </c>
       <c r="BG130" t="str">
-        <v>Washed Silk Blend</v>
+        <v>Fine Rib Cotton</v>
       </c>
       <c r="BH130" t="str">
-        <v>Wrap dress draped beside a window in soft daylight</v>
+        <v>Cream rib tank styled with a tonal blazer</v>
       </c>
       <c r="BI130" t="str">
-        <v>category:dresses|size:S|palette:Cream</v>
+        <v>category:tops|size:XS|palette:Cream</v>
       </c>
     </row>
     <row r="131">
@@ -24463,7 +24463,7 @@
         <v/>
       </c>
       <c r="E131" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F131" t="str">
         <v/>
@@ -24526,7 +24526,7 @@
         <v/>
       </c>
       <c r="Z131" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBEKFEZ7Xk7Fyqc9Uf8Rr7JfhPIghhY7j0HO6bqSglckdRAUU1XFK1Vy_uPXAbpLqczXmCH41FFfT4QIgBtt7oBHhaEojRqYoMhEeW0zN9yDlgFxnnAhZfa_FjmfnZNakXUp-HAT6D2gb_BUeHA5TXBmMVsObd_AHQfOwPuMZTKrAqSkXnJe60KUnlOWajJ6btQ5zyNadwls33tVZNcDlHyJ8_EUlUAhHRtQ90ZhEzMNN5Mzjf_Hr7Onn7MZF-hkz45XkPrdm6pngSw</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</v>
       </c>
       <c r="AA131" t="str">
         <v/>
@@ -24541,16 +24541,16 @@
         <v/>
       </c>
       <c r="AE131" t="str">
-        <v>women-008</v>
+        <v>women-012</v>
       </c>
       <c r="AF131" t="str">
         <v/>
       </c>
       <c r="AG131" t="str">
-        <v>Gallery Satin Blouse</v>
+        <v>Atelier Bias Midi Skirt</v>
       </c>
       <c r="AH131" t="str">
-        <v>295</v>
+        <v>430</v>
       </c>
       <c r="AI131" t="str">
         <v/>
@@ -24622,16 +24622,16 @@
         <v/>
       </c>
       <c r="BF131" t="str">
-        <v>Studio Essential</v>
+        <v>Fluid Line</v>
       </c>
       <c r="BG131" t="str">
-        <v>Liquid Satin</v>
+        <v>Washed Satin</v>
       </c>
       <c r="BH131" t="str">
-        <v>Stone satin blouse folded on a soft boucle chair</v>
+        <v>Bias midi skirt arranged in a softly lit studio</v>
       </c>
       <c r="BI131" t="str">
-        <v>category:tops|size:S|palette:Stone</v>
+        <v>category:bottoms|size:S|palette:Stone</v>
       </c>
     </row>
     <row r="132">
@@ -24648,7 +24648,7 @@
         <v/>
       </c>
       <c r="E132" t="str">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F132" t="str">
         <v/>
@@ -24657,7 +24657,7 @@
         <v/>
       </c>
       <c r="H132" t="str">
-        <v>/categories/Shop%20Women</v>
+        <v>/products/550e8400-e29b-41d4-a716-446655440002</v>
       </c>
       <c r="I132" t="str">
         <v/>
@@ -24711,7 +24711,7 @@
         <v/>
       </c>
       <c r="Z132" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAULIeOGtZd7vXZH0gSJHWiv3w1w4d6Tz7E7Y55Pp0wpbrudgRPkQEUxLNJ7z1iX2ofjNS4KSwbIFdzRgJR2rZEzslEi02TskRTUycOtweLNiBcTRv0RAiCUncTPXaXvHGzovAfwglQIxRlDavgkG0kp9z1__77ZtFulQa4AVlvR_muVhFSILTRpDDYMIgzrzsCEPjKJNyVc0k_NtV_qrK021aTU5RlI_Mg4TBu8JIzJLGkLHTEGfvWBezAYGbi6wNp_bgFRdeYEwST</v>
+        <v/>
       </c>
       <c r="AA132" t="str">
         <v/>
@@ -24726,16 +24726,16 @@
         <v/>
       </c>
       <c r="AE132" t="str">
-        <v>women-009</v>
+        <v>550e8400-e29b-41d4-a716-446655440002</v>
       </c>
       <c r="AF132" t="str">
         <v/>
       </c>
       <c r="AG132" t="str">
-        <v>Quiet Wool Column Coat</v>
+        <v>Silk Dress</v>
       </c>
       <c r="AH132" t="str">
-        <v>1180</v>
+        <v>229</v>
       </c>
       <c r="AI132" t="str">
         <v/>
@@ -24807,16 +24807,16 @@
         <v/>
       </c>
       <c r="BF132" t="str">
-        <v>Editorial Pick</v>
+        <v>Women</v>
       </c>
       <c r="BG132" t="str">
-        <v>Double-Faced Wool</v>
+        <v>Women</v>
       </c>
       <c r="BH132" t="str">
-        <v>Long wool column coat against a pale gallery wall</v>
+        <v>Silk Dress</v>
       </c>
       <c r="BI132" t="str">
-        <v>category:outerwear|size:M|palette:Forest</v>
+        <v>category:Women|price:$150-$500</v>
       </c>
     </row>
     <row r="133">
@@ -24833,7 +24833,7 @@
         <v/>
       </c>
       <c r="E133" t="str">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F133" t="str">
         <v/>
@@ -24842,7 +24842,7 @@
         <v/>
       </c>
       <c r="H133" t="str">
-        <v>/categories/Shop%20Women</v>
+        <v>/products/10000000-0000-4000-8000-000000000014</v>
       </c>
       <c r="I133" t="str">
         <v/>
@@ -24896,7 +24896,7 @@
         <v/>
       </c>
       <c r="Z133" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</v>
       </c>
       <c r="AA133" t="str">
         <v/>
@@ -24911,16 +24911,16 @@
         <v/>
       </c>
       <c r="AE133" t="str">
-        <v>women-010</v>
+        <v>10000000-0000-4000-8000-000000000014</v>
       </c>
       <c r="AF133" t="str">
         <v/>
       </c>
       <c r="AG133" t="str">
-        <v>Soft Structure Trouser</v>
+        <v>Architectural Overcoat</v>
       </c>
       <c r="AH133" t="str">
-        <v>365</v>
+        <v>1250</v>
       </c>
       <c r="AI133" t="str">
         <v/>
@@ -24992,16 +24992,16 @@
         <v/>
       </c>
       <c r="BF133" t="str">
-        <v>Tailored Bottoms</v>
+        <v>Limited</v>
       </c>
       <c r="BG133" t="str">
-        <v>Compact Viscose Twill</v>
+        <v>M / Forest</v>
       </c>
       <c r="BH133" t="str">
-        <v>Tailored trouser displayed with a clean crease and sculpted drape</v>
+        <v>Architectural Overcoat</v>
       </c>
       <c r="BI133" t="str">
-        <v>category:bottoms|size:M|palette:Charcoal</v>
+        <v>category:Women|size:M|size:L|color:Forest|price:$1000+</v>
       </c>
     </row>
     <row r="134">
@@ -25018,7 +25018,7 @@
         <v/>
       </c>
       <c r="E134" t="str">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F134" t="str">
         <v/>
@@ -25027,7 +25027,7 @@
         <v/>
       </c>
       <c r="H134" t="str">
-        <v>/categories/Shop%20Women</v>
+        <v>/products/10000000-0000-4000-8000-000000000015</v>
       </c>
       <c r="I134" t="str">
         <v/>
@@ -25081,7 +25081,7 @@
         <v/>
       </c>
       <c r="Z134" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBEKFEZ7Xk7Fyqc9Uf8Rr7JfhPIghhY7j0HO6bqSglckdRAUU1XFK1Vy_uPXAbpLqczXmCH41FFfT4QIgBtt7oBHhaEojRqYoMhEeW0zN9yDlgFxnnAhZfa_FjmfnZNakXUp-HAT6D2gb_BUeHA5TXBmMVsObd_AHQfOwPuMZTKrAqSkXnJe60KUnlOWajJ6btQ5zyNadwls33tVZNcDlHyJ8_EUlUAhHRtQ90ZhEzMNN5Mzjf_Hr7Onn7MZF-hkz45XkPrdm6pngSw</v>
       </c>
       <c r="AA134" t="str">
         <v/>
@@ -25096,16 +25096,16 @@
         <v/>
       </c>
       <c r="AE134" t="str">
-        <v>women-011</v>
+        <v>10000000-0000-4000-8000-000000000015</v>
       </c>
       <c r="AF134" t="str">
         <v/>
       </c>
       <c r="AG134" t="str">
-        <v>Moonstone Rib Tank</v>
+        <v>Cloud Cashmere Crew</v>
       </c>
       <c r="AH134" t="str">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="AI134" t="str">
         <v/>
@@ -25177,16 +25177,16 @@
         <v/>
       </c>
       <c r="BF134" t="str">
-        <v>Layering</v>
+        <v>Knitwear</v>
       </c>
       <c r="BG134" t="str">
-        <v>Fine Rib Cotton</v>
+        <v>M / Stone</v>
       </c>
       <c r="BH134" t="str">
-        <v>Cream rib tank styled with a tonal blazer</v>
+        <v>Cloud Cashmere Crew</v>
       </c>
       <c r="BI134" t="str">
-        <v>category:tops|size:XS|palette:Cream</v>
+        <v>category:Women|size:M|size:L|color:Stone|price:$150-$500</v>
       </c>
     </row>
     <row r="135">
@@ -25203,7 +25203,7 @@
         <v/>
       </c>
       <c r="E135" t="str">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F135" t="str">
         <v/>
@@ -25212,7 +25212,7 @@
         <v/>
       </c>
       <c r="H135" t="str">
-        <v>/categories/Shop%20Women</v>
+        <v>/categories/Footwear</v>
       </c>
       <c r="I135" t="str">
         <v/>
@@ -25266,7 +25266,7 @@
         <v/>
       </c>
       <c r="Z135" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</v>
       </c>
       <c r="AA135" t="str">
         <v/>
@@ -25281,16 +25281,16 @@
         <v/>
       </c>
       <c r="AE135" t="str">
-        <v>women-012</v>
+        <v>footwear-001</v>
       </c>
       <c r="AF135" t="str">
         <v/>
       </c>
       <c r="AG135" t="str">
-        <v>Atelier Bias Midi Skirt</v>
+        <v>Atelier Low Sneaker</v>
       </c>
       <c r="AH135" t="str">
-        <v>430</v>
+        <v>340</v>
       </c>
       <c r="AI135" t="str">
         <v/>
@@ -25350,7 +25350,7 @@
         <v/>
       </c>
       <c r="BB135" t="str">
-        <v>women-atelier</v>
+        <v>footwear-atelier</v>
       </c>
       <c r="BC135" t="str">
         <v/>
@@ -25362,16 +25362,16 @@
         <v/>
       </c>
       <c r="BF135" t="str">
-        <v>Fluid Line</v>
+        <v>New Arrival</v>
       </c>
       <c r="BG135" t="str">
-        <v>Washed Satin</v>
+        <v>Smooth Italian Calfskin</v>
       </c>
       <c r="BH135" t="str">
-        <v>Bias midi skirt arranged in a softly lit studio</v>
+        <v>Minimalist white leather sneaker on an architectural background</v>
       </c>
       <c r="BI135" t="str">
-        <v>category:bottoms|size:S|palette:Stone</v>
+        <v>type:Sneakers|size:41|material:Calfskin</v>
       </c>
     </row>
     <row r="136">
@@ -25388,7 +25388,7 @@
         <v/>
       </c>
       <c r="E136" t="str">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F136" t="str">
         <v/>
@@ -25397,7 +25397,7 @@
         <v/>
       </c>
       <c r="H136" t="str">
-        <v>/products/550e8400-e29b-41d4-a716-446655440002</v>
+        <v>/categories/Footwear</v>
       </c>
       <c r="I136" t="str">
         <v/>
@@ -25451,7 +25451,7 @@
         <v/>
       </c>
       <c r="Z136" t="str">
-        <v/>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</v>
       </c>
       <c r="AA136" t="str">
         <v/>
@@ -25466,16 +25466,16 @@
         <v/>
       </c>
       <c r="AE136" t="str">
-        <v>550e8400-e29b-41d4-a716-446655440002</v>
+        <v>footwear-002</v>
       </c>
       <c r="AF136" t="str">
         <v/>
       </c>
       <c r="AG136" t="str">
-        <v>Silk Dress</v>
+        <v>Chelsea Field Boot</v>
       </c>
       <c r="AH136" t="str">
-        <v>229</v>
+        <v>495</v>
       </c>
       <c r="AI136" t="str">
         <v/>
@@ -25535,7 +25535,7 @@
         <v/>
       </c>
       <c r="BB136" t="str">
-        <v>women-atelier</v>
+        <v>footwear-atelier</v>
       </c>
       <c r="BC136" t="str">
         <v/>
@@ -25547,16 +25547,16 @@
         <v/>
       </c>
       <c r="BF136" t="str">
-        <v>Women</v>
+        <v>Handcrafted</v>
       </c>
       <c r="BG136" t="str">
-        <v>Women</v>
+        <v>Waxed Roughout Leather</v>
       </c>
       <c r="BH136" t="str">
-        <v>Silk Dress</v>
+        <v>Dark brown leather chelsea boot with polished finish</v>
       </c>
       <c r="BI136" t="str">
-        <v>category:Women|price:$150-$500</v>
+        <v>type:Boots|size:42|material:Suede</v>
       </c>
     </row>
     <row r="137">
@@ -25573,7 +25573,7 @@
         <v/>
       </c>
       <c r="E137" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F137" t="str">
         <v/>
@@ -25636,7 +25636,7 @@
         <v/>
       </c>
       <c r="Z137" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</v>
       </c>
       <c r="AA137" t="str">
         <v/>
@@ -25651,16 +25651,16 @@
         <v/>
       </c>
       <c r="AE137" t="str">
-        <v>footwear-001</v>
+        <v>footwear-003</v>
       </c>
       <c r="AF137" t="str">
         <v/>
       </c>
       <c r="AG137" t="str">
-        <v>Atelier Low Sneaker</v>
+        <v>Classic Penny Loafer</v>
       </c>
       <c r="AH137" t="str">
-        <v>340</v>
+        <v>420</v>
       </c>
       <c r="AI137" t="str">
         <v/>
@@ -25732,16 +25732,16 @@
         <v/>
       </c>
       <c r="BF137" t="str">
-        <v>New Arrival</v>
+        <v>Studio Classic</v>
       </c>
       <c r="BG137" t="str">
-        <v>Smooth Italian Calfskin</v>
+        <v>Pebbled Grain Leather</v>
       </c>
       <c r="BH137" t="str">
-        <v>Minimalist white leather sneaker on an architectural background</v>
+        <v>Classic black penny loafer with minimalist buckle detail</v>
       </c>
       <c r="BI137" t="str">
-        <v>type:Sneakers|size:41|material:Calfskin</v>
+        <v>type:Loafers|size:40|material:Grain Leather</v>
       </c>
     </row>
     <row r="138">
@@ -25758,7 +25758,7 @@
         <v/>
       </c>
       <c r="E138" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F138" t="str">
         <v/>
@@ -25821,7 +25821,7 @@
         <v/>
       </c>
       <c r="Z138" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</v>
       </c>
       <c r="AA138" t="str">
         <v/>
@@ -25836,16 +25836,16 @@
         <v/>
       </c>
       <c r="AE138" t="str">
-        <v>footwear-002</v>
+        <v>footwear-004</v>
       </c>
       <c r="AF138" t="str">
         <v/>
       </c>
       <c r="AG138" t="str">
-        <v>Chelsea Field Boot</v>
+        <v>Moc Toe Service Boot</v>
       </c>
       <c r="AH138" t="str">
-        <v>495</v>
+        <v>560</v>
       </c>
       <c r="AI138" t="str">
         <v/>
@@ -25917,16 +25917,16 @@
         <v/>
       </c>
       <c r="BF138" t="str">
-        <v>Handcrafted</v>
+        <v>Workshop Build</v>
       </c>
       <c r="BG138" t="str">
-        <v>Waxed Roughout Leather</v>
+        <v>English Bridle Leather</v>
       </c>
       <c r="BH138" t="str">
-        <v>Dark brown leather chelsea boot with polished finish</v>
+        <v>High-top service boot in tobacco tan with premium hardware</v>
       </c>
       <c r="BI138" t="str">
-        <v>type:Boots|size:42|material:Suede</v>
+        <v>type:Boots|size:43|material:Bridle Leather</v>
       </c>
     </row>
     <row r="139">
@@ -25943,7 +25943,7 @@
         <v/>
       </c>
       <c r="E139" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F139" t="str">
         <v/>
@@ -26006,7 +26006,7 @@
         <v/>
       </c>
       <c r="Z139" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</v>
       </c>
       <c r="AA139" t="str">
         <v/>
@@ -26021,16 +26021,16 @@
         <v/>
       </c>
       <c r="AE139" t="str">
-        <v>footwear-003</v>
+        <v>footwear-005</v>
       </c>
       <c r="AF139" t="str">
         <v/>
       </c>
       <c r="AG139" t="str">
-        <v>Classic Penny Loafer</v>
+        <v>Ridge Runner Hiker</v>
       </c>
       <c r="AH139" t="str">
-        <v>420</v>
+        <v>610</v>
       </c>
       <c r="AI139" t="str">
         <v/>
@@ -26102,16 +26102,16 @@
         <v/>
       </c>
       <c r="BF139" t="str">
-        <v>Studio Classic</v>
+        <v>Trail Spec</v>
       </c>
       <c r="BG139" t="str">
-        <v>Pebbled Grain Leather</v>
+        <v>Stormwelt Bridle Leather</v>
       </c>
       <c r="BH139" t="str">
-        <v>Classic black penny loafer with minimalist buckle detail</v>
+        <v>Leather hiker boot styled on a stone ledge</v>
       </c>
       <c r="BI139" t="str">
-        <v>type:Loafers|size:40|material:Grain Leather</v>
+        <v>type:Boots|size:42|material:Bridle Leather</v>
       </c>
     </row>
     <row r="140">
@@ -26128,7 +26128,7 @@
         <v/>
       </c>
       <c r="E140" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F140" t="str">
         <v/>
@@ -26191,7 +26191,7 @@
         <v/>
       </c>
       <c r="Z140" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</v>
       </c>
       <c r="AA140" t="str">
         <v/>
@@ -26206,16 +26206,16 @@
         <v/>
       </c>
       <c r="AE140" t="str">
-        <v>footwear-004</v>
+        <v>footwear-006</v>
       </c>
       <c r="AF140" t="str">
         <v/>
       </c>
       <c r="AG140" t="str">
-        <v>Moc Toe Service Boot</v>
+        <v>Polished Derby Loafer</v>
       </c>
       <c r="AH140" t="str">
-        <v>560</v>
+        <v>450</v>
       </c>
       <c r="AI140" t="str">
         <v/>
@@ -26287,16 +26287,16 @@
         <v/>
       </c>
       <c r="BF140" t="str">
-        <v>Workshop Build</v>
+        <v>Hybrid Formal</v>
       </c>
       <c r="BG140" t="str">
-        <v>English Bridle Leather</v>
+        <v>Polished Grain Leather</v>
       </c>
       <c r="BH140" t="str">
-        <v>High-top service boot in tobacco tan with premium hardware</v>
+        <v>Polished derby-loafer hybrid with deep espresso shine</v>
       </c>
       <c r="BI140" t="str">
-        <v>type:Boots|size:43|material:Bridle Leather</v>
+        <v>type:Loafers|size:41|material:Grain Leather</v>
       </c>
     </row>
     <row r="141">
@@ -26313,7 +26313,7 @@
         <v/>
       </c>
       <c r="E141" t="str">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F141" t="str">
         <v/>
@@ -26376,7 +26376,7 @@
         <v/>
       </c>
       <c r="Z141" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</v>
       </c>
       <c r="AA141" t="str">
         <v/>
@@ -26391,16 +26391,16 @@
         <v/>
       </c>
       <c r="AE141" t="str">
-        <v>footwear-005</v>
+        <v>footwear-007</v>
       </c>
       <c r="AF141" t="str">
         <v/>
       </c>
       <c r="AG141" t="str">
-        <v>Ridge Runner Hiker</v>
+        <v>Slate Suede Desert Boot</v>
       </c>
       <c r="AH141" t="str">
-        <v>610</v>
+        <v>470</v>
       </c>
       <c r="AI141" t="str">
         <v/>
@@ -26472,16 +26472,16 @@
         <v/>
       </c>
       <c r="BF141" t="str">
-        <v>Trail Spec</v>
+        <v>Soft Utility</v>
       </c>
       <c r="BG141" t="str">
-        <v>Stormwelt Bridle Leather</v>
+        <v>Premium Suede</v>
       </c>
       <c r="BH141" t="str">
-        <v>Leather hiker boot styled on a stone ledge</v>
+        <v>Slate suede desert boot with tonal laces</v>
       </c>
       <c r="BI141" t="str">
-        <v>type:Boots|size:42|material:Bridle Leather</v>
+        <v>type:Boots|size:41|material:Suede</v>
       </c>
     </row>
     <row r="142">
@@ -26498,7 +26498,7 @@
         <v/>
       </c>
       <c r="E142" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F142" t="str">
         <v/>
@@ -26561,7 +26561,7 @@
         <v/>
       </c>
       <c r="Z142" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</v>
       </c>
       <c r="AA142" t="str">
         <v/>
@@ -26576,16 +26576,16 @@
         <v/>
       </c>
       <c r="AE142" t="str">
-        <v>footwear-006</v>
+        <v>footwear-008</v>
       </c>
       <c r="AF142" t="str">
         <v/>
       </c>
       <c r="AG142" t="str">
-        <v>Polished Derby Loafer</v>
+        <v>Court Leather Trainer</v>
       </c>
       <c r="AH142" t="str">
-        <v>450</v>
+        <v>360</v>
       </c>
       <c r="AI142" t="str">
         <v/>
@@ -26657,16 +26657,16 @@
         <v/>
       </c>
       <c r="BF142" t="str">
-        <v>Hybrid Formal</v>
+        <v>Everyday</v>
       </c>
       <c r="BG142" t="str">
-        <v>Polished Grain Leather</v>
+        <v>Full-Grain Calfskin</v>
       </c>
       <c r="BH142" t="str">
-        <v>Polished derby-loafer hybrid with deep espresso shine</v>
+        <v>Low-profile leather trainer set against pale concrete</v>
       </c>
       <c r="BI142" t="str">
-        <v>type:Loafers|size:41|material:Grain Leather</v>
+        <v>type:Sneakers|size:40|material:Calfskin</v>
       </c>
     </row>
     <row r="143">
@@ -26683,7 +26683,7 @@
         <v/>
       </c>
       <c r="E143" t="str">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F143" t="str">
         <v/>
@@ -26746,7 +26746,7 @@
         <v/>
       </c>
       <c r="Z143" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</v>
       </c>
       <c r="AA143" t="str">
         <v/>
@@ -26761,16 +26761,16 @@
         <v/>
       </c>
       <c r="AE143" t="str">
-        <v>footwear-007</v>
+        <v>footwear-009</v>
       </c>
       <c r="AF143" t="str">
         <v/>
       </c>
       <c r="AG143" t="str">
-        <v>Slate Suede Desert Boot</v>
+        <v>Artisan Monk Strap</v>
       </c>
       <c r="AH143" t="str">
-        <v>470</v>
+        <v>530</v>
       </c>
       <c r="AI143" t="str">
         <v/>
@@ -26842,16 +26842,16 @@
         <v/>
       </c>
       <c r="BF143" t="str">
-        <v>Soft Utility</v>
+        <v>Dress Line</v>
       </c>
       <c r="BG143" t="str">
-        <v>Premium Suede</v>
+        <v>Hand-Burnished Grain Leather</v>
       </c>
       <c r="BH143" t="str">
-        <v>Slate suede desert boot with tonal laces</v>
+        <v>Monk strap shoe with hand-burnished leather and metal buckle</v>
       </c>
       <c r="BI143" t="str">
-        <v>type:Boots|size:41|material:Suede</v>
+        <v>type:Loafers|size:41|material:Grain Leather</v>
       </c>
     </row>
     <row r="144">
@@ -26868,7 +26868,7 @@
         <v/>
       </c>
       <c r="E144" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F144" t="str">
         <v/>
@@ -26931,7 +26931,7 @@
         <v/>
       </c>
       <c r="Z144" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</v>
       </c>
       <c r="AA144" t="str">
         <v/>
@@ -26946,16 +26946,16 @@
         <v/>
       </c>
       <c r="AE144" t="str">
-        <v>footwear-008</v>
+        <v>footwear-010</v>
       </c>
       <c r="AF144" t="str">
         <v/>
       </c>
       <c r="AG144" t="str">
-        <v>Court Leather Trainer</v>
+        <v>Pebble Driving Loafer</v>
       </c>
       <c r="AH144" t="str">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="AI144" t="str">
         <v/>
@@ -27027,16 +27027,16 @@
         <v/>
       </c>
       <c r="BF144" t="str">
-        <v>Everyday</v>
+        <v>Soft Moc</v>
       </c>
       <c r="BG144" t="str">
-        <v>Full-Grain Calfskin</v>
+        <v>Pebbled Grain Leather</v>
       </c>
       <c r="BH144" t="str">
-        <v>Low-profile leather trainer set against pale concrete</v>
+        <v>Pebbled leather driving loafer on a textured stone plinth</v>
       </c>
       <c r="BI144" t="str">
-        <v>type:Sneakers|size:40|material:Calfskin</v>
+        <v>type:Loafers|size:40|material:Grain Leather</v>
       </c>
     </row>
     <row r="145">
@@ -27053,7 +27053,7 @@
         <v/>
       </c>
       <c r="E145" t="str">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F145" t="str">
         <v/>
@@ -27116,7 +27116,7 @@
         <v/>
       </c>
       <c r="Z145" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</v>
       </c>
       <c r="AA145" t="str">
         <v/>
@@ -27131,16 +27131,16 @@
         <v/>
       </c>
       <c r="AE145" t="str">
-        <v>footwear-009</v>
+        <v>footwear-011</v>
       </c>
       <c r="AF145" t="str">
         <v/>
       </c>
       <c r="AG145" t="str">
-        <v>Artisan Monk Strap</v>
+        <v>Harbor Fisher Sandal</v>
       </c>
       <c r="AH145" t="str">
-        <v>530</v>
+        <v>310</v>
       </c>
       <c r="AI145" t="str">
         <v/>
@@ -27212,16 +27212,16 @@
         <v/>
       </c>
       <c r="BF145" t="str">
-        <v>Dress Line</v>
+        <v>Warm Season</v>
       </c>
       <c r="BG145" t="str">
-        <v>Hand-Burnished Grain Leather</v>
+        <v>Matte Calfskin</v>
       </c>
       <c r="BH145" t="str">
-        <v>Monk strap shoe with hand-burnished leather and metal buckle</v>
+        <v>Minimal leather fisher sandal with matte finish</v>
       </c>
       <c r="BI145" t="str">
-        <v>type:Loafers|size:41|material:Grain Leather</v>
+        <v>type:Sandals|size:39|material:Calfskin</v>
       </c>
     </row>
     <row r="146">
@@ -27238,7 +27238,7 @@
         <v/>
       </c>
       <c r="E146" t="str">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F146" t="str">
         <v/>
@@ -27301,7 +27301,7 @@
         <v/>
       </c>
       <c r="Z146" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</v>
       </c>
       <c r="AA146" t="str">
         <v/>
@@ -27316,16 +27316,16 @@
         <v/>
       </c>
       <c r="AE146" t="str">
-        <v>footwear-010</v>
+        <v>footwear-012</v>
       </c>
       <c r="AF146" t="str">
         <v/>
       </c>
       <c r="AG146" t="str">
-        <v>Pebble Driving Loafer</v>
+        <v>Iron Commute Boot</v>
       </c>
       <c r="AH146" t="str">
-        <v>390</v>
+        <v>580</v>
       </c>
       <c r="AI146" t="str">
         <v/>
@@ -27397,16 +27397,16 @@
         <v/>
       </c>
       <c r="BF146" t="str">
-        <v>Soft Moc</v>
+        <v>City Build</v>
       </c>
       <c r="BG146" t="str">
-        <v>Pebbled Grain Leather</v>
+        <v>Weatherproof Bridle Leather</v>
       </c>
       <c r="BH146" t="str">
-        <v>Pebbled leather driving loafer on a textured stone plinth</v>
+        <v>City-ready leather boot with sturdy outsole and matte finish</v>
       </c>
       <c r="BI146" t="str">
-        <v>type:Loafers|size:40|material:Grain Leather</v>
+        <v>type:Boots|size:42|material:Bridle Leather</v>
       </c>
     </row>
     <row r="147">
@@ -27423,7 +27423,7 @@
         <v/>
       </c>
       <c r="E147" t="str">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F147" t="str">
         <v/>
@@ -27432,7 +27432,7 @@
         <v/>
       </c>
       <c r="H147" t="str">
-        <v>/categories/Footwear</v>
+        <v>/categories/Accessories</v>
       </c>
       <c r="I147" t="str">
         <v/>
@@ -27486,7 +27486,7 @@
         <v/>
       </c>
       <c r="Z147" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
       </c>
       <c r="AA147" t="str">
         <v/>
@@ -27501,16 +27501,16 @@
         <v/>
       </c>
       <c r="AE147" t="str">
-        <v>footwear-011</v>
+        <v>accessories-001</v>
       </c>
       <c r="AF147" t="str">
         <v/>
       </c>
       <c r="AG147" t="str">
-        <v>Harbor Fisher Sandal</v>
+        <v>Atelier Tote</v>
       </c>
       <c r="AH147" t="str">
-        <v>310</v>
+        <v>840</v>
       </c>
       <c r="AI147" t="str">
         <v/>
@@ -27570,7 +27570,7 @@
         <v/>
       </c>
       <c r="BB147" t="str">
-        <v>footwear-atelier</v>
+        <v>accessories-atelier</v>
       </c>
       <c r="BC147" t="str">
         <v/>
@@ -27582,16 +27582,16 @@
         <v/>
       </c>
       <c r="BF147" t="str">
-        <v>Warm Season</v>
+        <v>Limited Edition</v>
       </c>
       <c r="BG147" t="str">
-        <v>Matte Calfskin</v>
+        <v>Vegetable Tanned Leather</v>
       </c>
       <c r="BH147" t="str">
-        <v>Minimal leather fisher sandal with matte finish</v>
+        <v>Minimalist leather tote in deep forest green</v>
       </c>
       <c r="BI147" t="str">
-        <v>type:Sandals|size:39|material:Calfskin</v>
+        <v>category:Bags|material:Vachetta</v>
       </c>
     </row>
     <row r="148">
@@ -27608,7 +27608,7 @@
         <v/>
       </c>
       <c r="E148" t="str">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F148" t="str">
         <v/>
@@ -27617,7 +27617,7 @@
         <v/>
       </c>
       <c r="H148" t="str">
-        <v>/categories/Footwear</v>
+        <v>/categories/Accessories</v>
       </c>
       <c r="I148" t="str">
         <v/>
@@ -27671,7 +27671,7 @@
         <v/>
       </c>
       <c r="Z148" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
       </c>
       <c r="AA148" t="str">
         <v/>
@@ -27686,16 +27686,16 @@
         <v/>
       </c>
       <c r="AE148" t="str">
-        <v>footwear-012</v>
+        <v>accessories-002</v>
       </c>
       <c r="AF148" t="str">
         <v/>
       </c>
       <c r="AG148" t="str">
-        <v>Iron Commute Boot</v>
+        <v>Aurora Wrap</v>
       </c>
       <c r="AH148" t="str">
-        <v>580</v>
+        <v>215</v>
       </c>
       <c r="AI148" t="str">
         <v/>
@@ -27755,7 +27755,7 @@
         <v/>
       </c>
       <c r="BB148" t="str">
-        <v>footwear-atelier</v>
+        <v>accessories-atelier</v>
       </c>
       <c r="BC148" t="str">
         <v/>
@@ -27767,16 +27767,16 @@
         <v/>
       </c>
       <c r="BF148" t="str">
-        <v>City Build</v>
+        <v>Essential</v>
       </c>
       <c r="BG148" t="str">
-        <v>Weatherproof Bridle Leather</v>
+        <v>Organic Raw Silk</v>
       </c>
       <c r="BH148" t="str">
-        <v>City-ready leather boot with sturdy outsole and matte finish</v>
+        <v>Artisanal silk scarf draped over a wooden chair</v>
       </c>
       <c r="BI148" t="str">
-        <v>type:Boots|size:42|material:Bridle Leather</v>
+        <v>category:Scarves|material:Raw Silk</v>
       </c>
     </row>
     <row r="149">
@@ -27793,7 +27793,7 @@
         <v/>
       </c>
       <c r="E149" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F149" t="str">
         <v/>
@@ -27856,7 +27856,7 @@
         <v/>
       </c>
       <c r="Z149" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDclyoI7lW_Aez2lBayMz4ES5BVdH-wo43IL4ZwpD4HLQkaJqfV3eDM-qMUs4V8Uyl6BTZ9FSNg7ExFisE6J-TMxcflCy5mFritcP54bDT49eqwGnwGnsOeheOgbCmpdtfGvnHaqpfmRpU4zQvBD7B4tmigGgv7hCDEHWLojIzOlAfe5p-0cCnzLjktClPIw5lG6h2qfT0buVNcsY57FFriSrjdMpV_jPcwn3Dwsz1C-8IS20dhOYE1-Kak6Hi0R-OiEeULdIqMBj2c</v>
       </c>
       <c r="AA149" t="str">
         <v/>
@@ -27871,16 +27871,16 @@
         <v/>
       </c>
       <c r="AE149" t="str">
-        <v>accessories-001</v>
+        <v>accessories-003</v>
       </c>
       <c r="AF149" t="str">
         <v/>
       </c>
       <c r="AG149" t="str">
-        <v>Atelier Tote</v>
+        <v>Cintura Belt</v>
       </c>
       <c r="AH149" t="str">
-        <v>840</v>
+        <v>165</v>
       </c>
       <c r="AI149" t="str">
         <v/>
@@ -27952,16 +27952,16 @@
         <v/>
       </c>
       <c r="BF149" t="str">
-        <v>Limited Edition</v>
+        <v>Leather Detail</v>
       </c>
       <c r="BG149" t="str">
-        <v>Vegetable Tanned Leather</v>
+        <v>Full Grain Saddle Leather</v>
       </c>
       <c r="BH149" t="str">
-        <v>Minimalist leather tote in deep forest green</v>
+        <v>Classic leather belt with brass buckle</v>
       </c>
       <c r="BI149" t="str">
-        <v>category:Bags|material:Vachetta</v>
+        <v>category:Belts|material:Vachetta</v>
       </c>
     </row>
     <row r="150">
@@ -27978,7 +27978,7 @@
         <v/>
       </c>
       <c r="E150" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F150" t="str">
         <v/>
@@ -28041,7 +28041,7 @@
         <v/>
       </c>
       <c r="Z150" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAc-xgefZmjRHW4tYawNPs3ljWfgQ66YMBuFgX39XflOo-rQyjbJ2Ju2V0nLkyj2SVuz2BKsp1ucM74P4Gg2Q-TiJKsqrjsQRpxYORvaVExN0KFMkAU9KQFmWEmtNZHK5dm7iBBb1zYMTsluHO4Em5IwIi3lS3JGSUeU_unqmYgh-Fw65tcUaH2Ywxl8ag7h1znu1rGefQrkuDTARLHNwtQdpiGPKWCCp8JpO_yLO4kKGzLmwj8g3VfRzxs02GzkmBt2St6l1zyFYZU</v>
       </c>
       <c r="AA150" t="str">
         <v/>
@@ -28056,16 +28056,16 @@
         <v/>
       </c>
       <c r="AE150" t="str">
-        <v>accessories-002</v>
+        <v>accessories-004</v>
       </c>
       <c r="AF150" t="str">
         <v/>
       </c>
       <c r="AG150" t="str">
-        <v>Aurora Wrap</v>
+        <v>Vault Clutch</v>
       </c>
       <c r="AH150" t="str">
-        <v>215</v>
+        <v>420</v>
       </c>
       <c r="AI150" t="str">
         <v/>
@@ -28137,16 +28137,16 @@
         <v/>
       </c>
       <c r="BF150" t="str">
-        <v>Essential</v>
+        <v>Leather Detail</v>
       </c>
       <c r="BG150" t="str">
-        <v>Organic Raw Silk</v>
+        <v>Nappa Leather</v>
       </c>
       <c r="BH150" t="str">
-        <v>Artisanal silk scarf draped over a wooden chair</v>
+        <v>Sculptural leather clutch in warm cognac tone</v>
       </c>
       <c r="BI150" t="str">
-        <v>category:Scarves|material:Raw Silk</v>
+        <v>category:Bags|material:Nappa Leather</v>
       </c>
     </row>
     <row r="151">
@@ -28163,7 +28163,7 @@
         <v/>
       </c>
       <c r="E151" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F151" t="str">
         <v/>
@@ -28226,7 +28226,7 @@
         <v/>
       </c>
       <c r="Z151" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDclyoI7lW_Aez2lBayMz4ES5BVdH-wo43IL4ZwpD4HLQkaJqfV3eDM-qMUs4V8Uyl6BTZ9FSNg7ExFisE6J-TMxcflCy5mFritcP54bDT49eqwGnwGnsOeheOgbCmpdtfGvnHaqpfmRpU4zQvBD7B4tmigGgv7hCDEHWLojIzOlAfe5p-0cCnzLjktClPIw5lG6h2qfT0buVNcsY57FFriSrjdMpV_jPcwn3Dwsz1C-8IS20dhOYE1-Kak6Hi0R-OiEeULdIqMBj2c</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDwib-yVKWuTMsi4heheiLMLuw3Aukcrj4t8F5TLsWcUDULrkliTF_b5hFcyekqcaoBOrRCOob6yU3tV5aJCQChHBAggBedojt1THWZ_F-1GiBclBPJw389BrO0MvSA5xrOo1ssievm9rXO2UiIT0Ix_tHvr6rnGAPSAVNt1DYmLJVg_7vuvdan2zI6d3Z7JsuFwAqcipqjdi0FbCpFwqD4d7bZrq5JeL4i4aGx5NsOkOBZScx3UPHkR_rmJldHJi3Cb4MoiZaIoNsN</v>
       </c>
       <c r="AA151" t="str">
         <v/>
@@ -28241,16 +28241,16 @@
         <v/>
       </c>
       <c r="AE151" t="str">
-        <v>accessories-003</v>
+        <v>accessories-005</v>
       </c>
       <c r="AF151" t="str">
         <v/>
       </c>
       <c r="AG151" t="str">
-        <v>Cintura Belt</v>
+        <v>Obsidian Band</v>
       </c>
       <c r="AH151" t="str">
-        <v>165</v>
+        <v>310</v>
       </c>
       <c r="AI151" t="str">
         <v/>
@@ -28322,16 +28322,16 @@
         <v/>
       </c>
       <c r="BF151" t="str">
-        <v>Leather Detail</v>
+        <v>Limited Edition</v>
       </c>
       <c r="BG151" t="str">
-        <v>Full Grain Saddle Leather</v>
+        <v>925 Sterling Silver</v>
       </c>
       <c r="BH151" t="str">
-        <v>Classic leather belt with brass buckle</v>
+        <v>Hand-hammered sterling silver ring on dark stone</v>
       </c>
       <c r="BI151" t="str">
-        <v>category:Belts|material:Vachetta</v>
+        <v>category:Jewelry|material:Sterling Silver</v>
       </c>
     </row>
     <row r="152">
@@ -28348,7 +28348,7 @@
         <v/>
       </c>
       <c r="E152" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F152" t="str">
         <v/>
@@ -28411,7 +28411,7 @@
         <v/>
       </c>
       <c r="Z152" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAc-xgefZmjRHW4tYawNPs3ljWfgQ66YMBuFgX39XflOo-rQyjbJ2Ju2V0nLkyj2SVuz2BKsp1ucM74P4Gg2Q-TiJKsqrjsQRpxYORvaVExN0KFMkAU9KQFmWEmtNZHK5dm7iBBb1zYMTsluHO4Em5IwIi3lS3JGSUeU_unqmYgh-Fw65tcUaH2Ywxl8ag7h1znu1rGefQrkuDTARLHNwtQdpiGPKWCCp8JpO_yLO4kKGzLmwj8g3VfRzxs02GzkmBt2St6l1zyFYZU</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
       </c>
       <c r="AA152" t="str">
         <v/>
@@ -28426,16 +28426,16 @@
         <v/>
       </c>
       <c r="AE152" t="str">
-        <v>accessories-004</v>
+        <v>accessories-006</v>
       </c>
       <c r="AF152" t="str">
         <v/>
       </c>
       <c r="AG152" t="str">
-        <v>Vault Clutch</v>
+        <v>Mist Scarf</v>
       </c>
       <c r="AH152" t="str">
-        <v>420</v>
+        <v>190</v>
       </c>
       <c r="AI152" t="str">
         <v/>
@@ -28507,16 +28507,16 @@
         <v/>
       </c>
       <c r="BF152" t="str">
-        <v>Leather Detail</v>
+        <v>Soft Finish</v>
       </c>
       <c r="BG152" t="str">
-        <v>Nappa Leather</v>
+        <v>Cashmere Blend</v>
       </c>
       <c r="BH152" t="str">
-        <v>Sculptural leather clutch in warm cognac tone</v>
+        <v>Monochromatic scarf with delicate fringe detail</v>
       </c>
       <c r="BI152" t="str">
-        <v>category:Bags|material:Nappa Leather</v>
+        <v>category:Scarves|material:Cashmere</v>
       </c>
     </row>
     <row r="153">
@@ -28533,7 +28533,7 @@
         <v/>
       </c>
       <c r="E153" t="str">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F153" t="str">
         <v/>
@@ -28596,7 +28596,7 @@
         <v/>
       </c>
       <c r="Z153" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDwib-yVKWuTMsi4heheiLMLuw3Aukcrj4t8F5TLsWcUDULrkliTF_b5hFcyekqcaoBOrRCOob6yU3tV5aJCQChHBAggBedojt1THWZ_F-1GiBclBPJw389BrO0MvSA5xrOo1ssievm9rXO2UiIT0Ix_tHvr6rnGAPSAVNt1DYmLJVg_7vuvdan2zI6d3Z7JsuFwAqcipqjdi0FbCpFwqD4d7bZrq5JeL4i4aGx5NsOkOBZScx3UPHkR_rmJldHJi3Cb4MoiZaIoNsN</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
       </c>
       <c r="AA153" t="str">
         <v/>
@@ -28611,16 +28611,16 @@
         <v/>
       </c>
       <c r="AE153" t="str">
-        <v>accessories-005</v>
+        <v>accessories-007</v>
       </c>
       <c r="AF153" t="str">
         <v/>
       </c>
       <c r="AG153" t="str">
-        <v>Obsidian Band</v>
+        <v>Meridian Weekender</v>
       </c>
       <c r="AH153" t="str">
-        <v>310</v>
+        <v>980</v>
       </c>
       <c r="AI153" t="str">
         <v/>
@@ -28692,16 +28692,16 @@
         <v/>
       </c>
       <c r="BF153" t="str">
-        <v>Limited Edition</v>
+        <v>Travel Object</v>
       </c>
       <c r="BG153" t="str">
-        <v>925 Sterling Silver</v>
+        <v>Vachetta Leather</v>
       </c>
       <c r="BH153" t="str">
-        <v>Hand-hammered sterling silver ring on dark stone</v>
+        <v>Leather weekender bag with rolled handles and matte hardware</v>
       </c>
       <c r="BI153" t="str">
-        <v>category:Jewelry|material:Sterling Silver</v>
+        <v>category:Bags|material:Vachetta</v>
       </c>
     </row>
     <row r="154">
@@ -28718,7 +28718,7 @@
         <v/>
       </c>
       <c r="E154" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F154" t="str">
         <v/>
@@ -28781,7 +28781,7 @@
         <v/>
       </c>
       <c r="Z154" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDclyoI7lW_Aez2lBayMz4ES5BVdH-wo43IL4ZwpD4HLQkaJqfV3eDM-qMUs4V8Uyl6BTZ9FSNg7ExFisE6J-TMxcflCy5mFritcP54bDT49eqwGnwGnsOeheOgbCmpdtfGvnHaqpfmRpU4zQvBD7B4tmigGgv7hCDEHWLojIzOlAfe5p-0cCnzLjktClPIw5lG6h2qfT0buVNcsY57FFriSrjdMpV_jPcwn3Dwsz1C-8IS20dhOYE1-Kak6Hi0R-OiEeULdIqMBj2c</v>
       </c>
       <c r="AA154" t="str">
         <v/>
@@ -28796,16 +28796,16 @@
         <v/>
       </c>
       <c r="AE154" t="str">
-        <v>accessories-006</v>
+        <v>accessories-008</v>
       </c>
       <c r="AF154" t="str">
         <v/>
       </c>
       <c r="AG154" t="str">
-        <v>Mist Scarf</v>
+        <v>Sculptor Card Holder</v>
       </c>
       <c r="AH154" t="str">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="AI154" t="str">
         <v/>
@@ -28877,16 +28877,16 @@
         <v/>
       </c>
       <c r="BF154" t="str">
-        <v>Soft Finish</v>
+        <v>Daily Carry</v>
       </c>
       <c r="BG154" t="str">
-        <v>Cashmere Blend</v>
+        <v>Vachetta Leather</v>
       </c>
       <c r="BH154" t="str">
-        <v>Monochromatic scarf with delicate fringe detail</v>
+        <v>Compact leather card holder resting on textured stone</v>
       </c>
       <c r="BI154" t="str">
-        <v>category:Scarves|material:Cashmere</v>
+        <v>category:Bags|material:Vachetta</v>
       </c>
     </row>
     <row r="155">
@@ -28903,7 +28903,7 @@
         <v/>
       </c>
       <c r="E155" t="str">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F155" t="str">
         <v/>
@@ -28966,7 +28966,7 @@
         <v/>
       </c>
       <c r="Z155" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAc-xgefZmjRHW4tYawNPs3ljWfgQ66YMBuFgX39XflOo-rQyjbJ2Ju2V0nLkyj2SVuz2BKsp1ucM74P4Gg2Q-TiJKsqrjsQRpxYORvaVExN0KFMkAU9KQFmWEmtNZHK5dm7iBBb1zYMTsluHO4Em5IwIi3lS3JGSUeU_unqmYgh-Fw65tcUaH2Ywxl8ag7h1znu1rGefQrkuDTARLHNwtQdpiGPKWCCp8JpO_yLO4kKGzLmwj8g3VfRzxs02GzkmBt2St6l1zyFYZU</v>
       </c>
       <c r="AA155" t="str">
         <v/>
@@ -28981,16 +28981,16 @@
         <v/>
       </c>
       <c r="AE155" t="str">
-        <v>accessories-007</v>
+        <v>accessories-009</v>
       </c>
       <c r="AF155" t="str">
         <v/>
       </c>
       <c r="AG155" t="str">
-        <v>Meridian Weekender</v>
+        <v>Studio Key Lanyard</v>
       </c>
       <c r="AH155" t="str">
-        <v>980</v>
+        <v>110</v>
       </c>
       <c r="AI155" t="str">
         <v/>
@@ -29062,16 +29062,16 @@
         <v/>
       </c>
       <c r="BF155" t="str">
-        <v>Travel Object</v>
+        <v>Utility Detail</v>
       </c>
       <c r="BG155" t="str">
-        <v>Vachetta Leather</v>
+        <v>Bridle Leather</v>
       </c>
       <c r="BH155" t="str">
-        <v>Leather weekender bag with rolled handles and matte hardware</v>
+        <v>Leather key lanyard draped across a pale wooden table</v>
       </c>
       <c r="BI155" t="str">
-        <v>category:Bags|material:Vachetta</v>
+        <v>category:All Objects|material:Vachetta</v>
       </c>
     </row>
     <row r="156">
@@ -29088,7 +29088,7 @@
         <v/>
       </c>
       <c r="E156" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F156" t="str">
         <v/>
@@ -29151,7 +29151,7 @@
         <v/>
       </c>
       <c r="Z156" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDclyoI7lW_Aez2lBayMz4ES5BVdH-wo43IL4ZwpD4HLQkaJqfV3eDM-qMUs4V8Uyl6BTZ9FSNg7ExFisE6J-TMxcflCy5mFritcP54bDT49eqwGnwGnsOeheOgbCmpdtfGvnHaqpfmRpU4zQvBD7B4tmigGgv7hCDEHWLojIzOlAfe5p-0cCnzLjktClPIw5lG6h2qfT0buVNcsY57FFriSrjdMpV_jPcwn3Dwsz1C-8IS20dhOYE1-Kak6Hi0R-OiEeULdIqMBj2c</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDwib-yVKWuTMsi4heheiLMLuw3Aukcrj4t8F5TLsWcUDULrkliTF_b5hFcyekqcaoBOrRCOob6yU3tV5aJCQChHBAggBedojt1THWZ_F-1GiBclBPJw389BrO0MvSA5xrOo1ssievm9rXO2UiIT0Ix_tHvr6rnGAPSAVNt1DYmLJVg_7vuvdan2zI6d3Z7JsuFwAqcipqjdi0FbCpFwqD4d7bZrq5JeL4i4aGx5NsOkOBZScx3UPHkR_rmJldHJi3Cb4MoiZaIoNsN</v>
       </c>
       <c r="AA156" t="str">
         <v/>
@@ -29166,16 +29166,16 @@
         <v/>
       </c>
       <c r="AE156" t="str">
-        <v>accessories-008</v>
+        <v>accessories-010</v>
       </c>
       <c r="AF156" t="str">
         <v/>
       </c>
       <c r="AG156" t="str">
-        <v>Sculptor Card Holder</v>
+        <v>Veil Silk Neckerchief</v>
       </c>
       <c r="AH156" t="str">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="AI156" t="str">
         <v/>
@@ -29247,16 +29247,16 @@
         <v/>
       </c>
       <c r="BF156" t="str">
-        <v>Daily Carry</v>
+        <v>Silk Accent</v>
       </c>
       <c r="BG156" t="str">
-        <v>Vachetta Leather</v>
+        <v>Printed Raw Silk</v>
       </c>
       <c r="BH156" t="str">
-        <v>Compact leather card holder resting on textured stone</v>
+        <v>Silk neckerchief arranged beside a polished leather bag</v>
       </c>
       <c r="BI156" t="str">
-        <v>category:Bags|material:Vachetta</v>
+        <v>category:Scarves|material:Raw Silk</v>
       </c>
     </row>
     <row r="157">
@@ -29273,7 +29273,7 @@
         <v/>
       </c>
       <c r="E157" t="str">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F157" t="str">
         <v/>
@@ -29336,7 +29336,7 @@
         <v/>
       </c>
       <c r="Z157" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAc-xgefZmjRHW4tYawNPs3ljWfgQ66YMBuFgX39XflOo-rQyjbJ2Ju2V0nLkyj2SVuz2BKsp1ucM74P4Gg2Q-TiJKsqrjsQRpxYORvaVExN0KFMkAU9KQFmWEmtNZHK5dm7iBBb1zYMTsluHO4Em5IwIi3lS3JGSUeU_unqmYgh-Fw65tcUaH2Ywxl8ag7h1znu1rGefQrkuDTARLHNwtQdpiGPKWCCp8JpO_yLO4kKGzLmwj8g3VfRzxs02GzkmBt2St6l1zyFYZU</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
       </c>
       <c r="AA157" t="str">
         <v/>
@@ -29351,16 +29351,16 @@
         <v/>
       </c>
       <c r="AE157" t="str">
-        <v>accessories-009</v>
+        <v>accessories-011</v>
       </c>
       <c r="AF157" t="str">
         <v/>
       </c>
       <c r="AG157" t="str">
-        <v>Studio Key Lanyard</v>
+        <v>Hinge Cuff</v>
       </c>
       <c r="AH157" t="str">
-        <v>110</v>
+        <v>265</v>
       </c>
       <c r="AI157" t="str">
         <v/>
@@ -29432,16 +29432,16 @@
         <v/>
       </c>
       <c r="BF157" t="str">
-        <v>Utility Detail</v>
+        <v>Metal Form</v>
       </c>
       <c r="BG157" t="str">
-        <v>Bridle Leather</v>
+        <v>Sterling Silver</v>
       </c>
       <c r="BH157" t="str">
-        <v>Leather key lanyard draped across a pale wooden table</v>
+        <v>Sterling silver cuff displayed on matte black stone</v>
       </c>
       <c r="BI157" t="str">
-        <v>category:All Objects|material:Vachetta</v>
+        <v>category:Jewelry|material:Sterling Silver</v>
       </c>
     </row>
     <row r="158">
@@ -29458,7 +29458,7 @@
         <v/>
       </c>
       <c r="E158" t="str">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F158" t="str">
         <v/>
@@ -29521,7 +29521,7 @@
         <v/>
       </c>
       <c r="Z158" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDwib-yVKWuTMsi4heheiLMLuw3Aukcrj4t8F5TLsWcUDULrkliTF_b5hFcyekqcaoBOrRCOob6yU3tV5aJCQChHBAggBedojt1THWZ_F-1GiBclBPJw389BrO0MvSA5xrOo1ssievm9rXO2UiIT0Ix_tHvr6rnGAPSAVNt1DYmLJVg_7vuvdan2zI6d3Z7JsuFwAqcipqjdi0FbCpFwqD4d7bZrq5JeL4i4aGx5NsOkOBZScx3UPHkR_rmJldHJi3Cb4MoiZaIoNsN</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
       </c>
       <c r="AA158" t="str">
         <v/>
@@ -29536,16 +29536,16 @@
         <v/>
       </c>
       <c r="AE158" t="str">
-        <v>accessories-010</v>
+        <v>accessories-012</v>
       </c>
       <c r="AF158" t="str">
         <v/>
       </c>
       <c r="AG158" t="str">
-        <v>Veil Silk Neckerchief</v>
+        <v>Atelier Bucket Pouch</v>
       </c>
       <c r="AH158" t="str">
-        <v>175</v>
+        <v>390</v>
       </c>
       <c r="AI158" t="str">
         <v/>
@@ -29617,391 +29617,21 @@
         <v/>
       </c>
       <c r="BF158" t="str">
-        <v>Silk Accent</v>
+        <v>Compact Bag</v>
       </c>
       <c r="BG158" t="str">
-        <v>Printed Raw Silk</v>
+        <v>Nappa Leather</v>
       </c>
       <c r="BH158" t="str">
-        <v>Silk neckerchief arranged beside a polished leather bag</v>
+        <v>Drawstring leather pouch with minimal hardware</v>
       </c>
       <c r="BI158" t="str">
-        <v>category:Scarves|material:Raw Silk</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="str">
-        <v>category_page_product</v>
-      </c>
-      <c r="B159" t="str">
-        <v/>
-      </c>
-      <c r="C159" t="str">
-        <v/>
-      </c>
-      <c r="D159" t="str">
-        <v/>
-      </c>
-      <c r="E159" t="str">
-        <v>11</v>
-      </c>
-      <c r="F159" t="str">
-        <v/>
-      </c>
-      <c r="G159" t="str">
-        <v/>
-      </c>
-      <c r="H159" t="str">
-        <v>/categories/Accessories</v>
-      </c>
-      <c r="I159" t="str">
-        <v/>
-      </c>
-      <c r="J159" t="str">
-        <v/>
-      </c>
-      <c r="K159" t="str">
-        <v/>
-      </c>
-      <c r="L159" t="str">
-        <v/>
-      </c>
-      <c r="M159" t="str">
-        <v/>
-      </c>
-      <c r="N159" t="str">
-        <v/>
-      </c>
-      <c r="O159" t="str">
-        <v/>
-      </c>
-      <c r="P159" t="str">
-        <v/>
-      </c>
-      <c r="Q159" t="str">
-        <v/>
-      </c>
-      <c r="R159" t="str">
-        <v/>
-      </c>
-      <c r="S159" t="str">
-        <v/>
-      </c>
-      <c r="T159" t="str">
-        <v/>
-      </c>
-      <c r="U159" t="str">
-        <v/>
-      </c>
-      <c r="V159" t="str">
-        <v/>
-      </c>
-      <c r="W159" t="str">
-        <v/>
-      </c>
-      <c r="X159" t="str">
-        <v/>
-      </c>
-      <c r="Y159" t="str">
-        <v/>
-      </c>
-      <c r="Z159" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
-      </c>
-      <c r="AA159" t="str">
-        <v/>
-      </c>
-      <c r="AB159" t="str">
-        <v/>
-      </c>
-      <c r="AC159" t="str">
-        <v/>
-      </c>
-      <c r="AD159" t="str">
-        <v/>
-      </c>
-      <c r="AE159" t="str">
-        <v>accessories-011</v>
-      </c>
-      <c r="AF159" t="str">
-        <v/>
-      </c>
-      <c r="AG159" t="str">
-        <v>Hinge Cuff</v>
-      </c>
-      <c r="AH159" t="str">
-        <v>265</v>
-      </c>
-      <c r="AI159" t="str">
-        <v/>
-      </c>
-      <c r="AJ159" t="str">
-        <v/>
-      </c>
-      <c r="AK159" t="str">
-        <v/>
-      </c>
-      <c r="AL159" t="str">
-        <v/>
-      </c>
-      <c r="AM159" t="str">
-        <v/>
-      </c>
-      <c r="AN159" t="str">
-        <v/>
-      </c>
-      <c r="AO159" t="str">
-        <v/>
-      </c>
-      <c r="AP159" t="str">
-        <v/>
-      </c>
-      <c r="AQ159" t="str">
-        <v/>
-      </c>
-      <c r="AR159" t="str">
-        <v/>
-      </c>
-      <c r="AS159" t="str">
-        <v/>
-      </c>
-      <c r="AT159" t="str">
-        <v/>
-      </c>
-      <c r="AU159" t="str">
-        <v/>
-      </c>
-      <c r="AV159" t="str">
-        <v/>
-      </c>
-      <c r="AW159" t="str">
-        <v/>
-      </c>
-      <c r="AX159" t="str">
-        <v/>
-      </c>
-      <c r="AY159" t="str">
-        <v/>
-      </c>
-      <c r="AZ159" t="str">
-        <v/>
-      </c>
-      <c r="BA159" t="str">
-        <v/>
-      </c>
-      <c r="BB159" t="str">
-        <v>accessories-atelier</v>
-      </c>
-      <c r="BC159" t="str">
-        <v/>
-      </c>
-      <c r="BD159" t="str">
-        <v/>
-      </c>
-      <c r="BE159" t="str">
-        <v/>
-      </c>
-      <c r="BF159" t="str">
-        <v>Metal Form</v>
-      </c>
-      <c r="BG159" t="str">
-        <v>Sterling Silver</v>
-      </c>
-      <c r="BH159" t="str">
-        <v>Sterling silver cuff displayed on matte black stone</v>
-      </c>
-      <c r="BI159" t="str">
-        <v>category:Jewelry|material:Sterling Silver</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="str">
-        <v>category_page_product</v>
-      </c>
-      <c r="B160" t="str">
-        <v/>
-      </c>
-      <c r="C160" t="str">
-        <v/>
-      </c>
-      <c r="D160" t="str">
-        <v/>
-      </c>
-      <c r="E160" t="str">
-        <v>12</v>
-      </c>
-      <c r="F160" t="str">
-        <v/>
-      </c>
-      <c r="G160" t="str">
-        <v/>
-      </c>
-      <c r="H160" t="str">
-        <v>/categories/Accessories</v>
-      </c>
-      <c r="I160" t="str">
-        <v/>
-      </c>
-      <c r="J160" t="str">
-        <v/>
-      </c>
-      <c r="K160" t="str">
-        <v/>
-      </c>
-      <c r="L160" t="str">
-        <v/>
-      </c>
-      <c r="M160" t="str">
-        <v/>
-      </c>
-      <c r="N160" t="str">
-        <v/>
-      </c>
-      <c r="O160" t="str">
-        <v/>
-      </c>
-      <c r="P160" t="str">
-        <v/>
-      </c>
-      <c r="Q160" t="str">
-        <v/>
-      </c>
-      <c r="R160" t="str">
-        <v/>
-      </c>
-      <c r="S160" t="str">
-        <v/>
-      </c>
-      <c r="T160" t="str">
-        <v/>
-      </c>
-      <c r="U160" t="str">
-        <v/>
-      </c>
-      <c r="V160" t="str">
-        <v/>
-      </c>
-      <c r="W160" t="str">
-        <v/>
-      </c>
-      <c r="X160" t="str">
-        <v/>
-      </c>
-      <c r="Y160" t="str">
-        <v/>
-      </c>
-      <c r="Z160" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
-      </c>
-      <c r="AA160" t="str">
-        <v/>
-      </c>
-      <c r="AB160" t="str">
-        <v/>
-      </c>
-      <c r="AC160" t="str">
-        <v/>
-      </c>
-      <c r="AD160" t="str">
-        <v/>
-      </c>
-      <c r="AE160" t="str">
-        <v>accessories-012</v>
-      </c>
-      <c r="AF160" t="str">
-        <v/>
-      </c>
-      <c r="AG160" t="str">
-        <v>Atelier Bucket Pouch</v>
-      </c>
-      <c r="AH160" t="str">
-        <v>390</v>
-      </c>
-      <c r="AI160" t="str">
-        <v/>
-      </c>
-      <c r="AJ160" t="str">
-        <v/>
-      </c>
-      <c r="AK160" t="str">
-        <v/>
-      </c>
-      <c r="AL160" t="str">
-        <v/>
-      </c>
-      <c r="AM160" t="str">
-        <v/>
-      </c>
-      <c r="AN160" t="str">
-        <v/>
-      </c>
-      <c r="AO160" t="str">
-        <v/>
-      </c>
-      <c r="AP160" t="str">
-        <v/>
-      </c>
-      <c r="AQ160" t="str">
-        <v/>
-      </c>
-      <c r="AR160" t="str">
-        <v/>
-      </c>
-      <c r="AS160" t="str">
-        <v/>
-      </c>
-      <c r="AT160" t="str">
-        <v/>
-      </c>
-      <c r="AU160" t="str">
-        <v/>
-      </c>
-      <c r="AV160" t="str">
-        <v/>
-      </c>
-      <c r="AW160" t="str">
-        <v/>
-      </c>
-      <c r="AX160" t="str">
-        <v/>
-      </c>
-      <c r="AY160" t="str">
-        <v/>
-      </c>
-      <c r="AZ160" t="str">
-        <v/>
-      </c>
-      <c r="BA160" t="str">
-        <v/>
-      </c>
-      <c r="BB160" t="str">
-        <v>accessories-atelier</v>
-      </c>
-      <c r="BC160" t="str">
-        <v/>
-      </c>
-      <c r="BD160" t="str">
-        <v/>
-      </c>
-      <c r="BE160" t="str">
-        <v/>
-      </c>
-      <c r="BF160" t="str">
-        <v>Compact Bag</v>
-      </c>
-      <c r="BG160" t="str">
-        <v>Nappa Leather</v>
-      </c>
-      <c r="BH160" t="str">
-        <v>Drawstring leather pouch with minimal hardware</v>
-      </c>
-      <c r="BI160" t="str">
         <v>category:Bags|material:Nappa Leather</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:BI160"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:BI158"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/frontend/public/content/stitchfix-home.xlsx
+++ b/frontend/public/content/stitchfix-home.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI158"/>
+  <dimension ref="A1:BI154"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -12531,7 +12531,7 @@
         <v>Brushed Wool Blend</v>
       </c>
       <c r="AJ66" t="str">
-        <v>A tapered trouser used to ground the softer tops in the womenÃÂÃÂ¢ÃÂÃÂÃÂÃÂs rail.</v>
+        <v>A tapered trouser used to ground the softer tops in the womenÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¢ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂs rail.</v>
       </c>
       <c r="AK66" t="str">
         <v/>
@@ -12901,7 +12901,7 @@
         <v>Washed Silk Blend</v>
       </c>
       <c r="AJ68" t="str">
-        <v>A wrapped silhouette that keeps the womenÃÂÃÂ¢ÃÂÃÂÃÂÃÂs page light and fluid.</v>
+        <v>A wrapped silhouette that keeps the womenÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¢ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂs page light and fluid.</v>
       </c>
       <c r="AK68" t="str">
         <v/>
@@ -14196,7 +14196,7 @@
         <v>M / Forest</v>
       </c>
       <c r="AJ75" t="str">
-        <v>Sharper outerwear line pulled into the womenÃÂÃÂ¢ÃÂÃÂÃÂÃÂs edit for contrast. Curated into the All Archive rail for a fuller workbook seed.</v>
+        <v>Sharper outerwear line pulled into the womenÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¢ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂs edit for contrast. Curated into the All Archive rail for a fuller workbook seed.</v>
       </c>
       <c r="AK75" t="str">
         <v/>
@@ -14381,7 +14381,7 @@
         <v>M / Stone</v>
       </c>
       <c r="AJ76" t="str">
-        <v>A softer knit layer that keeps the womenÃÂÃÂ¢ÃÂÃÂÃÂÃÂs tab calm and tactile. Curated into the All Archive rail for a fuller workbook seed.</v>
+        <v>A softer knit layer that keeps the womenÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¢ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂs tab calm and tactile. Curated into the All Archive rail for a fuller workbook seed.</v>
       </c>
       <c r="AK76" t="str">
         <v/>
@@ -16311,7 +16311,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>product</v>
+        <v>footer_link</v>
       </c>
       <c r="B87" t="str">
         <v/>
@@ -16323,22 +16323,22 @@
         <v/>
       </c>
       <c r="E87" t="str">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F87" t="str">
         <v/>
       </c>
       <c r="G87" t="str">
-        <v/>
+        <v>Sustainability</v>
       </c>
       <c r="H87" t="str">
-        <v>/categories/Accessories</v>
+        <v>/products</v>
       </c>
       <c r="I87" t="str">
         <v/>
       </c>
       <c r="J87" t="str">
-        <v>accessories</v>
+        <v/>
       </c>
       <c r="K87" t="str">
         <v/>
@@ -16380,13 +16380,13 @@
         <v/>
       </c>
       <c r="X87" t="str">
-        <v>Metal Form</v>
+        <v/>
       </c>
       <c r="Y87" t="str">
         <v/>
       </c>
       <c r="Z87" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
+        <v/>
       </c>
       <c r="AA87" t="str">
         <v/>
@@ -16401,22 +16401,22 @@
         <v/>
       </c>
       <c r="AE87" t="str">
-        <v>accessories-011</v>
+        <v/>
       </c>
       <c r="AF87" t="str">
-        <v>ND Atelier</v>
+        <v/>
       </c>
       <c r="AG87" t="str">
-        <v>Hinge Cuff</v>
+        <v/>
       </c>
       <c r="AH87" t="str">
-        <v>265</v>
+        <v/>
       </c>
       <c r="AI87" t="str">
-        <v>Sterling Silver</v>
+        <v/>
       </c>
       <c r="AJ87" t="str">
-        <v>A cuff silhouette that expands the jewelry edit without overpowering it.</v>
+        <v/>
       </c>
       <c r="AK87" t="str">
         <v/>
@@ -16496,7 +16496,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>product</v>
+        <v>footer_link</v>
       </c>
       <c r="B88" t="str">
         <v/>
@@ -16508,22 +16508,22 @@
         <v/>
       </c>
       <c r="E88" t="str">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F88" t="str">
         <v/>
       </c>
       <c r="G88" t="str">
-        <v/>
+        <v>Atelier Services</v>
       </c>
       <c r="H88" t="str">
-        <v>/categories/Accessories</v>
+        <v>/products</v>
       </c>
       <c r="I88" t="str">
         <v/>
       </c>
       <c r="J88" t="str">
-        <v>accessories</v>
+        <v/>
       </c>
       <c r="K88" t="str">
         <v/>
@@ -16565,13 +16565,13 @@
         <v/>
       </c>
       <c r="X88" t="str">
-        <v>Compact Bag</v>
+        <v/>
       </c>
       <c r="Y88" t="str">
         <v/>
       </c>
       <c r="Z88" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
+        <v/>
       </c>
       <c r="AA88" t="str">
         <v/>
@@ -16586,22 +16586,22 @@
         <v/>
       </c>
       <c r="AE88" t="str">
-        <v>accessories-012</v>
+        <v/>
       </c>
       <c r="AF88" t="str">
-        <v>ND Atelier</v>
+        <v/>
       </c>
       <c r="AG88" t="str">
-        <v>Atelier Bucket Pouch</v>
+        <v/>
       </c>
       <c r="AH88" t="str">
-        <v>390</v>
+        <v/>
       </c>
       <c r="AI88" t="str">
-        <v>Nappa Leather</v>
+        <v/>
       </c>
       <c r="AJ88" t="str">
-        <v>A compact drawstring bag used to finish the accessories rail with a softer silhouette.</v>
+        <v/>
       </c>
       <c r="AK88" t="str">
         <v/>
@@ -16693,13 +16693,13 @@
         <v/>
       </c>
       <c r="E89" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F89" t="str">
         <v/>
       </c>
       <c r="G89" t="str">
-        <v>Sustainability</v>
+        <v>Privacy</v>
       </c>
       <c r="H89" t="str">
         <v>/products</v>
@@ -16878,13 +16878,13 @@
         <v/>
       </c>
       <c r="E90" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F90" t="str">
         <v/>
       </c>
       <c r="G90" t="str">
-        <v>Atelier Services</v>
+        <v>Terms</v>
       </c>
       <c r="H90" t="str">
         <v>/products</v>
@@ -17051,7 +17051,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>footer_link</v>
+        <v>category_page</v>
       </c>
       <c r="B91" t="str">
         <v/>
@@ -17060,19 +17060,19 @@
         <v/>
       </c>
       <c r="D91" t="str">
-        <v/>
+        <v>Workbook-driven category page aligned to the Men's Atelier screen in Stitch.</v>
       </c>
       <c r="E91" t="str">
-        <v>3</v>
+        <v/>
       </c>
       <c r="F91" t="str">
-        <v/>
+        <v>men-atelier</v>
       </c>
       <c r="G91" t="str">
-        <v>Privacy</v>
+        <v/>
       </c>
       <c r="H91" t="str">
-        <v>/products</v>
+        <v/>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -17108,7 +17108,7 @@
         <v/>
       </c>
       <c r="T91" t="str">
-        <v/>
+        <v>Structure, restraint, and material depth staged with a quieter editorial rhythm.</v>
       </c>
       <c r="U91" t="str">
         <v/>
@@ -17159,55 +17159,55 @@
         <v/>
       </c>
       <c r="AK91" t="str">
-        <v/>
+        <v>Men</v>
       </c>
       <c r="AL91" t="str">
-        <v/>
+        <v>Shop Men|shop-men|Men|men</v>
       </c>
       <c r="AM91" t="str">
-        <v/>
+        <v>The Men's</v>
       </c>
       <c r="AN91" t="str">
-        <v/>
+        <v>Men's Atelier</v>
       </c>
       <c r="AO91" t="str">
-        <v/>
+        <v>An architectural study in silhouette and structure. Crafted for the modern artisan with a steadier, darker editorial tone.</v>
       </c>
       <c r="AP91" t="str">
-        <v/>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuACWMir-mH0L8UXbUXQWypp-pFR6ldBwMeB_P57xJ4h6lF91JgCYYyEJ27pPIbRuST3wzOd8tibscQ-NbIurAXAyGOUWfZstI5mdT9d5_jh6VLXet-x-y-OPWmMV69qNvZALg2WhY1PVY_SFZnR1pxtNpFxR9lsyyLR7XmqRbJ_dhy0WQE2rK_YiUzI2TXstgAkQ537sWLyCCgyHe5Z2QW16TODc2jAY392leqTD0jFdmPyw689W_PhHTFoOURRakfD2ODeVuxVtb-u</v>
       </c>
       <c r="AQ91" t="str">
-        <v/>
+        <v>Close-up of dark wool fabric and tailored structure in the Men's Atelier</v>
       </c>
       <c r="AR91" t="str">
-        <v/>
+        <v>ND Atelier</v>
       </c>
       <c r="AS91" t="str">
-        <v/>
+        <v>Material Study</v>
       </c>
       <c r="AT91" t="str">
-        <v/>
+        <v>The Obsidian Overcoat</v>
       </c>
       <c r="AU91" t="str">
-        <v/>
+        <v>Outerwear anchors the men's edit with denser texture, stronger shoulders, and a cleaner break through the full silhouette.</v>
       </c>
       <c r="AV91" t="str">
-        <v/>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</v>
       </c>
       <c r="AW91" t="str">
-        <v/>
+        <v>Black luxury overcoat silhouette on a dark moody background</v>
       </c>
       <c r="AX91" t="str">
-        <v/>
+        <v>View Outerwear</v>
       </c>
       <c r="AY91" t="str">
-        <v/>
+        <v>/categories/Shop%20Men</v>
       </c>
       <c r="AZ91" t="str">
-        <v/>
+        <v>Showing %count% results</v>
       </c>
       <c r="BA91" t="str">
-        <v/>
+        <v>Sort by: Relevance</v>
       </c>
       <c r="BB91" t="str">
         <v/>
@@ -17236,7 +17236,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>footer_link</v>
+        <v>category_page</v>
       </c>
       <c r="B92" t="str">
         <v/>
@@ -17245,19 +17245,19 @@
         <v/>
       </c>
       <c r="D92" t="str">
-        <v/>
+        <v>Workbook-driven category page aligned to the Women's Atelier screen in Stitch.</v>
       </c>
       <c r="E92" t="str">
-        <v>4</v>
+        <v/>
       </c>
       <c r="F92" t="str">
-        <v/>
+        <v>women-atelier</v>
       </c>
       <c r="G92" t="str">
-        <v>Terms</v>
+        <v/>
       </c>
       <c r="H92" t="str">
-        <v>/products</v>
+        <v/>
       </c>
       <c r="I92" t="str">
         <v/>
@@ -17293,7 +17293,7 @@
         <v/>
       </c>
       <c r="T92" t="str">
-        <v/>
+        <v>Quiet luxury, defined by purpose.</v>
       </c>
       <c r="U92" t="str">
         <v/>
@@ -17344,55 +17344,55 @@
         <v/>
       </c>
       <c r="AK92" t="str">
-        <v/>
+        <v>Women</v>
       </c>
       <c r="AL92" t="str">
-        <v/>
+        <v>Shop Women|shop-women|Women|women</v>
       </c>
       <c r="AM92" t="str">
-        <v/>
+        <v>The Women's</v>
       </c>
       <c r="AN92" t="str">
-        <v/>
+        <v>Women's Atelier</v>
       </c>
       <c r="AO92" t="str">
-        <v/>
+        <v>Quiet luxury, sculptural drape, and natural fibers arranged with more room to breathe and a calmer editorial pace.</v>
       </c>
       <c r="AP92" t="str">
-        <v/>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCCHjHHNBD0bZoSfUrXMIUsusvSJpfmxcJRzVyGEWriuKDCynB8NOcLil0MHJfUCfgjmGv_IMPAfbmEm73hz3s6Y6ycMQrKq1qnMzNHz4QbDczvsSfdf8SaL9vw3qoSEt36Xm52OFG4ej1BLs2XxqsJW_tPT1C2xruIyndF6i4KCKATXFKExblf5UqEURDlAYRnWNDYbLXe8GGoCndX4q2IeRKAuk6Etam3vFkW85HI4vZvrHKCLYN63hA-DGdTKTpY9k-VBO3aY4le</v>
       </c>
       <c r="AQ92" t="str">
-        <v/>
+        <v>Close-up of ethereal cream silk fabric draping in a softly lit atelier</v>
       </c>
       <c r="AR92" t="str">
-        <v/>
+        <v>ND Atelier</v>
       </c>
       <c r="AS92" t="str">
-        <v/>
+        <v>The Craftsmanship</v>
       </c>
       <c r="AT92" t="str">
-        <v/>
+        <v>Soft drape, clear line, grounded warmth.</v>
       </c>
       <c r="AU92" t="str">
-        <v/>
+        <v>The women's story holds its softness without losing structure, balancing fluid dresses with sharper outerwear and richer texture.</v>
       </c>
       <c r="AV92" t="str">
-        <v/>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</v>
       </c>
       <c r="AW92" t="str">
-        <v/>
+        <v>Wide atelier scene with natural light and tactile fabric study</v>
       </c>
       <c r="AX92" t="str">
-        <v/>
+        <v>Read the Story</v>
       </c>
       <c r="AY92" t="str">
-        <v/>
+        <v>/categories/Shop%20Women</v>
       </c>
       <c r="AZ92" t="str">
-        <v/>
+        <v>Showing %count% pieces</v>
       </c>
       <c r="BA92" t="str">
-        <v/>
+        <v>Sort By</v>
       </c>
       <c r="BB92" t="str">
         <v/>
@@ -17430,13 +17430,13 @@
         <v/>
       </c>
       <c r="D93" t="str">
-        <v>Workbook-driven category page aligned to the Men's Atelier screen in Stitch.</v>
+        <v>Workbook-driven category page aligned to the Footwear Atelier screen in Stitch.</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>men-atelier</v>
+        <v>footwear-atelier</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -17478,7 +17478,7 @@
         <v/>
       </c>
       <c r="T93" t="str">
-        <v>Structure, restraint, and material depth staged with a quieter editorial rhythm.</v>
+        <v>"Luxury is not the absence of imperfection, but the presence of character."</v>
       </c>
       <c r="U93" t="str">
         <v/>
@@ -17529,49 +17529,49 @@
         <v/>
       </c>
       <c r="AK93" t="str">
-        <v>Men</v>
+        <v>Footwear</v>
       </c>
       <c r="AL93" t="str">
-        <v>Shop Men|shop-men|Men|men</v>
+        <v>Footwear|footwear</v>
       </c>
       <c r="AM93" t="str">
-        <v>The Men's</v>
+        <v>The Digital Atelier</v>
       </c>
       <c r="AN93" t="str">
-        <v>Men's Atelier</v>
+        <v>Footwear Atelier</v>
       </c>
       <c r="AO93" t="str">
-        <v>An architectural study in silhouette and structure. Crafted for the modern artisan with a steadier, darker editorial tone.</v>
+        <v>Handcrafted performance, sculptural form, and material precision for the modern explorer.</v>
       </c>
       <c r="AP93" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuACWMir-mH0L8UXbUXQWypp-pFR6ldBwMeB_P57xJ4h6lF91JgCYYyEJ27pPIbRuST3wzOd8tibscQ-NbIurAXAyGOUWfZstI5mdT9d5_jh6VLXet-x-y-OPWmMV69qNvZALg2WhY1PVY_SFZnR1pxtNpFxR9lsyyLR7XmqRbJ_dhy0WQE2rK_YiUzI2TXstgAkQ537sWLyCCgyHe5Z2QW16TODc2jAY392leqTD0jFdmPyw689W_PhHTFoOURRakfD2ODeVuxVtb-u</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAFXvDME4hl86EBAExrs0TPuPyrDnhtwEb8MCDCvjzu2OS-kjWnUF7XkqwYs0MGf5WGZS6B5xPKLv0OXCG5ZrDjkm-McNkALLC0DCYp5LC9beGhY0SnzFUMFF998AElRWMoxze_NVDcZ1jJ4qerfPiE1xI5Xjc0Euy-lzfbdQzjbDW9gtsemGrCxPBq4MDAxVn_PdqcdHWaZ05cl7EMLinkvr6U9D8RGxe-UFtVaee5Q6n-Ohev-vr9h8DwExyawlWEZa9kUKDqsxlQ</v>
       </c>
       <c r="AQ93" t="str">
-        <v>Close-up of dark wool fabric and tailored structure in the Men's Atelier</v>
+        <v>Premium leather shoemaking tools and footwear materials in a bright artisan workshop</v>
       </c>
       <c r="AR93" t="str">
-        <v>ND Atelier</v>
+        <v>Master Shoemaker, ND Atelier</v>
       </c>
       <c r="AS93" t="str">
-        <v>Material Study</v>
+        <v>The Heritage Series</v>
       </c>
       <c r="AT93" t="str">
-        <v>The Obsidian Overcoat</v>
+        <v>Heritage craft, modern proportion.</v>
       </c>
       <c r="AU93" t="str">
-        <v>Outerwear anchors the men's edit with denser texture, stronger shoulders, and a cleaner break through the full silhouette.</v>
+        <v>Leather, edge finishing, and hardware carry the footwear story with a more tactile, workshop-led tone throughout the page.</v>
       </c>
       <c r="AV93" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</v>
       </c>
       <c r="AW93" t="str">
-        <v>Black luxury overcoat silhouette on a dark moody background</v>
+        <v>Abstract editorial shot of leather boots and workshop detail</v>
       </c>
       <c r="AX93" t="str">
-        <v>View Outerwear</v>
+        <v>Discover Craft</v>
       </c>
       <c r="AY93" t="str">
-        <v>/categories/Shop%20Men</v>
+        <v>/categories/Footwear</v>
       </c>
       <c r="AZ93" t="str">
         <v>Showing %count% results</v>
@@ -17615,13 +17615,13 @@
         <v/>
       </c>
       <c r="D94" t="str">
-        <v>Workbook-driven category page aligned to the Women's Atelier screen in Stitch.</v>
+        <v>Workbook-driven category page aligned to the Accessories Atelier screen in Stitch.</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>women-atelier</v>
+        <v>accessories-atelier</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -17663,7 +17663,7 @@
         <v/>
       </c>
       <c r="T94" t="str">
-        <v>Quiet luxury, defined by purpose.</v>
+        <v>True luxury is found in the hidden details of the stitch.</v>
       </c>
       <c r="U94" t="str">
         <v/>
@@ -17714,55 +17714,55 @@
         <v/>
       </c>
       <c r="AK94" t="str">
-        <v>Women</v>
+        <v>Accessories</v>
       </c>
       <c r="AL94" t="str">
-        <v>Shop Women|shop-women|Women|women</v>
+        <v>Accessories|accessories</v>
       </c>
       <c r="AM94" t="str">
-        <v>The Women's</v>
+        <v>Accessories</v>
       </c>
       <c r="AN94" t="str">
-        <v>Women's Atelier</v>
+        <v>Accessories Atelier</v>
       </c>
       <c r="AO94" t="str">
-        <v>Quiet luxury, sculptural drape, and natural fibers arranged with more room to breathe and a calmer editorial pace.</v>
+        <v>Objects, bags, and finishing pieces shaped by material integrity and quieter architectural form.</v>
       </c>
       <c r="AP94" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCCHjHHNBD0bZoSfUrXMIUsusvSJpfmxcJRzVyGEWriuKDCynB8NOcLil0MHJfUCfgjmGv_IMPAfbmEm73hz3s6Y6ycMQrKq1qnMzNHz4QbDczvsSfdf8SaL9vw3qoSEt36Xm52OFG4ej1BLs2XxqsJW_tPT1C2xruIyndF6i4KCKATXFKExblf5UqEURDlAYRnWNDYbLXe8GGoCndX4q2IeRKAuk6Etam3vFkW85HI4vZvrHKCLYN63hA-DGdTKTpY9k-VBO3aY4le</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBlb713Ad1ZqSwci4xtZudIi3pLSP2LntjrYOZbjlMC3NLKbFllzQBjpelA2EcNqh24qXtAEpJDAyVB3yIDQIFXvkmKD86_5kVoAVPrMjID1bCAWG7fccKmwcS9kJ41ohvAPtYZJCMl2fOWYpy8JLZLlE7ksjMmFK7UnFdxUeGvbhsRltWVAsAFxPv7hkz1uizaDdvr0s5HWGulhxwsX6bDRakqRxoA2bYrvMeQA0Nta95LkdO9PMTmAYDvvqhCUeQTFYjDd4sXr9q0</v>
       </c>
       <c r="AQ94" t="str">
-        <v>Close-up of ethereal cream silk fabric draping in a softly lit atelier</v>
+        <v>Close-up of vegetable tanned leather and fine stitching tools in warm light</v>
       </c>
       <c r="AR94" t="str">
-        <v>ND Atelier</v>
+        <v>The Master Artisan</v>
       </c>
       <c r="AS94" t="str">
-        <v>The Craftsmanship</v>
+        <v>Material Focus</v>
       </c>
       <c r="AT94" t="str">
-        <v>Soft drape, clear line, grounded warmth.</v>
+        <v>Objects designed to finish the silhouette.</v>
       </c>
       <c r="AU94" t="str">
-        <v>The women's story holds its softness without losing structure, balancing fluid dresses with sharper outerwear and richer texture.</v>
+        <v>From vegetable tanned leather to raw silk, the accessory page keeps the same airy composition while every object stays editable in the workbook.</v>
       </c>
       <c r="AV94" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDwib-yVKWuTMsi4heheiLMLuw3Aukcrj4t8F5TLsWcUDULrkliTF_b5hFcyekqcaoBOrRCOob6yU3tV5aJCQChHBAggBedojt1THWZ_F-1GiBclBPJw389BrO0MvSA5xrOo1ssievm9rXO2UiIT0Ix_tHvr6rnGAPSAVNt1DYmLJVg_7vuvdan2zI6d3Z7JsuFwAqcipqjdi0FbCpFwqD4d7bZrq5JeL4i4aGx5NsOkOBZScx3UPHkR_rmJldHJi3Cb4MoiZaIoNsN</v>
       </c>
       <c r="AW94" t="str">
-        <v>Wide atelier scene with natural light and tactile fabric study</v>
+        <v>Monochromatic scarf and accessory study in a cream-toned set</v>
       </c>
       <c r="AX94" t="str">
-        <v>Read the Story</v>
+        <v>Discover Objects</v>
       </c>
       <c r="AY94" t="str">
-        <v>/categories/Shop%20Women</v>
+        <v>/categories/Accessories</v>
       </c>
       <c r="AZ94" t="str">
-        <v>Showing %count% pieces</v>
+        <v>Showing %count% results</v>
       </c>
       <c r="BA94" t="str">
-        <v>Sort By</v>
+        <v>Sort by: Relevance</v>
       </c>
       <c r="BB94" t="str">
         <v/>
@@ -17791,7 +17791,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>category_page</v>
+        <v>category_filter</v>
       </c>
       <c r="B95" t="str">
         <v/>
@@ -17800,16 +17800,16 @@
         <v/>
       </c>
       <c r="D95" t="str">
-        <v>Workbook-driven category page aligned to the Footwear Atelier screen in Stitch.</v>
+        <v/>
       </c>
       <c r="E95" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F95" t="str">
-        <v>footwear-atelier</v>
+        <v/>
       </c>
       <c r="G95" t="str">
-        <v/>
+        <v>Category</v>
       </c>
       <c r="H95" t="str">
         <v/>
@@ -17848,7 +17848,7 @@
         <v/>
       </c>
       <c r="T95" t="str">
-        <v>"Luxury is not the absence of imperfection, but the presence of character."</v>
+        <v/>
       </c>
       <c r="U95" t="str">
         <v/>
@@ -17899,64 +17899,64 @@
         <v/>
       </c>
       <c r="AK95" t="str">
-        <v>Footwear</v>
+        <v/>
       </c>
       <c r="AL95" t="str">
-        <v>Footwear|footwear</v>
+        <v/>
       </c>
       <c r="AM95" t="str">
-        <v>The Digital Atelier</v>
+        <v/>
       </c>
       <c r="AN95" t="str">
-        <v>Footwear Atelier</v>
+        <v/>
       </c>
       <c r="AO95" t="str">
-        <v>Handcrafted performance, sculptural form, and material precision for the modern explorer.</v>
+        <v/>
       </c>
       <c r="AP95" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAFXvDME4hl86EBAExrs0TPuPyrDnhtwEb8MCDCvjzu2OS-kjWnUF7XkqwYs0MGf5WGZS6B5xPKLv0OXCG5ZrDjkm-McNkALLC0DCYp5LC9beGhY0SnzFUMFF998AElRWMoxze_NVDcZ1jJ4qerfPiE1xI5Xjc0Euy-lzfbdQzjbDW9gtsemGrCxPBq4MDAxVn_PdqcdHWaZ05cl7EMLinkvr6U9D8RGxe-UFtVaee5Q6n-Ohev-vr9h8DwExyawlWEZa9kUKDqsxlQ</v>
+        <v/>
       </c>
       <c r="AQ95" t="str">
-        <v>Premium leather shoemaking tools and footwear materials in a bright artisan workshop</v>
+        <v/>
       </c>
       <c r="AR95" t="str">
-        <v>Master Shoemaker, ND Atelier</v>
+        <v/>
       </c>
       <c r="AS95" t="str">
-        <v>The Heritage Series</v>
+        <v/>
       </c>
       <c r="AT95" t="str">
-        <v>Heritage craft, modern proportion.</v>
+        <v/>
       </c>
       <c r="AU95" t="str">
-        <v>Leather, edge finishing, and hardware carry the footwear story with a more tactile, workshop-led tone throughout the page.</v>
+        <v/>
       </c>
       <c r="AV95" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</v>
+        <v/>
       </c>
       <c r="AW95" t="str">
-        <v>Abstract editorial shot of leather boots and workshop detail</v>
+        <v/>
       </c>
       <c r="AX95" t="str">
-        <v>Discover Craft</v>
+        <v/>
       </c>
       <c r="AY95" t="str">
-        <v>/categories/Footwear</v>
+        <v/>
       </c>
       <c r="AZ95" t="str">
-        <v>Showing %count% results</v>
+        <v/>
       </c>
       <c r="BA95" t="str">
-        <v>Sort by: Relevance</v>
+        <v/>
       </c>
       <c r="BB95" t="str">
-        <v/>
+        <v>men-atelier</v>
       </c>
       <c r="BC95" t="str">
-        <v/>
+        <v>category</v>
       </c>
       <c r="BD95" t="str">
-        <v/>
+        <v>Shirts|Outerwear|Trousers|Knitwear</v>
       </c>
       <c r="BE95" t="str">
         <v/>
@@ -17976,7 +17976,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>category_page</v>
+        <v>category_filter</v>
       </c>
       <c r="B96" t="str">
         <v/>
@@ -17985,16 +17985,16 @@
         <v/>
       </c>
       <c r="D96" t="str">
-        <v>Workbook-driven category page aligned to the Accessories Atelier screen in Stitch.</v>
+        <v/>
       </c>
       <c r="E96" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="F96" t="str">
-        <v>accessories-atelier</v>
+        <v/>
       </c>
       <c r="G96" t="str">
-        <v/>
+        <v>Size</v>
       </c>
       <c r="H96" t="str">
         <v/>
@@ -18033,7 +18033,7 @@
         <v/>
       </c>
       <c r="T96" t="str">
-        <v>True luxury is found in the hidden details of the stitch.</v>
+        <v/>
       </c>
       <c r="U96" t="str">
         <v/>
@@ -18084,64 +18084,64 @@
         <v/>
       </c>
       <c r="AK96" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="AL96" t="str">
-        <v>Accessories|accessories</v>
+        <v/>
       </c>
       <c r="AM96" t="str">
-        <v>Accessories</v>
+        <v/>
       </c>
       <c r="AN96" t="str">
-        <v>Accessories Atelier</v>
+        <v/>
       </c>
       <c r="AO96" t="str">
-        <v>Objects, bags, and finishing pieces shaped by material integrity and quieter architectural form.</v>
+        <v/>
       </c>
       <c r="AP96" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBlb713Ad1ZqSwci4xtZudIi3pLSP2LntjrYOZbjlMC3NLKbFllzQBjpelA2EcNqh24qXtAEpJDAyVB3yIDQIFXvkmKD86_5kVoAVPrMjID1bCAWG7fccKmwcS9kJ41ohvAPtYZJCMl2fOWYpy8JLZLlE7ksjMmFK7UnFdxUeGvbhsRltWVAsAFxPv7hkz1uizaDdvr0s5HWGulhxwsX6bDRakqRxoA2bYrvMeQA0Nta95LkdO9PMTmAYDvvqhCUeQTFYjDd4sXr9q0</v>
+        <v/>
       </c>
       <c r="AQ96" t="str">
-        <v>Close-up of vegetable tanned leather and fine stitching tools in warm light</v>
+        <v/>
       </c>
       <c r="AR96" t="str">
-        <v>The Master Artisan</v>
+        <v/>
       </c>
       <c r="AS96" t="str">
-        <v>Material Focus</v>
+        <v/>
       </c>
       <c r="AT96" t="str">
-        <v>Objects designed to finish the silhouette.</v>
+        <v/>
       </c>
       <c r="AU96" t="str">
-        <v>From vegetable tanned leather to raw silk, the accessory page keeps the same airy composition while every object stays editable in the workbook.</v>
+        <v/>
       </c>
       <c r="AV96" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDwib-yVKWuTMsi4heheiLMLuw3Aukcrj4t8F5TLsWcUDULrkliTF_b5hFcyekqcaoBOrRCOob6yU3tV5aJCQChHBAggBedojt1THWZ_F-1GiBclBPJw389BrO0MvSA5xrOo1ssievm9rXO2UiIT0Ix_tHvr6rnGAPSAVNt1DYmLJVg_7vuvdan2zI6d3Z7JsuFwAqcipqjdi0FbCpFwqD4d7bZrq5JeL4i4aGx5NsOkOBZScx3UPHkR_rmJldHJi3Cb4MoiZaIoNsN</v>
+        <v/>
       </c>
       <c r="AW96" t="str">
-        <v>Monochromatic scarf and accessory study in a cream-toned set</v>
+        <v/>
       </c>
       <c r="AX96" t="str">
-        <v>Discover Objects</v>
+        <v/>
       </c>
       <c r="AY96" t="str">
-        <v>/categories/Accessories</v>
+        <v/>
       </c>
       <c r="AZ96" t="str">
-        <v>Showing %count% results</v>
+        <v/>
       </c>
       <c r="BA96" t="str">
-        <v>Sort by: Relevance</v>
+        <v/>
       </c>
       <c r="BB96" t="str">
-        <v/>
+        <v>men-atelier</v>
       </c>
       <c r="BC96" t="str">
-        <v/>
+        <v>size</v>
       </c>
       <c r="BD96" t="str">
-        <v/>
+        <v>S|M|L|XL</v>
       </c>
       <c r="BE96" t="str">
         <v/>
@@ -18173,13 +18173,13 @@
         <v/>
       </c>
       <c r="E97" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F97" t="str">
         <v/>
       </c>
       <c r="G97" t="str">
-        <v>Category</v>
+        <v>Price Range</v>
       </c>
       <c r="H97" t="str">
         <v/>
@@ -18323,10 +18323,10 @@
         <v>men-atelier</v>
       </c>
       <c r="BC97" t="str">
-        <v>category</v>
+        <v>price</v>
       </c>
       <c r="BD97" t="str">
-        <v>Shirts|Outerwear|Trousers|Knitwear</v>
+        <v>$150-$500|$500-$1000|$1000+</v>
       </c>
       <c r="BE97" t="str">
         <v/>
@@ -18358,13 +18358,13 @@
         <v/>
       </c>
       <c r="E98" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F98" t="str">
         <v/>
       </c>
       <c r="G98" t="str">
-        <v>Size</v>
+        <v>Categories</v>
       </c>
       <c r="H98" t="str">
         <v/>
@@ -18505,13 +18505,13 @@
         <v/>
       </c>
       <c r="BB98" t="str">
-        <v>men-atelier</v>
+        <v>women-atelier</v>
       </c>
       <c r="BC98" t="str">
-        <v>size</v>
+        <v>category</v>
       </c>
       <c r="BD98" t="str">
-        <v>S|M|L|XL</v>
+        <v>Dresses|Tops|Bottoms|Outerwear</v>
       </c>
       <c r="BE98" t="str">
         <v/>
@@ -18543,13 +18543,13 @@
         <v/>
       </c>
       <c r="E99" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F99" t="str">
         <v/>
       </c>
       <c r="G99" t="str">
-        <v>Price Range</v>
+        <v>Size</v>
       </c>
       <c r="H99" t="str">
         <v/>
@@ -18690,13 +18690,13 @@
         <v/>
       </c>
       <c r="BB99" t="str">
-        <v>men-atelier</v>
+        <v>women-atelier</v>
       </c>
       <c r="BC99" t="str">
-        <v>price</v>
+        <v>size</v>
       </c>
       <c r="BD99" t="str">
-        <v>$150-$500|$500-$1000|$1000+</v>
+        <v>XS|S|M|L|XL</v>
       </c>
       <c r="BE99" t="str">
         <v/>
@@ -18728,13 +18728,13 @@
         <v/>
       </c>
       <c r="E100" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F100" t="str">
         <v/>
       </c>
       <c r="G100" t="str">
-        <v>Categories</v>
+        <v>Palette</v>
       </c>
       <c r="H100" t="str">
         <v/>
@@ -18878,10 +18878,10 @@
         <v>women-atelier</v>
       </c>
       <c r="BC100" t="str">
-        <v>category</v>
+        <v>palette</v>
       </c>
       <c r="BD100" t="str">
-        <v>Dresses|Tops|Bottoms|Outerwear</v>
+        <v>Cream|Forest|Stone|Charcoal</v>
       </c>
       <c r="BE100" t="str">
         <v/>
@@ -18913,13 +18913,13 @@
         <v/>
       </c>
       <c r="E101" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F101" t="str">
         <v/>
       </c>
       <c r="G101" t="str">
-        <v>Size</v>
+        <v>Type</v>
       </c>
       <c r="H101" t="str">
         <v/>
@@ -19060,13 +19060,13 @@
         <v/>
       </c>
       <c r="BB101" t="str">
-        <v>women-atelier</v>
+        <v>footwear-atelier</v>
       </c>
       <c r="BC101" t="str">
-        <v>size</v>
+        <v>type</v>
       </c>
       <c r="BD101" t="str">
-        <v>XS|S|M|L|XL</v>
+        <v>Boots|Sneakers|Loafers|Sandals</v>
       </c>
       <c r="BE101" t="str">
         <v/>
@@ -19098,13 +19098,13 @@
         <v/>
       </c>
       <c r="E102" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F102" t="str">
         <v/>
       </c>
       <c r="G102" t="str">
-        <v>Palette</v>
+        <v>Size</v>
       </c>
       <c r="H102" t="str">
         <v/>
@@ -19245,13 +19245,13 @@
         <v/>
       </c>
       <c r="BB102" t="str">
-        <v>women-atelier</v>
+        <v>footwear-atelier</v>
       </c>
       <c r="BC102" t="str">
-        <v>palette</v>
+        <v>size</v>
       </c>
       <c r="BD102" t="str">
-        <v>Cream|Forest|Stone|Charcoal</v>
+        <v>39|40|41|42|43</v>
       </c>
       <c r="BE102" t="str">
         <v/>
@@ -19283,13 +19283,13 @@
         <v/>
       </c>
       <c r="E103" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F103" t="str">
         <v/>
       </c>
       <c r="G103" t="str">
-        <v>Type</v>
+        <v>Material</v>
       </c>
       <c r="H103" t="str">
         <v/>
@@ -19433,10 +19433,10 @@
         <v>footwear-atelier</v>
       </c>
       <c r="BC103" t="str">
-        <v>type</v>
+        <v>material</v>
       </c>
       <c r="BD103" t="str">
-        <v>Boots|Sneakers|Loafers|Sandals</v>
+        <v>Calfskin|Suede|Grain Leather|Bridle Leather</v>
       </c>
       <c r="BE103" t="str">
         <v/>
@@ -19468,13 +19468,13 @@
         <v/>
       </c>
       <c r="E104" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F104" t="str">
         <v/>
       </c>
       <c r="G104" t="str">
-        <v>Size</v>
+        <v>Category</v>
       </c>
       <c r="H104" t="str">
         <v/>
@@ -19615,13 +19615,13 @@
         <v/>
       </c>
       <c r="BB104" t="str">
-        <v>footwear-atelier</v>
+        <v>accessories-atelier</v>
       </c>
       <c r="BC104" t="str">
-        <v>size</v>
+        <v>category</v>
       </c>
       <c r="BD104" t="str">
-        <v>39|40|41|42|43</v>
+        <v>All Objects|Bags|Belts|Jewelry|Scarves</v>
       </c>
       <c r="BE104" t="str">
         <v/>
@@ -19653,7 +19653,7 @@
         <v/>
       </c>
       <c r="E105" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F105" t="str">
         <v/>
@@ -19800,13 +19800,13 @@
         <v/>
       </c>
       <c r="BB105" t="str">
-        <v>footwear-atelier</v>
+        <v>accessories-atelier</v>
       </c>
       <c r="BC105" t="str">
         <v>material</v>
       </c>
       <c r="BD105" t="str">
-        <v>Calfskin|Suede|Grain Leather|Bridle Leather</v>
+        <v>Raw Silk|Vachetta|Sterling Silver|Cashmere|Nappa Leather</v>
       </c>
       <c r="BE105" t="str">
         <v/>
@@ -19826,7 +19826,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>category_filter</v>
+        <v>category_page_product</v>
       </c>
       <c r="B106" t="str">
         <v/>
@@ -19844,10 +19844,10 @@
         <v/>
       </c>
       <c r="G106" t="str">
-        <v>Category</v>
+        <v/>
       </c>
       <c r="H106" t="str">
-        <v/>
+        <v>/categories/Shop%20Men</v>
       </c>
       <c r="I106" t="str">
         <v/>
@@ -19901,7 +19901,7 @@
         <v/>
       </c>
       <c r="Z106" t="str">
-        <v/>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</v>
       </c>
       <c r="AA106" t="str">
         <v/>
@@ -19916,16 +19916,16 @@
         <v/>
       </c>
       <c r="AE106" t="str">
-        <v/>
+        <v>men-001</v>
       </c>
       <c r="AF106" t="str">
         <v/>
       </c>
       <c r="AG106" t="str">
-        <v/>
+        <v>Sculpted Linen Shirt</v>
       </c>
       <c r="AH106" t="str">
-        <v/>
+        <v>420</v>
       </c>
       <c r="AI106" t="str">
         <v/>
@@ -19985,33 +19985,33 @@
         <v/>
       </c>
       <c r="BB106" t="str">
-        <v>accessories-atelier</v>
+        <v>men-atelier</v>
       </c>
       <c r="BC106" t="str">
-        <v>category</v>
+        <v/>
       </c>
       <c r="BD106" t="str">
-        <v>All Objects|Bags|Belts|Jewelry|Scarves</v>
+        <v/>
       </c>
       <c r="BE106" t="str">
         <v/>
       </c>
       <c r="BF106" t="str">
-        <v/>
+        <v>New Arrival</v>
       </c>
       <c r="BG106" t="str">
-        <v/>
+        <v>Italian Linen Blend</v>
       </c>
       <c r="BH106" t="str">
-        <v/>
+        <v>Cream tailored linen shirt in morning light</v>
       </c>
       <c r="BI106" t="str">
-        <v/>
+        <v>category:shirts|size:M|price:$150-$500</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>category_filter</v>
+        <v>category_page_product</v>
       </c>
       <c r="B107" t="str">
         <v/>
@@ -20029,10 +20029,10 @@
         <v/>
       </c>
       <c r="G107" t="str">
-        <v>Material</v>
+        <v/>
       </c>
       <c r="H107" t="str">
-        <v/>
+        <v>/categories/Shop%20Men</v>
       </c>
       <c r="I107" t="str">
         <v/>
@@ -20086,7 +20086,7 @@
         <v/>
       </c>
       <c r="Z107" t="str">
-        <v/>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</v>
       </c>
       <c r="AA107" t="str">
         <v/>
@@ -20101,16 +20101,16 @@
         <v/>
       </c>
       <c r="AE107" t="str">
-        <v/>
+        <v>men-002</v>
       </c>
       <c r="AF107" t="str">
         <v/>
       </c>
       <c r="AG107" t="str">
-        <v/>
+        <v>Structured Atelier Jacket</v>
       </c>
       <c r="AH107" t="str">
-        <v/>
+        <v>1250</v>
       </c>
       <c r="AI107" t="str">
         <v/>
@@ -20170,28 +20170,28 @@
         <v/>
       </c>
       <c r="BB107" t="str">
-        <v>accessories-atelier</v>
+        <v>men-atelier</v>
       </c>
       <c r="BC107" t="str">
-        <v>material</v>
+        <v/>
       </c>
       <c r="BD107" t="str">
-        <v>Raw Silk|Vachetta|Sterling Silver|Cashmere|Nappa Leather</v>
+        <v/>
       </c>
       <c r="BE107" t="str">
         <v/>
       </c>
       <c r="BF107" t="str">
-        <v/>
+        <v>Limited Edition</v>
       </c>
       <c r="BG107" t="str">
-        <v/>
+        <v>100% Merino Wool</v>
       </c>
       <c r="BH107" t="str">
-        <v/>
+        <v>Structured dark wool jacket with precise lapel detail</v>
       </c>
       <c r="BI107" t="str">
-        <v/>
+        <v>category:outerwear|size:L|price:$1000+</v>
       </c>
     </row>
     <row r="108">
@@ -20208,7 +20208,7 @@
         <v/>
       </c>
       <c r="E108" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F108" t="str">
         <v/>
@@ -20271,7 +20271,7 @@
         <v/>
       </c>
       <c r="Z108" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBXRSWOWcHtCNyaMDYLCJzvRD_aYObkVBkIHPoz_HZOOuihWxPKo82MAX7anUmfBqHwOgx_6YthGokOn-aqEtAkMya3di9RNTlqqA2-zqT6x85Yh0CGWy5_gOTjOOMYxnRJ7B8A9ihZaMR-PzIAILb7T5rSMUCiZ-3CZRTX_u3XxJpOlXlYjWEZj4aFLaV_mamuWkKjkhTxSRpw7LyICx9lPITcKUuGOxJ0NkpKweDI4rMjqFkSSGZJssErigmmpbKq5Z6kLPVUehXg</v>
       </c>
       <c r="AA108" t="str">
         <v/>
@@ -20286,16 +20286,16 @@
         <v/>
       </c>
       <c r="AE108" t="str">
-        <v>men-001</v>
+        <v>men-003</v>
       </c>
       <c r="AF108" t="str">
         <v/>
       </c>
       <c r="AG108" t="str">
-        <v>Sculpted Linen Shirt</v>
+        <v>Modern Drape Trousers</v>
       </c>
       <c r="AH108" t="str">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="AI108" t="str">
         <v/>
@@ -20367,16 +20367,16 @@
         <v/>
       </c>
       <c r="BF108" t="str">
-        <v>New Arrival</v>
+        <v>Tailoring</v>
       </c>
       <c r="BG108" t="str">
-        <v>Italian Linen Blend</v>
+        <v>Fine Serge Cotton</v>
       </c>
       <c r="BH108" t="str">
-        <v>Cream tailored linen shirt in morning light</v>
+        <v>Folded olive trousers with sharp crease</v>
       </c>
       <c r="BI108" t="str">
-        <v>category:shirts|size:M|price:$150-$500</v>
+        <v>category:trousers|size:M|price:$150-$500</v>
       </c>
     </row>
     <row r="109">
@@ -20393,7 +20393,7 @@
         <v/>
       </c>
       <c r="E109" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F109" t="str">
         <v/>
@@ -20456,7 +20456,7 @@
         <v/>
       </c>
       <c r="Z109" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDBowt2AR0QGkZ_teHLK0qG2iUl8fGSUuNTrZHreU_s95xtmrbnCTB8LYOShnHaraaNDqoUnziBnVe2Rh6OAlJpU9ZSpF84L0-k23aokXc6aJdWswRdyGowycFswnENPgO9tfnUyUaMa2VjW8lGJYkmhPbnJhSE0zC0BdoSTdae8pmGnQwaAXzVlJJRhWYysiO1yf2n_lREj8nVxarkGub1OLnfLI4QrhAiAGV-AZTWnZg1MCqdpNi1pBSjb6RIPFAzXw0h_iTQCqrp</v>
       </c>
       <c r="AA109" t="str">
         <v/>
@@ -20471,16 +20471,16 @@
         <v/>
       </c>
       <c r="AE109" t="str">
-        <v>men-002</v>
+        <v>men-004</v>
       </c>
       <c r="AF109" t="str">
         <v/>
       </c>
       <c r="AG109" t="str">
-        <v>Structured Atelier Jacket</v>
+        <v>Atelier Knit Polo</v>
       </c>
       <c r="AH109" t="str">
-        <v>1250</v>
+        <v>290</v>
       </c>
       <c r="AI109" t="str">
         <v/>
@@ -20552,16 +20552,16 @@
         <v/>
       </c>
       <c r="BF109" t="str">
-        <v>Limited Edition</v>
+        <v>Knitwear</v>
       </c>
       <c r="BG109" t="str">
-        <v>100% Merino Wool</v>
+        <v>Sea Island Cotton</v>
       </c>
       <c r="BH109" t="str">
-        <v>Structured dark wool jacket with precise lapel detail</v>
+        <v>Dark green knit polo with horn buttons</v>
       </c>
       <c r="BI109" t="str">
-        <v>category:outerwear|size:L|price:$1000+</v>
+        <v>category:knitwear|size:M|price:$150-$500</v>
       </c>
     </row>
     <row r="110">
@@ -20578,7 +20578,7 @@
         <v/>
       </c>
       <c r="E110" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F110" t="str">
         <v/>
@@ -20641,7 +20641,7 @@
         <v/>
       </c>
       <c r="Z110" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBXRSWOWcHtCNyaMDYLCJzvRD_aYObkVBkIHPoz_HZOOuihWxPKo82MAX7anUmfBqHwOgx_6YthGokOn-aqEtAkMya3di9RNTlqqA2-zqT6x85Yh0CGWy5_gOTjOOMYxnRJ7B8A9ihZaMR-PzIAILb7T5rSMUCiZ-3CZRTX_u3XxJpOlXlYjWEZj4aFLaV_mamuWkKjkhTxSRpw7LyICx9lPITcKUuGOxJ0NkpKweDI4rMjqFkSSGZJssErigmmpbKq5Z6kLPVUehXg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</v>
       </c>
       <c r="AA110" t="str">
         <v/>
@@ -20656,16 +20656,16 @@
         <v/>
       </c>
       <c r="AE110" t="str">
-        <v>men-003</v>
+        <v>men-005</v>
       </c>
       <c r="AF110" t="str">
         <v/>
       </c>
       <c r="AG110" t="str">
-        <v>Modern Drape Trousers</v>
+        <v>The Obsidian Overcoat</v>
       </c>
       <c r="AH110" t="str">
-        <v>380</v>
+        <v>1890</v>
       </c>
       <c r="AI110" t="str">
         <v/>
@@ -20737,16 +20737,16 @@
         <v/>
       </c>
       <c r="BF110" t="str">
-        <v>Tailoring</v>
+        <v>Editorial Pick</v>
       </c>
       <c r="BG110" t="str">
-        <v>Fine Serge Cotton</v>
+        <v>Cashmere Blend</v>
       </c>
       <c r="BH110" t="str">
-        <v>Folded olive trousers with sharp crease</v>
+        <v>Black overcoat silhouette on a dark background</v>
       </c>
       <c r="BI110" t="str">
-        <v>category:trousers|size:M|price:$150-$500</v>
+        <v>category:outerwear|size:L|price:$1000+</v>
       </c>
     </row>
     <row r="111">
@@ -20763,7 +20763,7 @@
         <v/>
       </c>
       <c r="E111" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F111" t="str">
         <v/>
@@ -20826,7 +20826,7 @@
         <v/>
       </c>
       <c r="Z111" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDBowt2AR0QGkZ_teHLK0qG2iUl8fGSUuNTrZHreU_s95xtmrbnCTB8LYOShnHaraaNDqoUnziBnVe2Rh6OAlJpU9ZSpF84L0-k23aokXc6aJdWswRdyGowycFswnENPgO9tfnUyUaMa2VjW8lGJYkmhPbnJhSE0zC0BdoSTdae8pmGnQwaAXzVlJJRhWYysiO1yf2n_lREj8nVxarkGub1OLnfLI4QrhAiAGV-AZTWnZg1MCqdpNi1pBSjb6RIPFAzXw0h_iTQCqrp</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</v>
       </c>
       <c r="AA111" t="str">
         <v/>
@@ -20841,16 +20841,16 @@
         <v/>
       </c>
       <c r="AE111" t="str">
-        <v>men-004</v>
+        <v>men-006</v>
       </c>
       <c r="AF111" t="str">
         <v/>
       </c>
       <c r="AG111" t="str">
-        <v>Atelier Knit Polo</v>
+        <v>Relaxed Cargo Trouser</v>
       </c>
       <c r="AH111" t="str">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="AI111" t="str">
         <v/>
@@ -20922,16 +20922,16 @@
         <v/>
       </c>
       <c r="BF111" t="str">
-        <v>Knitwear</v>
+        <v>Studio Essential</v>
       </c>
       <c r="BG111" t="str">
-        <v>Sea Island Cotton</v>
+        <v>Brushed Twill</v>
       </c>
       <c r="BH111" t="str">
-        <v>Dark green knit polo with horn buttons</v>
+        <v>Khaki trouser texture and pocket detail</v>
       </c>
       <c r="BI111" t="str">
-        <v>category:knitwear|size:M|price:$150-$500</v>
+        <v>category:trousers|size:S|price:$150-$500</v>
       </c>
     </row>
     <row r="112">
@@ -20948,7 +20948,7 @@
         <v/>
       </c>
       <c r="E112" t="str">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F112" t="str">
         <v/>
@@ -21011,7 +21011,7 @@
         <v/>
       </c>
       <c r="Z112" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</v>
       </c>
       <c r="AA112" t="str">
         <v/>
@@ -21026,16 +21026,16 @@
         <v/>
       </c>
       <c r="AE112" t="str">
-        <v>men-005</v>
+        <v>men-007</v>
       </c>
       <c r="AF112" t="str">
         <v/>
       </c>
       <c r="AG112" t="str">
-        <v>The Obsidian Overcoat</v>
+        <v>Stonewashed Utility Overshirt</v>
       </c>
       <c r="AH112" t="str">
-        <v>1890</v>
+        <v>360</v>
       </c>
       <c r="AI112" t="str">
         <v/>
@@ -21107,16 +21107,16 @@
         <v/>
       </c>
       <c r="BF112" t="str">
-        <v>Editorial Pick</v>
+        <v>Workshop Layer</v>
       </c>
       <c r="BG112" t="str">
-        <v>Cashmere Blend</v>
+        <v>Washed Cotton Drill</v>
       </c>
       <c r="BH112" t="str">
-        <v>Black overcoat silhouette on a dark background</v>
+        <v>Stonewashed overshirt on a wooden hanger</v>
       </c>
       <c r="BI112" t="str">
-        <v>category:outerwear|size:L|price:$1000+</v>
+        <v>category:shirts|size:M|price:$150-$500</v>
       </c>
     </row>
     <row r="113">
@@ -21133,7 +21133,7 @@
         <v/>
       </c>
       <c r="E113" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F113" t="str">
         <v/>
@@ -21196,7 +21196,7 @@
         <v/>
       </c>
       <c r="Z113" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBXRSWOWcHtCNyaMDYLCJzvRD_aYObkVBkIHPoz_HZOOuihWxPKo82MAX7anUmfBqHwOgx_6YthGokOn-aqEtAkMya3di9RNTlqqA2-zqT6x85Yh0CGWy5_gOTjOOMYxnRJ7B8A9ihZaMR-PzIAILb7T5rSMUCiZ-3CZRTX_u3XxJpOlXlYjWEZj4aFLaV_mamuWkKjkhTxSRpw7LyICx9lPITcKUuGOxJ0NkpKweDI4rMjqFkSSGZJssErigmmpbKq5Z6kLPVUehXg</v>
       </c>
       <c r="AA113" t="str">
         <v/>
@@ -21211,16 +21211,16 @@
         <v/>
       </c>
       <c r="AE113" t="str">
-        <v>men-006</v>
+        <v>men-008</v>
       </c>
       <c r="AF113" t="str">
         <v/>
       </c>
       <c r="AG113" t="str">
-        <v>Relaxed Cargo Trouser</v>
+        <v>Meridian Wool Cardigan</v>
       </c>
       <c r="AH113" t="str">
-        <v>340</v>
+        <v>410</v>
       </c>
       <c r="AI113" t="str">
         <v/>
@@ -21292,16 +21292,16 @@
         <v/>
       </c>
       <c r="BF113" t="str">
-        <v>Studio Essential</v>
+        <v>Soft Structure</v>
       </c>
       <c r="BG113" t="str">
-        <v>Brushed Twill</v>
+        <v>Merino Wool</v>
       </c>
       <c r="BH113" t="str">
-        <v>Khaki trouser texture and pocket detail</v>
+        <v>Merino cardigan folded on a leather bench</v>
       </c>
       <c r="BI113" t="str">
-        <v>category:trousers|size:S|price:$150-$500</v>
+        <v>category:knitwear|size:M|price:$150-$500</v>
       </c>
     </row>
     <row r="114">
@@ -21318,7 +21318,7 @@
         <v/>
       </c>
       <c r="E114" t="str">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F114" t="str">
         <v/>
@@ -21381,7 +21381,7 @@
         <v/>
       </c>
       <c r="Z114" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDBowt2AR0QGkZ_teHLK0qG2iUl8fGSUuNTrZHreU_s95xtmrbnCTB8LYOShnHaraaNDqoUnziBnVe2Rh6OAlJpU9ZSpF84L0-k23aokXc6aJdWswRdyGowycFswnENPgO9tfnUyUaMa2VjW8lGJYkmhPbnJhSE0zC0BdoSTdae8pmGnQwaAXzVlJJRhWYysiO1yf2n_lREj8nVxarkGub1OLnfLI4QrhAiAGV-AZTWnZg1MCqdpNi1pBSjb6RIPFAzXw0h_iTQCqrp</v>
       </c>
       <c r="AA114" t="str">
         <v/>
@@ -21396,16 +21396,16 @@
         <v/>
       </c>
       <c r="AE114" t="str">
-        <v>men-007</v>
+        <v>men-009</v>
       </c>
       <c r="AF114" t="str">
         <v/>
       </c>
       <c r="AG114" t="str">
-        <v>Stonewashed Utility Overshirt</v>
+        <v>Foundry Pleat Short</v>
       </c>
       <c r="AH114" t="str">
-        <v>360</v>
+        <v>250</v>
       </c>
       <c r="AI114" t="str">
         <v/>
@@ -21477,16 +21477,16 @@
         <v/>
       </c>
       <c r="BF114" t="str">
-        <v>Workshop Layer</v>
+        <v>Warm Weather</v>
       </c>
       <c r="BG114" t="str">
-        <v>Washed Cotton Drill</v>
+        <v>Tumbled Cotton Poplin</v>
       </c>
       <c r="BH114" t="str">
-        <v>Stonewashed overshirt on a wooden hanger</v>
+        <v>Pleated cotton short with a clean hem</v>
       </c>
       <c r="BI114" t="str">
-        <v>category:shirts|size:M|price:$150-$500</v>
+        <v>category:trousers|size:S|price:$150-$500</v>
       </c>
     </row>
     <row r="115">
@@ -21503,7 +21503,7 @@
         <v/>
       </c>
       <c r="E115" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F115" t="str">
         <v/>
@@ -21566,7 +21566,7 @@
         <v/>
       </c>
       <c r="Z115" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBXRSWOWcHtCNyaMDYLCJzvRD_aYObkVBkIHPoz_HZOOuihWxPKo82MAX7anUmfBqHwOgx_6YthGokOn-aqEtAkMya3di9RNTlqqA2-zqT6x85Yh0CGWy5_gOTjOOMYxnRJ7B8A9ihZaMR-PzIAILb7T5rSMUCiZ-3CZRTX_u3XxJpOlXlYjWEZj4aFLaV_mamuWkKjkhTxSRpw7LyICx9lPITcKUuGOxJ0NkpKweDI4rMjqFkSSGZJssErigmmpbKq5Z6kLPVUehXg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</v>
       </c>
       <c r="AA115" t="str">
         <v/>
@@ -21581,16 +21581,16 @@
         <v/>
       </c>
       <c r="AE115" t="str">
-        <v>men-008</v>
+        <v>men-010</v>
       </c>
       <c r="AF115" t="str">
         <v/>
       </c>
       <c r="AG115" t="str">
-        <v>Meridian Wool Cardigan</v>
+        <v>Tailored Poplin Bandshirt</v>
       </c>
       <c r="AH115" t="str">
-        <v>410</v>
+        <v>280</v>
       </c>
       <c r="AI115" t="str">
         <v/>
@@ -21662,16 +21662,16 @@
         <v/>
       </c>
       <c r="BF115" t="str">
-        <v>Soft Structure</v>
+        <v>Shirting</v>
       </c>
       <c r="BG115" t="str">
-        <v>Merino Wool</v>
+        <v>Compact Cotton Poplin</v>
       </c>
       <c r="BH115" t="str">
-        <v>Merino cardigan folded on a leather bench</v>
+        <v>Band-collar shirt hanging in soft daylight</v>
       </c>
       <c r="BI115" t="str">
-        <v>category:knitwear|size:M|price:$150-$500</v>
+        <v>category:shirts|size:M|price:$150-$500</v>
       </c>
     </row>
     <row r="116">
@@ -21688,7 +21688,7 @@
         <v/>
       </c>
       <c r="E116" t="str">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F116" t="str">
         <v/>
@@ -21751,7 +21751,7 @@
         <v/>
       </c>
       <c r="Z116" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDBowt2AR0QGkZ_teHLK0qG2iUl8fGSUuNTrZHreU_s95xtmrbnCTB8LYOShnHaraaNDqoUnziBnVe2Rh6OAlJpU9ZSpF84L0-k23aokXc6aJdWswRdyGowycFswnENPgO9tfnUyUaMa2VjW8lGJYkmhPbnJhSE0zC0BdoSTdae8pmGnQwaAXzVlJJRhWYysiO1yf2n_lREj8nVxarkGub1OLnfLI4QrhAiAGV-AZTWnZg1MCqdpNi1pBSjb6RIPFAzXw0h_iTQCqrp</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</v>
       </c>
       <c r="AA116" t="str">
         <v/>
@@ -21766,16 +21766,16 @@
         <v/>
       </c>
       <c r="AE116" t="str">
-        <v>men-009</v>
+        <v>men-011</v>
       </c>
       <c r="AF116" t="str">
         <v/>
       </c>
       <c r="AG116" t="str">
-        <v>Foundry Pleat Short</v>
+        <v>Alpine Field Parka</v>
       </c>
       <c r="AH116" t="str">
-        <v>250</v>
+        <v>980</v>
       </c>
       <c r="AI116" t="str">
         <v/>
@@ -21847,16 +21847,16 @@
         <v/>
       </c>
       <c r="BF116" t="str">
-        <v>Warm Weather</v>
+        <v>Outerwear</v>
       </c>
       <c r="BG116" t="str">
-        <v>Tumbled Cotton Poplin</v>
+        <v>Technical Cotton Shell</v>
       </c>
       <c r="BH116" t="str">
-        <v>Pleated cotton short with a clean hem</v>
+        <v>Moss field parka styled against stone walls</v>
       </c>
       <c r="BI116" t="str">
-        <v>category:trousers|size:S|price:$150-$500</v>
+        <v>category:outerwear|size:L|price:$500-$1000</v>
       </c>
     </row>
     <row r="117">
@@ -21873,7 +21873,7 @@
         <v/>
       </c>
       <c r="E117" t="str">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F117" t="str">
         <v/>
@@ -21936,7 +21936,7 @@
         <v/>
       </c>
       <c r="Z117" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</v>
       </c>
       <c r="AA117" t="str">
         <v/>
@@ -21951,16 +21951,16 @@
         <v/>
       </c>
       <c r="AE117" t="str">
-        <v>men-010</v>
+        <v>men-012</v>
       </c>
       <c r="AF117" t="str">
         <v/>
       </c>
       <c r="AG117" t="str">
-        <v>Tailored Poplin Bandshirt</v>
+        <v>Slate Double Pleat Trouser</v>
       </c>
       <c r="AH117" t="str">
-        <v>280</v>
+        <v>390</v>
       </c>
       <c r="AI117" t="str">
         <v/>
@@ -22032,16 +22032,16 @@
         <v/>
       </c>
       <c r="BF117" t="str">
-        <v>Shirting</v>
+        <v>Tailoring</v>
       </c>
       <c r="BG117" t="str">
-        <v>Compact Cotton Poplin</v>
+        <v>Worsted Wool Blend</v>
       </c>
       <c r="BH117" t="str">
-        <v>Band-collar shirt hanging in soft daylight</v>
+        <v>Slate trouser with double pleat and pressed finish</v>
       </c>
       <c r="BI117" t="str">
-        <v>category:shirts|size:M|price:$150-$500</v>
+        <v>category:trousers|size:M|price:$150-$500</v>
       </c>
     </row>
     <row r="118">
@@ -22058,7 +22058,7 @@
         <v/>
       </c>
       <c r="E118" t="str">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F118" t="str">
         <v/>
@@ -22067,7 +22067,7 @@
         <v/>
       </c>
       <c r="H118" t="str">
-        <v>/categories/Shop%20Men</v>
+        <v>/products/550e8400-e29b-41d4-a716-446655440001</v>
       </c>
       <c r="I118" t="str">
         <v/>
@@ -22121,7 +22121,7 @@
         <v/>
       </c>
       <c r="Z118" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</v>
+        <v>https://example.com/images/sm002-s.jpg</v>
       </c>
       <c r="AA118" t="str">
         <v/>
@@ -22136,16 +22136,16 @@
         <v/>
       </c>
       <c r="AE118" t="str">
-        <v>men-011</v>
+        <v>550e8400-e29b-41d4-a716-446655440001</v>
       </c>
       <c r="AF118" t="str">
         <v/>
       </c>
       <c r="AG118" t="str">
-        <v>Alpine Field Parka</v>
+        <v>Cotton Tee</v>
       </c>
       <c r="AH118" t="str">
-        <v>980</v>
+        <v>49.99</v>
       </c>
       <c r="AI118" t="str">
         <v/>
@@ -22217,16 +22217,16 @@
         <v/>
       </c>
       <c r="BF118" t="str">
-        <v>Outerwear</v>
+        <v>Men</v>
       </c>
       <c r="BG118" t="str">
-        <v>Technical Cotton Shell</v>
+        <v>S / Navy</v>
       </c>
       <c r="BH118" t="str">
-        <v>Moss field parka styled against stone walls</v>
+        <v>Cotton Tee</v>
       </c>
       <c r="BI118" t="str">
-        <v>category:outerwear|size:L|price:$500-$1000</v>
+        <v>category:Men|size:S|color:Navy|price:$0-$150</v>
       </c>
     </row>
     <row r="119">
@@ -22243,7 +22243,7 @@
         <v/>
       </c>
       <c r="E119" t="str">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F119" t="str">
         <v/>
@@ -22252,7 +22252,7 @@
         <v/>
       </c>
       <c r="H119" t="str">
-        <v>/categories/Shop%20Men</v>
+        <v>/products/550e8400-e29b-41d4-a716-446655440000</v>
       </c>
       <c r="I119" t="str">
         <v/>
@@ -22306,7 +22306,7 @@
         <v/>
       </c>
       <c r="Z119" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</v>
+        <v>https://example.com/images/sm001-m.jpg</v>
       </c>
       <c r="AA119" t="str">
         <v/>
@@ -22321,16 +22321,16 @@
         <v/>
       </c>
       <c r="AE119" t="str">
-        <v>men-012</v>
+        <v>550e8400-e29b-41d4-a716-446655440000</v>
       </c>
       <c r="AF119" t="str">
         <v/>
       </c>
       <c r="AG119" t="str">
-        <v>Slate Double Pleat Trouser</v>
+        <v>Linen Shirt</v>
       </c>
       <c r="AH119" t="str">
-        <v>390</v>
+        <v>129.99</v>
       </c>
       <c r="AI119" t="str">
         <v/>
@@ -22402,16 +22402,16 @@
         <v/>
       </c>
       <c r="BF119" t="str">
-        <v>Tailoring</v>
+        <v>Men</v>
       </c>
       <c r="BG119" t="str">
-        <v>Worsted Wool Blend</v>
+        <v>M / White</v>
       </c>
       <c r="BH119" t="str">
-        <v>Slate trouser with double pleat and pressed finish</v>
+        <v>Linen Shirt</v>
       </c>
       <c r="BI119" t="str">
-        <v>category:trousers|size:M|price:$150-$500</v>
+        <v>category:Men|size:M|size:L|color:White|price:$0-$150</v>
       </c>
     </row>
     <row r="120">
@@ -22428,7 +22428,7 @@
         <v/>
       </c>
       <c r="E120" t="str">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F120" t="str">
         <v/>
@@ -22437,7 +22437,7 @@
         <v/>
       </c>
       <c r="H120" t="str">
-        <v>/products/550e8400-e29b-41d4-a716-446655440001</v>
+        <v>/categories/Shop%20Women</v>
       </c>
       <c r="I120" t="str">
         <v/>
@@ -22491,7 +22491,7 @@
         <v/>
       </c>
       <c r="Z120" t="str">
-        <v>https://example.com/images/sm002-s.jpg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</v>
       </c>
       <c r="AA120" t="str">
         <v/>
@@ -22506,16 +22506,16 @@
         <v/>
       </c>
       <c r="AE120" t="str">
-        <v>550e8400-e29b-41d4-a716-446655440001</v>
+        <v>women-001</v>
       </c>
       <c r="AF120" t="str">
         <v/>
       </c>
       <c r="AG120" t="str">
-        <v>Cotton Tee</v>
+        <v>Ethereal Silk Slip</v>
       </c>
       <c r="AH120" t="str">
-        <v>49.99</v>
+        <v>340</v>
       </c>
       <c r="AI120" t="str">
         <v/>
@@ -22575,7 +22575,7 @@
         <v/>
       </c>
       <c r="BB120" t="str">
-        <v>men-atelier</v>
+        <v>women-atelier</v>
       </c>
       <c r="BC120" t="str">
         <v/>
@@ -22587,16 +22587,16 @@
         <v/>
       </c>
       <c r="BF120" t="str">
-        <v>Men</v>
+        <v>New Arrival</v>
       </c>
       <c r="BG120" t="str">
-        <v>S / Navy</v>
+        <v>Mulberry Silk</v>
       </c>
       <c r="BH120" t="str">
-        <v>Cotton Tee</v>
+        <v>Model in a cream silk slip dress</v>
       </c>
       <c r="BI120" t="str">
-        <v>category:Men|size:S|color:Navy|price:$0-$150</v>
+        <v>category:dresses|size:S|palette:Cream</v>
       </c>
     </row>
     <row r="121">
@@ -22613,7 +22613,7 @@
         <v/>
       </c>
       <c r="E121" t="str">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F121" t="str">
         <v/>
@@ -22622,7 +22622,7 @@
         <v/>
       </c>
       <c r="H121" t="str">
-        <v>/products/550e8400-e29b-41d4-a716-446655440000</v>
+        <v>/categories/Shop%20Women</v>
       </c>
       <c r="I121" t="str">
         <v/>
@@ -22676,7 +22676,7 @@
         <v/>
       </c>
       <c r="Z121" t="str">
-        <v>https://example.com/images/sm001-m.jpg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAULIeOGtZd7vXZH0gSJHWiv3w1w4d6Tz7E7Y55Pp0wpbrudgRPkQEUxLNJ7z1iX2ofjNS4KSwbIFdzRgJR2rZEzslEi02TskRTUycOtweLNiBcTRv0RAiCUncTPXaXvHGzovAfwglQIxRlDavgkG0kp9z1__77ZtFulQa4AVlvR_muVhFSILTRpDDYMIgzrzsCEPjKJNyVc0k_NtV_qrK021aTU5RlI_Mg4TBu8JIzJLGkLHTEGfvWBezAYGbi6wNp_bgFRdeYEwST</v>
       </c>
       <c r="AA121" t="str">
         <v/>
@@ -22691,16 +22691,16 @@
         <v/>
       </c>
       <c r="AE121" t="str">
-        <v>550e8400-e29b-41d4-a716-446655440000</v>
+        <v>women-004</v>
       </c>
       <c r="AF121" t="str">
         <v/>
       </c>
       <c r="AG121" t="str">
-        <v>Linen Shirt</v>
+        <v>Sculptural Pleated Skirt</v>
       </c>
       <c r="AH121" t="str">
-        <v>129.99</v>
+        <v>490</v>
       </c>
       <c r="AI121" t="str">
         <v/>
@@ -22760,7 +22760,7 @@
         <v/>
       </c>
       <c r="BB121" t="str">
-        <v>men-atelier</v>
+        <v>women-atelier</v>
       </c>
       <c r="BC121" t="str">
         <v/>
@@ -22772,16 +22772,16 @@
         <v/>
       </c>
       <c r="BF121" t="str">
-        <v>Men</v>
+        <v>Bottoms</v>
       </c>
       <c r="BG121" t="str">
-        <v>M / White</v>
+        <v>Pleated Wool Crepe</v>
       </c>
       <c r="BH121" t="str">
-        <v>Linen Shirt</v>
+        <v>Pleated charcoal skirt in motion through concrete architecture</v>
       </c>
       <c r="BI121" t="str">
-        <v>category:Men|size:M|size:L|color:White|price:$0-$150</v>
+        <v>category:bottoms|size:S|palette:Charcoal</v>
       </c>
     </row>
     <row r="122">
@@ -22798,7 +22798,7 @@
         <v/>
       </c>
       <c r="E122" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F122" t="str">
         <v/>
@@ -22861,7 +22861,7 @@
         <v/>
       </c>
       <c r="Z122" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</v>
       </c>
       <c r="AA122" t="str">
         <v/>
@@ -22876,16 +22876,16 @@
         <v/>
       </c>
       <c r="AE122" t="str">
-        <v>women-001</v>
+        <v>women-005</v>
       </c>
       <c r="AF122" t="str">
         <v/>
       </c>
       <c r="AG122" t="str">
-        <v>Ethereal Silk Slip</v>
+        <v>Hearth Tapered Pant</v>
       </c>
       <c r="AH122" t="str">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AI122" t="str">
         <v/>
@@ -22957,16 +22957,16 @@
         <v/>
       </c>
       <c r="BF122" t="str">
-        <v>New Arrival</v>
+        <v>Bottoms</v>
       </c>
       <c r="BG122" t="str">
-        <v>Mulberry Silk</v>
+        <v>Brushed Wool Blend</v>
       </c>
       <c r="BH122" t="str">
-        <v>Model in a cream silk slip dress</v>
+        <v>High-end trouser detail in soft terracotta</v>
       </c>
       <c r="BI122" t="str">
-        <v>category:dresses|size:S|palette:Cream</v>
+        <v>category:bottoms|size:M|palette:Charcoal</v>
       </c>
     </row>
     <row r="123">
@@ -22983,7 +22983,7 @@
         <v/>
       </c>
       <c r="E123" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F123" t="str">
         <v/>
@@ -23046,7 +23046,7 @@
         <v/>
       </c>
       <c r="Z123" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAULIeOGtZd7vXZH0gSJHWiv3w1w4d6Tz7E7Y55Pp0wpbrudgRPkQEUxLNJ7z1iX2ofjNS4KSwbIFdzRgJR2rZEzslEi02TskRTUycOtweLNiBcTRv0RAiCUncTPXaXvHGzovAfwglQIxRlDavgkG0kp9z1__77ZtFulQa4AVlvR_muVhFSILTRpDDYMIgzrzsCEPjKJNyVc0k_NtV_qrK021aTU5RlI_Mg4TBu8JIzJLGkLHTEGfvWBezAYGbi6wNp_bgFRdeYEwST</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</v>
       </c>
       <c r="AA123" t="str">
         <v/>
@@ -23061,16 +23061,16 @@
         <v/>
       </c>
       <c r="AE123" t="str">
-        <v>women-004</v>
+        <v>women-006</v>
       </c>
       <c r="AF123" t="str">
         <v/>
       </c>
       <c r="AG123" t="str">
-        <v>Sculptural Pleated Skirt</v>
+        <v>Atelier Formal Blazer</v>
       </c>
       <c r="AH123" t="str">
-        <v>490</v>
+        <v>850</v>
       </c>
       <c r="AI123" t="str">
         <v/>
@@ -23142,16 +23142,16 @@
         <v/>
       </c>
       <c r="BF123" t="str">
-        <v>Bottoms</v>
+        <v>Outerwear</v>
       </c>
       <c r="BG123" t="str">
-        <v>Pleated Wool Crepe</v>
+        <v>Tailored Wool Blend</v>
       </c>
       <c r="BH123" t="str">
-        <v>Pleated charcoal skirt in motion through concrete architecture</v>
+        <v>Structured blazer in forest green with atelier styling</v>
       </c>
       <c r="BI123" t="str">
-        <v>category:bottoms|size:S|palette:Charcoal</v>
+        <v>category:outerwear|size:L|palette:Forest</v>
       </c>
     </row>
     <row r="124">
@@ -23168,7 +23168,7 @@
         <v/>
       </c>
       <c r="E124" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F124" t="str">
         <v/>
@@ -23231,7 +23231,7 @@
         <v/>
       </c>
       <c r="Z124" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</v>
       </c>
       <c r="AA124" t="str">
         <v/>
@@ -23246,16 +23246,16 @@
         <v/>
       </c>
       <c r="AE124" t="str">
-        <v>women-005</v>
+        <v>women-007</v>
       </c>
       <c r="AF124" t="str">
         <v/>
       </c>
       <c r="AG124" t="str">
-        <v>Hearth Tapered Pant</v>
+        <v>Botanical Wrap Dress</v>
       </c>
       <c r="AH124" t="str">
-        <v>320</v>
+        <v>410</v>
       </c>
       <c r="AI124" t="str">
         <v/>
@@ -23327,16 +23327,16 @@
         <v/>
       </c>
       <c r="BF124" t="str">
-        <v>Bottoms</v>
+        <v>Draped</v>
       </c>
       <c r="BG124" t="str">
-        <v>Brushed Wool Blend</v>
+        <v>Washed Silk Blend</v>
       </c>
       <c r="BH124" t="str">
-        <v>High-end trouser detail in soft terracotta</v>
+        <v>Wrap dress draped beside a window in soft daylight</v>
       </c>
       <c r="BI124" t="str">
-        <v>category:bottoms|size:M|palette:Charcoal</v>
+        <v>category:dresses|size:S|palette:Cream</v>
       </c>
     </row>
     <row r="125">
@@ -23353,7 +23353,7 @@
         <v/>
       </c>
       <c r="E125" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F125" t="str">
         <v/>
@@ -23416,7 +23416,7 @@
         <v/>
       </c>
       <c r="Z125" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBEKFEZ7Xk7Fyqc9Uf8Rr7JfhPIghhY7j0HO6bqSglckdRAUU1XFK1Vy_uPXAbpLqczXmCH41FFfT4QIgBtt7oBHhaEojRqYoMhEeW0zN9yDlgFxnnAhZfa_FjmfnZNakXUp-HAT6D2gb_BUeHA5TXBmMVsObd_AHQfOwPuMZTKrAqSkXnJe60KUnlOWajJ6btQ5zyNadwls33tVZNcDlHyJ8_EUlUAhHRtQ90ZhEzMNN5Mzjf_Hr7Onn7MZF-hkz45XkPrdm6pngSw</v>
       </c>
       <c r="AA125" t="str">
         <v/>
@@ -23431,16 +23431,16 @@
         <v/>
       </c>
       <c r="AE125" t="str">
-        <v>women-006</v>
+        <v>women-008</v>
       </c>
       <c r="AF125" t="str">
         <v/>
       </c>
       <c r="AG125" t="str">
-        <v>Atelier Formal Blazer</v>
+        <v>Gallery Satin Blouse</v>
       </c>
       <c r="AH125" t="str">
-        <v>850</v>
+        <v>295</v>
       </c>
       <c r="AI125" t="str">
         <v/>
@@ -23512,16 +23512,16 @@
         <v/>
       </c>
       <c r="BF125" t="str">
-        <v>Outerwear</v>
+        <v>Studio Essential</v>
       </c>
       <c r="BG125" t="str">
-        <v>Tailored Wool Blend</v>
+        <v>Liquid Satin</v>
       </c>
       <c r="BH125" t="str">
-        <v>Structured blazer in forest green with atelier styling</v>
+        <v>Stone satin blouse folded on a soft boucle chair</v>
       </c>
       <c r="BI125" t="str">
-        <v>category:outerwear|size:L|palette:Forest</v>
+        <v>category:tops|size:S|palette:Stone</v>
       </c>
     </row>
     <row r="126">
@@ -23538,7 +23538,7 @@
         <v/>
       </c>
       <c r="E126" t="str">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F126" t="str">
         <v/>
@@ -23601,7 +23601,7 @@
         <v/>
       </c>
       <c r="Z126" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAULIeOGtZd7vXZH0gSJHWiv3w1w4d6Tz7E7Y55Pp0wpbrudgRPkQEUxLNJ7z1iX2ofjNS4KSwbIFdzRgJR2rZEzslEi02TskRTUycOtweLNiBcTRv0RAiCUncTPXaXvHGzovAfwglQIxRlDavgkG0kp9z1__77ZtFulQa4AVlvR_muVhFSILTRpDDYMIgzrzsCEPjKJNyVc0k_NtV_qrK021aTU5RlI_Mg4TBu8JIzJLGkLHTEGfvWBezAYGbi6wNp_bgFRdeYEwST</v>
       </c>
       <c r="AA126" t="str">
         <v/>
@@ -23616,16 +23616,16 @@
         <v/>
       </c>
       <c r="AE126" t="str">
-        <v>women-007</v>
+        <v>women-009</v>
       </c>
       <c r="AF126" t="str">
         <v/>
       </c>
       <c r="AG126" t="str">
-        <v>Botanical Wrap Dress</v>
+        <v>Quiet Wool Column Coat</v>
       </c>
       <c r="AH126" t="str">
-        <v>410</v>
+        <v>1180</v>
       </c>
       <c r="AI126" t="str">
         <v/>
@@ -23697,16 +23697,16 @@
         <v/>
       </c>
       <c r="BF126" t="str">
-        <v>Draped</v>
+        <v>Editorial Pick</v>
       </c>
       <c r="BG126" t="str">
-        <v>Washed Silk Blend</v>
+        <v>Double-Faced Wool</v>
       </c>
       <c r="BH126" t="str">
-        <v>Wrap dress draped beside a window in soft daylight</v>
+        <v>Long wool column coat against a pale gallery wall</v>
       </c>
       <c r="BI126" t="str">
-        <v>category:dresses|size:S|palette:Cream</v>
+        <v>category:outerwear|size:M|palette:Forest</v>
       </c>
     </row>
     <row r="127">
@@ -23723,7 +23723,7 @@
         <v/>
       </c>
       <c r="E127" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F127" t="str">
         <v/>
@@ -23786,7 +23786,7 @@
         <v/>
       </c>
       <c r="Z127" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBEKFEZ7Xk7Fyqc9Uf8Rr7JfhPIghhY7j0HO6bqSglckdRAUU1XFK1Vy_uPXAbpLqczXmCH41FFfT4QIgBtt7oBHhaEojRqYoMhEeW0zN9yDlgFxnnAhZfa_FjmfnZNakXUp-HAT6D2gb_BUeHA5TXBmMVsObd_AHQfOwPuMZTKrAqSkXnJe60KUnlOWajJ6btQ5zyNadwls33tVZNcDlHyJ8_EUlUAhHRtQ90ZhEzMNN5Mzjf_Hr7Onn7MZF-hkz45XkPrdm6pngSw</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</v>
       </c>
       <c r="AA127" t="str">
         <v/>
@@ -23801,16 +23801,16 @@
         <v/>
       </c>
       <c r="AE127" t="str">
-        <v>women-008</v>
+        <v>women-010</v>
       </c>
       <c r="AF127" t="str">
         <v/>
       </c>
       <c r="AG127" t="str">
-        <v>Gallery Satin Blouse</v>
+        <v>Soft Structure Trouser</v>
       </c>
       <c r="AH127" t="str">
-        <v>295</v>
+        <v>365</v>
       </c>
       <c r="AI127" t="str">
         <v/>
@@ -23882,16 +23882,16 @@
         <v/>
       </c>
       <c r="BF127" t="str">
-        <v>Studio Essential</v>
+        <v>Tailored Bottoms</v>
       </c>
       <c r="BG127" t="str">
-        <v>Liquid Satin</v>
+        <v>Compact Viscose Twill</v>
       </c>
       <c r="BH127" t="str">
-        <v>Stone satin blouse folded on a soft boucle chair</v>
+        <v>Tailored trouser displayed with a clean crease and sculpted drape</v>
       </c>
       <c r="BI127" t="str">
-        <v>category:tops|size:S|palette:Stone</v>
+        <v>category:bottoms|size:M|palette:Charcoal</v>
       </c>
     </row>
     <row r="128">
@@ -23908,7 +23908,7 @@
         <v/>
       </c>
       <c r="E128" t="str">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F128" t="str">
         <v/>
@@ -23971,7 +23971,7 @@
         <v/>
       </c>
       <c r="Z128" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAULIeOGtZd7vXZH0gSJHWiv3w1w4d6Tz7E7Y55Pp0wpbrudgRPkQEUxLNJ7z1iX2ofjNS4KSwbIFdzRgJR2rZEzslEi02TskRTUycOtweLNiBcTRv0RAiCUncTPXaXvHGzovAfwglQIxRlDavgkG0kp9z1__77ZtFulQa4AVlvR_muVhFSILTRpDDYMIgzrzsCEPjKJNyVc0k_NtV_qrK021aTU5RlI_Mg4TBu8JIzJLGkLHTEGfvWBezAYGbi6wNp_bgFRdeYEwST</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</v>
       </c>
       <c r="AA128" t="str">
         <v/>
@@ -23986,16 +23986,16 @@
         <v/>
       </c>
       <c r="AE128" t="str">
-        <v>women-009</v>
+        <v>women-011</v>
       </c>
       <c r="AF128" t="str">
         <v/>
       </c>
       <c r="AG128" t="str">
-        <v>Quiet Wool Column Coat</v>
+        <v>Moonstone Rib Tank</v>
       </c>
       <c r="AH128" t="str">
-        <v>1180</v>
+        <v>180</v>
       </c>
       <c r="AI128" t="str">
         <v/>
@@ -24067,16 +24067,16 @@
         <v/>
       </c>
       <c r="BF128" t="str">
-        <v>Editorial Pick</v>
+        <v>Layering</v>
       </c>
       <c r="BG128" t="str">
-        <v>Double-Faced Wool</v>
+        <v>Fine Rib Cotton</v>
       </c>
       <c r="BH128" t="str">
-        <v>Long wool column coat against a pale gallery wall</v>
+        <v>Cream rib tank styled with a tonal blazer</v>
       </c>
       <c r="BI128" t="str">
-        <v>category:outerwear|size:M|palette:Forest</v>
+        <v>category:tops|size:XS|palette:Cream</v>
       </c>
     </row>
     <row r="129">
@@ -24093,7 +24093,7 @@
         <v/>
       </c>
       <c r="E129" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F129" t="str">
         <v/>
@@ -24156,7 +24156,7 @@
         <v/>
       </c>
       <c r="Z129" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</v>
       </c>
       <c r="AA129" t="str">
         <v/>
@@ -24171,16 +24171,16 @@
         <v/>
       </c>
       <c r="AE129" t="str">
-        <v>women-010</v>
+        <v>women-012</v>
       </c>
       <c r="AF129" t="str">
         <v/>
       </c>
       <c r="AG129" t="str">
-        <v>Soft Structure Trouser</v>
+        <v>Atelier Bias Midi Skirt</v>
       </c>
       <c r="AH129" t="str">
-        <v>365</v>
+        <v>430</v>
       </c>
       <c r="AI129" t="str">
         <v/>
@@ -24252,16 +24252,16 @@
         <v/>
       </c>
       <c r="BF129" t="str">
-        <v>Tailored Bottoms</v>
+        <v>Fluid Line</v>
       </c>
       <c r="BG129" t="str">
-        <v>Compact Viscose Twill</v>
+        <v>Washed Satin</v>
       </c>
       <c r="BH129" t="str">
-        <v>Tailored trouser displayed with a clean crease and sculpted drape</v>
+        <v>Bias midi skirt arranged in a softly lit studio</v>
       </c>
       <c r="BI129" t="str">
-        <v>category:bottoms|size:M|palette:Charcoal</v>
+        <v>category:bottoms|size:S|palette:Stone</v>
       </c>
     </row>
     <row r="130">
@@ -24278,7 +24278,7 @@
         <v/>
       </c>
       <c r="E130" t="str">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F130" t="str">
         <v/>
@@ -24287,7 +24287,7 @@
         <v/>
       </c>
       <c r="H130" t="str">
-        <v>/categories/Shop%20Women</v>
+        <v>/products/550e8400-e29b-41d4-a716-446655440002</v>
       </c>
       <c r="I130" t="str">
         <v/>
@@ -24341,7 +24341,7 @@
         <v/>
       </c>
       <c r="Z130" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</v>
+        <v/>
       </c>
       <c r="AA130" t="str">
         <v/>
@@ -24356,16 +24356,16 @@
         <v/>
       </c>
       <c r="AE130" t="str">
-        <v>women-011</v>
+        <v>550e8400-e29b-41d4-a716-446655440002</v>
       </c>
       <c r="AF130" t="str">
         <v/>
       </c>
       <c r="AG130" t="str">
-        <v>Moonstone Rib Tank</v>
+        <v>Silk Dress</v>
       </c>
       <c r="AH130" t="str">
-        <v>180</v>
+        <v>229</v>
       </c>
       <c r="AI130" t="str">
         <v/>
@@ -24437,16 +24437,16 @@
         <v/>
       </c>
       <c r="BF130" t="str">
-        <v>Layering</v>
+        <v>Women</v>
       </c>
       <c r="BG130" t="str">
-        <v>Fine Rib Cotton</v>
+        <v>Women</v>
       </c>
       <c r="BH130" t="str">
-        <v>Cream rib tank styled with a tonal blazer</v>
+        <v>Silk Dress</v>
       </c>
       <c r="BI130" t="str">
-        <v>category:tops|size:XS|palette:Cream</v>
+        <v>category:Women|price:$150-$500</v>
       </c>
     </row>
     <row r="131">
@@ -24463,7 +24463,7 @@
         <v/>
       </c>
       <c r="E131" t="str">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F131" t="str">
         <v/>
@@ -24472,7 +24472,7 @@
         <v/>
       </c>
       <c r="H131" t="str">
-        <v>/categories/Shop%20Women</v>
+        <v>/products/10000000-0000-4000-8000-000000000014</v>
       </c>
       <c r="I131" t="str">
         <v/>
@@ -24541,16 +24541,16 @@
         <v/>
       </c>
       <c r="AE131" t="str">
-        <v>women-012</v>
+        <v>10000000-0000-4000-8000-000000000014</v>
       </c>
       <c r="AF131" t="str">
         <v/>
       </c>
       <c r="AG131" t="str">
-        <v>Atelier Bias Midi Skirt</v>
+        <v>Architectural Overcoat</v>
       </c>
       <c r="AH131" t="str">
-        <v>430</v>
+        <v>1250</v>
       </c>
       <c r="AI131" t="str">
         <v/>
@@ -24622,16 +24622,16 @@
         <v/>
       </c>
       <c r="BF131" t="str">
-        <v>Fluid Line</v>
+        <v>Limited</v>
       </c>
       <c r="BG131" t="str">
-        <v>Washed Satin</v>
+        <v>M / Forest</v>
       </c>
       <c r="BH131" t="str">
-        <v>Bias midi skirt arranged in a softly lit studio</v>
+        <v>Architectural Overcoat</v>
       </c>
       <c r="BI131" t="str">
-        <v>category:bottoms|size:S|palette:Stone</v>
+        <v>category:Women|size:M|size:L|color:Forest|price:$1000+</v>
       </c>
     </row>
     <row r="132">
@@ -24648,7 +24648,7 @@
         <v/>
       </c>
       <c r="E132" t="str">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F132" t="str">
         <v/>
@@ -24657,7 +24657,7 @@
         <v/>
       </c>
       <c r="H132" t="str">
-        <v>/products/550e8400-e29b-41d4-a716-446655440002</v>
+        <v>/products/10000000-0000-4000-8000-000000000015</v>
       </c>
       <c r="I132" t="str">
         <v/>
@@ -24711,7 +24711,7 @@
         <v/>
       </c>
       <c r="Z132" t="str">
-        <v/>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBEKFEZ7Xk7Fyqc9Uf8Rr7JfhPIghhY7j0HO6bqSglckdRAUU1XFK1Vy_uPXAbpLqczXmCH41FFfT4QIgBtt7oBHhaEojRqYoMhEeW0zN9yDlgFxnnAhZfa_FjmfnZNakXUp-HAT6D2gb_BUeHA5TXBmMVsObd_AHQfOwPuMZTKrAqSkXnJe60KUnlOWajJ6btQ5zyNadwls33tVZNcDlHyJ8_EUlUAhHRtQ90ZhEzMNN5Mzjf_Hr7Onn7MZF-hkz45XkPrdm6pngSw</v>
       </c>
       <c r="AA132" t="str">
         <v/>
@@ -24726,16 +24726,16 @@
         <v/>
       </c>
       <c r="AE132" t="str">
-        <v>550e8400-e29b-41d4-a716-446655440002</v>
+        <v>10000000-0000-4000-8000-000000000015</v>
       </c>
       <c r="AF132" t="str">
         <v/>
       </c>
       <c r="AG132" t="str">
-        <v>Silk Dress</v>
+        <v>Cloud Cashmere Crew</v>
       </c>
       <c r="AH132" t="str">
-        <v>229</v>
+        <v>280</v>
       </c>
       <c r="AI132" t="str">
         <v/>
@@ -24807,16 +24807,16 @@
         <v/>
       </c>
       <c r="BF132" t="str">
-        <v>Women</v>
+        <v>Knitwear</v>
       </c>
       <c r="BG132" t="str">
-        <v>Women</v>
+        <v>M / Stone</v>
       </c>
       <c r="BH132" t="str">
-        <v>Silk Dress</v>
+        <v>Cloud Cashmere Crew</v>
       </c>
       <c r="BI132" t="str">
-        <v>category:Women|price:$150-$500</v>
+        <v>category:Women|size:M|size:L|color:Stone|price:$150-$500</v>
       </c>
     </row>
     <row r="133">
@@ -24833,7 +24833,7 @@
         <v/>
       </c>
       <c r="E133" t="str">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F133" t="str">
         <v/>
@@ -24842,7 +24842,7 @@
         <v/>
       </c>
       <c r="H133" t="str">
-        <v>/products/10000000-0000-4000-8000-000000000014</v>
+        <v>/categories/Footwear</v>
       </c>
       <c r="I133" t="str">
         <v/>
@@ -24896,7 +24896,7 @@
         <v/>
       </c>
       <c r="Z133" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</v>
       </c>
       <c r="AA133" t="str">
         <v/>
@@ -24911,16 +24911,16 @@
         <v/>
       </c>
       <c r="AE133" t="str">
-        <v>10000000-0000-4000-8000-000000000014</v>
+        <v>footwear-001</v>
       </c>
       <c r="AF133" t="str">
         <v/>
       </c>
       <c r="AG133" t="str">
-        <v>Architectural Overcoat</v>
+        <v>Atelier Low Sneaker</v>
       </c>
       <c r="AH133" t="str">
-        <v>1250</v>
+        <v>340</v>
       </c>
       <c r="AI133" t="str">
         <v/>
@@ -24980,7 +24980,7 @@
         <v/>
       </c>
       <c r="BB133" t="str">
-        <v>women-atelier</v>
+        <v>footwear-atelier</v>
       </c>
       <c r="BC133" t="str">
         <v/>
@@ -24992,16 +24992,16 @@
         <v/>
       </c>
       <c r="BF133" t="str">
-        <v>Limited</v>
+        <v>New Arrival</v>
       </c>
       <c r="BG133" t="str">
-        <v>M / Forest</v>
+        <v>Smooth Italian Calfskin</v>
       </c>
       <c r="BH133" t="str">
-        <v>Architectural Overcoat</v>
+        <v>Minimalist white leather sneaker on an architectural background</v>
       </c>
       <c r="BI133" t="str">
-        <v>category:Women|size:M|size:L|color:Forest|price:$1000+</v>
+        <v>type:Sneakers|size:41|material:Calfskin</v>
       </c>
     </row>
     <row r="134">
@@ -25018,7 +25018,7 @@
         <v/>
       </c>
       <c r="E134" t="str">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F134" t="str">
         <v/>
@@ -25027,7 +25027,7 @@
         <v/>
       </c>
       <c r="H134" t="str">
-        <v>/products/10000000-0000-4000-8000-000000000015</v>
+        <v>/categories/Footwear</v>
       </c>
       <c r="I134" t="str">
         <v/>
@@ -25081,7 +25081,7 @@
         <v/>
       </c>
       <c r="Z134" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBEKFEZ7Xk7Fyqc9Uf8Rr7JfhPIghhY7j0HO6bqSglckdRAUU1XFK1Vy_uPXAbpLqczXmCH41FFfT4QIgBtt7oBHhaEojRqYoMhEeW0zN9yDlgFxnnAhZfa_FjmfnZNakXUp-HAT6D2gb_BUeHA5TXBmMVsObd_AHQfOwPuMZTKrAqSkXnJe60KUnlOWajJ6btQ5zyNadwls33tVZNcDlHyJ8_EUlUAhHRtQ90ZhEzMNN5Mzjf_Hr7Onn7MZF-hkz45XkPrdm6pngSw</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</v>
       </c>
       <c r="AA134" t="str">
         <v/>
@@ -25096,16 +25096,16 @@
         <v/>
       </c>
       <c r="AE134" t="str">
-        <v>10000000-0000-4000-8000-000000000015</v>
+        <v>footwear-002</v>
       </c>
       <c r="AF134" t="str">
         <v/>
       </c>
       <c r="AG134" t="str">
-        <v>Cloud Cashmere Crew</v>
+        <v>Chelsea Field Boot</v>
       </c>
       <c r="AH134" t="str">
-        <v>280</v>
+        <v>495</v>
       </c>
       <c r="AI134" t="str">
         <v/>
@@ -25165,7 +25165,7 @@
         <v/>
       </c>
       <c r="BB134" t="str">
-        <v>women-atelier</v>
+        <v>footwear-atelier</v>
       </c>
       <c r="BC134" t="str">
         <v/>
@@ -25177,16 +25177,16 @@
         <v/>
       </c>
       <c r="BF134" t="str">
-        <v>Knitwear</v>
+        <v>Handcrafted</v>
       </c>
       <c r="BG134" t="str">
-        <v>M / Stone</v>
+        <v>Waxed Roughout Leather</v>
       </c>
       <c r="BH134" t="str">
-        <v>Cloud Cashmere Crew</v>
+        <v>Dark brown leather chelsea boot with polished finish</v>
       </c>
       <c r="BI134" t="str">
-        <v>category:Women|size:M|size:L|color:Stone|price:$150-$500</v>
+        <v>type:Boots|size:42|material:Suede</v>
       </c>
     </row>
     <row r="135">
@@ -25203,7 +25203,7 @@
         <v/>
       </c>
       <c r="E135" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F135" t="str">
         <v/>
@@ -25266,7 +25266,7 @@
         <v/>
       </c>
       <c r="Z135" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</v>
       </c>
       <c r="AA135" t="str">
         <v/>
@@ -25281,16 +25281,16 @@
         <v/>
       </c>
       <c r="AE135" t="str">
-        <v>footwear-001</v>
+        <v>footwear-003</v>
       </c>
       <c r="AF135" t="str">
         <v/>
       </c>
       <c r="AG135" t="str">
-        <v>Atelier Low Sneaker</v>
+        <v>Classic Penny Loafer</v>
       </c>
       <c r="AH135" t="str">
-        <v>340</v>
+        <v>420</v>
       </c>
       <c r="AI135" t="str">
         <v/>
@@ -25362,16 +25362,16 @@
         <v/>
       </c>
       <c r="BF135" t="str">
-        <v>New Arrival</v>
+        <v>Studio Classic</v>
       </c>
       <c r="BG135" t="str">
-        <v>Smooth Italian Calfskin</v>
+        <v>Pebbled Grain Leather</v>
       </c>
       <c r="BH135" t="str">
-        <v>Minimalist white leather sneaker on an architectural background</v>
+        <v>Classic black penny loafer with minimalist buckle detail</v>
       </c>
       <c r="BI135" t="str">
-        <v>type:Sneakers|size:41|material:Calfskin</v>
+        <v>type:Loafers|size:40|material:Grain Leather</v>
       </c>
     </row>
     <row r="136">
@@ -25388,7 +25388,7 @@
         <v/>
       </c>
       <c r="E136" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F136" t="str">
         <v/>
@@ -25451,7 +25451,7 @@
         <v/>
       </c>
       <c r="Z136" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</v>
       </c>
       <c r="AA136" t="str">
         <v/>
@@ -25466,16 +25466,16 @@
         <v/>
       </c>
       <c r="AE136" t="str">
-        <v>footwear-002</v>
+        <v>footwear-004</v>
       </c>
       <c r="AF136" t="str">
         <v/>
       </c>
       <c r="AG136" t="str">
-        <v>Chelsea Field Boot</v>
+        <v>Moc Toe Service Boot</v>
       </c>
       <c r="AH136" t="str">
-        <v>495</v>
+        <v>560</v>
       </c>
       <c r="AI136" t="str">
         <v/>
@@ -25547,16 +25547,16 @@
         <v/>
       </c>
       <c r="BF136" t="str">
-        <v>Handcrafted</v>
+        <v>Workshop Build</v>
       </c>
       <c r="BG136" t="str">
-        <v>Waxed Roughout Leather</v>
+        <v>English Bridle Leather</v>
       </c>
       <c r="BH136" t="str">
-        <v>Dark brown leather chelsea boot with polished finish</v>
+        <v>High-top service boot in tobacco tan with premium hardware</v>
       </c>
       <c r="BI136" t="str">
-        <v>type:Boots|size:42|material:Suede</v>
+        <v>type:Boots|size:43|material:Bridle Leather</v>
       </c>
     </row>
     <row r="137">
@@ -25573,7 +25573,7 @@
         <v/>
       </c>
       <c r="E137" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F137" t="str">
         <v/>
@@ -25636,7 +25636,7 @@
         <v/>
       </c>
       <c r="Z137" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</v>
       </c>
       <c r="AA137" t="str">
         <v/>
@@ -25651,16 +25651,16 @@
         <v/>
       </c>
       <c r="AE137" t="str">
-        <v>footwear-003</v>
+        <v>footwear-005</v>
       </c>
       <c r="AF137" t="str">
         <v/>
       </c>
       <c r="AG137" t="str">
-        <v>Classic Penny Loafer</v>
+        <v>Ridge Runner Hiker</v>
       </c>
       <c r="AH137" t="str">
-        <v>420</v>
+        <v>610</v>
       </c>
       <c r="AI137" t="str">
         <v/>
@@ -25732,16 +25732,16 @@
         <v/>
       </c>
       <c r="BF137" t="str">
-        <v>Studio Classic</v>
+        <v>Trail Spec</v>
       </c>
       <c r="BG137" t="str">
-        <v>Pebbled Grain Leather</v>
+        <v>Stormwelt Bridle Leather</v>
       </c>
       <c r="BH137" t="str">
-        <v>Classic black penny loafer with minimalist buckle detail</v>
+        <v>Leather hiker boot styled on a stone ledge</v>
       </c>
       <c r="BI137" t="str">
-        <v>type:Loafers|size:40|material:Grain Leather</v>
+        <v>type:Boots|size:42|material:Bridle Leather</v>
       </c>
     </row>
     <row r="138">
@@ -25758,7 +25758,7 @@
         <v/>
       </c>
       <c r="E138" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F138" t="str">
         <v/>
@@ -25821,7 +25821,7 @@
         <v/>
       </c>
       <c r="Z138" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</v>
       </c>
       <c r="AA138" t="str">
         <v/>
@@ -25836,16 +25836,16 @@
         <v/>
       </c>
       <c r="AE138" t="str">
-        <v>footwear-004</v>
+        <v>footwear-006</v>
       </c>
       <c r="AF138" t="str">
         <v/>
       </c>
       <c r="AG138" t="str">
-        <v>Moc Toe Service Boot</v>
+        <v>Polished Derby Loafer</v>
       </c>
       <c r="AH138" t="str">
-        <v>560</v>
+        <v>450</v>
       </c>
       <c r="AI138" t="str">
         <v/>
@@ -25917,16 +25917,16 @@
         <v/>
       </c>
       <c r="BF138" t="str">
-        <v>Workshop Build</v>
+        <v>Hybrid Formal</v>
       </c>
       <c r="BG138" t="str">
-        <v>English Bridle Leather</v>
+        <v>Polished Grain Leather</v>
       </c>
       <c r="BH138" t="str">
-        <v>High-top service boot in tobacco tan with premium hardware</v>
+        <v>Polished derby-loafer hybrid with deep espresso shine</v>
       </c>
       <c r="BI138" t="str">
-        <v>type:Boots|size:43|material:Bridle Leather</v>
+        <v>type:Loafers|size:41|material:Grain Leather</v>
       </c>
     </row>
     <row r="139">
@@ -25943,7 +25943,7 @@
         <v/>
       </c>
       <c r="E139" t="str">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F139" t="str">
         <v/>
@@ -26006,7 +26006,7 @@
         <v/>
       </c>
       <c r="Z139" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</v>
       </c>
       <c r="AA139" t="str">
         <v/>
@@ -26021,16 +26021,16 @@
         <v/>
       </c>
       <c r="AE139" t="str">
-        <v>footwear-005</v>
+        <v>footwear-007</v>
       </c>
       <c r="AF139" t="str">
         <v/>
       </c>
       <c r="AG139" t="str">
-        <v>Ridge Runner Hiker</v>
+        <v>Slate Suede Desert Boot</v>
       </c>
       <c r="AH139" t="str">
-        <v>610</v>
+        <v>470</v>
       </c>
       <c r="AI139" t="str">
         <v/>
@@ -26102,16 +26102,16 @@
         <v/>
       </c>
       <c r="BF139" t="str">
-        <v>Trail Spec</v>
+        <v>Soft Utility</v>
       </c>
       <c r="BG139" t="str">
-        <v>Stormwelt Bridle Leather</v>
+        <v>Premium Suede</v>
       </c>
       <c r="BH139" t="str">
-        <v>Leather hiker boot styled on a stone ledge</v>
+        <v>Slate suede desert boot with tonal laces</v>
       </c>
       <c r="BI139" t="str">
-        <v>type:Boots|size:42|material:Bridle Leather</v>
+        <v>type:Boots|size:41|material:Suede</v>
       </c>
     </row>
     <row r="140">
@@ -26128,7 +26128,7 @@
         <v/>
       </c>
       <c r="E140" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F140" t="str">
         <v/>
@@ -26191,7 +26191,7 @@
         <v/>
       </c>
       <c r="Z140" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</v>
       </c>
       <c r="AA140" t="str">
         <v/>
@@ -26206,16 +26206,16 @@
         <v/>
       </c>
       <c r="AE140" t="str">
-        <v>footwear-006</v>
+        <v>footwear-008</v>
       </c>
       <c r="AF140" t="str">
         <v/>
       </c>
       <c r="AG140" t="str">
-        <v>Polished Derby Loafer</v>
+        <v>Court Leather Trainer</v>
       </c>
       <c r="AH140" t="str">
-        <v>450</v>
+        <v>360</v>
       </c>
       <c r="AI140" t="str">
         <v/>
@@ -26287,16 +26287,16 @@
         <v/>
       </c>
       <c r="BF140" t="str">
-        <v>Hybrid Formal</v>
+        <v>Everyday</v>
       </c>
       <c r="BG140" t="str">
-        <v>Polished Grain Leather</v>
+        <v>Full-Grain Calfskin</v>
       </c>
       <c r="BH140" t="str">
-        <v>Polished derby-loafer hybrid with deep espresso shine</v>
+        <v>Low-profile leather trainer set against pale concrete</v>
       </c>
       <c r="BI140" t="str">
-        <v>type:Loafers|size:41|material:Grain Leather</v>
+        <v>type:Sneakers|size:40|material:Calfskin</v>
       </c>
     </row>
     <row r="141">
@@ -26313,7 +26313,7 @@
         <v/>
       </c>
       <c r="E141" t="str">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F141" t="str">
         <v/>
@@ -26376,7 +26376,7 @@
         <v/>
       </c>
       <c r="Z141" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</v>
       </c>
       <c r="AA141" t="str">
         <v/>
@@ -26391,16 +26391,16 @@
         <v/>
       </c>
       <c r="AE141" t="str">
-        <v>footwear-007</v>
+        <v>footwear-009</v>
       </c>
       <c r="AF141" t="str">
         <v/>
       </c>
       <c r="AG141" t="str">
-        <v>Slate Suede Desert Boot</v>
+        <v>Artisan Monk Strap</v>
       </c>
       <c r="AH141" t="str">
-        <v>470</v>
+        <v>530</v>
       </c>
       <c r="AI141" t="str">
         <v/>
@@ -26472,16 +26472,16 @@
         <v/>
       </c>
       <c r="BF141" t="str">
-        <v>Soft Utility</v>
+        <v>Dress Line</v>
       </c>
       <c r="BG141" t="str">
-        <v>Premium Suede</v>
+        <v>Hand-Burnished Grain Leather</v>
       </c>
       <c r="BH141" t="str">
-        <v>Slate suede desert boot with tonal laces</v>
+        <v>Monk strap shoe with hand-burnished leather and metal buckle</v>
       </c>
       <c r="BI141" t="str">
-        <v>type:Boots|size:41|material:Suede</v>
+        <v>type:Loafers|size:41|material:Grain Leather</v>
       </c>
     </row>
     <row r="142">
@@ -26498,7 +26498,7 @@
         <v/>
       </c>
       <c r="E142" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F142" t="str">
         <v/>
@@ -26561,7 +26561,7 @@
         <v/>
       </c>
       <c r="Z142" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</v>
       </c>
       <c r="AA142" t="str">
         <v/>
@@ -26576,16 +26576,16 @@
         <v/>
       </c>
       <c r="AE142" t="str">
-        <v>footwear-008</v>
+        <v>footwear-010</v>
       </c>
       <c r="AF142" t="str">
         <v/>
       </c>
       <c r="AG142" t="str">
-        <v>Court Leather Trainer</v>
+        <v>Pebble Driving Loafer</v>
       </c>
       <c r="AH142" t="str">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="AI142" t="str">
         <v/>
@@ -26657,16 +26657,16 @@
         <v/>
       </c>
       <c r="BF142" t="str">
-        <v>Everyday</v>
+        <v>Soft Moc</v>
       </c>
       <c r="BG142" t="str">
-        <v>Full-Grain Calfskin</v>
+        <v>Pebbled Grain Leather</v>
       </c>
       <c r="BH142" t="str">
-        <v>Low-profile leather trainer set against pale concrete</v>
+        <v>Pebbled leather driving loafer on a textured stone plinth</v>
       </c>
       <c r="BI142" t="str">
-        <v>type:Sneakers|size:40|material:Calfskin</v>
+        <v>type:Loafers|size:40|material:Grain Leather</v>
       </c>
     </row>
     <row r="143">
@@ -26683,7 +26683,7 @@
         <v/>
       </c>
       <c r="E143" t="str">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F143" t="str">
         <v/>
@@ -26746,7 +26746,7 @@
         <v/>
       </c>
       <c r="Z143" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</v>
       </c>
       <c r="AA143" t="str">
         <v/>
@@ -26761,16 +26761,16 @@
         <v/>
       </c>
       <c r="AE143" t="str">
-        <v>footwear-009</v>
+        <v>footwear-011</v>
       </c>
       <c r="AF143" t="str">
         <v/>
       </c>
       <c r="AG143" t="str">
-        <v>Artisan Monk Strap</v>
+        <v>Harbor Fisher Sandal</v>
       </c>
       <c r="AH143" t="str">
-        <v>530</v>
+        <v>310</v>
       </c>
       <c r="AI143" t="str">
         <v/>
@@ -26842,16 +26842,16 @@
         <v/>
       </c>
       <c r="BF143" t="str">
-        <v>Dress Line</v>
+        <v>Warm Season</v>
       </c>
       <c r="BG143" t="str">
-        <v>Hand-Burnished Grain Leather</v>
+        <v>Matte Calfskin</v>
       </c>
       <c r="BH143" t="str">
-        <v>Monk strap shoe with hand-burnished leather and metal buckle</v>
+        <v>Minimal leather fisher sandal with matte finish</v>
       </c>
       <c r="BI143" t="str">
-        <v>type:Loafers|size:41|material:Grain Leather</v>
+        <v>type:Sandals|size:39|material:Calfskin</v>
       </c>
     </row>
     <row r="144">
@@ -26868,7 +26868,7 @@
         <v/>
       </c>
       <c r="E144" t="str">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F144" t="str">
         <v/>
@@ -26931,7 +26931,7 @@
         <v/>
       </c>
       <c r="Z144" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</v>
       </c>
       <c r="AA144" t="str">
         <v/>
@@ -26946,16 +26946,16 @@
         <v/>
       </c>
       <c r="AE144" t="str">
-        <v>footwear-010</v>
+        <v>footwear-012</v>
       </c>
       <c r="AF144" t="str">
         <v/>
       </c>
       <c r="AG144" t="str">
-        <v>Pebble Driving Loafer</v>
+        <v>Iron Commute Boot</v>
       </c>
       <c r="AH144" t="str">
-        <v>390</v>
+        <v>580</v>
       </c>
       <c r="AI144" t="str">
         <v/>
@@ -27027,16 +27027,16 @@
         <v/>
       </c>
       <c r="BF144" t="str">
-        <v>Soft Moc</v>
+        <v>City Build</v>
       </c>
       <c r="BG144" t="str">
-        <v>Pebbled Grain Leather</v>
+        <v>Weatherproof Bridle Leather</v>
       </c>
       <c r="BH144" t="str">
-        <v>Pebbled leather driving loafer on a textured stone plinth</v>
+        <v>City-ready leather boot with sturdy outsole and matte finish</v>
       </c>
       <c r="BI144" t="str">
-        <v>type:Loafers|size:40|material:Grain Leather</v>
+        <v>type:Boots|size:42|material:Bridle Leather</v>
       </c>
     </row>
     <row r="145">
@@ -27053,7 +27053,7 @@
         <v/>
       </c>
       <c r="E145" t="str">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F145" t="str">
         <v/>
@@ -27062,7 +27062,7 @@
         <v/>
       </c>
       <c r="H145" t="str">
-        <v>/categories/Footwear</v>
+        <v>/categories/Accessories</v>
       </c>
       <c r="I145" t="str">
         <v/>
@@ -27116,7 +27116,7 @@
         <v/>
       </c>
       <c r="Z145" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
       </c>
       <c r="AA145" t="str">
         <v/>
@@ -27131,16 +27131,16 @@
         <v/>
       </c>
       <c r="AE145" t="str">
-        <v>footwear-011</v>
+        <v>accessories-001</v>
       </c>
       <c r="AF145" t="str">
         <v/>
       </c>
       <c r="AG145" t="str">
-        <v>Harbor Fisher Sandal</v>
+        <v>Atelier Tote</v>
       </c>
       <c r="AH145" t="str">
-        <v>310</v>
+        <v>840</v>
       </c>
       <c r="AI145" t="str">
         <v/>
@@ -27200,7 +27200,7 @@
         <v/>
       </c>
       <c r="BB145" t="str">
-        <v>footwear-atelier</v>
+        <v>accessories-atelier</v>
       </c>
       <c r="BC145" t="str">
         <v/>
@@ -27212,16 +27212,16 @@
         <v/>
       </c>
       <c r="BF145" t="str">
-        <v>Warm Season</v>
+        <v>Limited Edition</v>
       </c>
       <c r="BG145" t="str">
-        <v>Matte Calfskin</v>
+        <v>Vegetable Tanned Leather</v>
       </c>
       <c r="BH145" t="str">
-        <v>Minimal leather fisher sandal with matte finish</v>
+        <v>Minimalist leather tote in deep forest green</v>
       </c>
       <c r="BI145" t="str">
-        <v>type:Sandals|size:39|material:Calfskin</v>
+        <v>category:Bags|material:Vachetta</v>
       </c>
     </row>
     <row r="146">
@@ -27238,7 +27238,7 @@
         <v/>
       </c>
       <c r="E146" t="str">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F146" t="str">
         <v/>
@@ -27247,7 +27247,7 @@
         <v/>
       </c>
       <c r="H146" t="str">
-        <v>/categories/Footwear</v>
+        <v>/categories/Accessories</v>
       </c>
       <c r="I146" t="str">
         <v/>
@@ -27301,7 +27301,7 @@
         <v/>
       </c>
       <c r="Z146" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
       </c>
       <c r="AA146" t="str">
         <v/>
@@ -27316,16 +27316,16 @@
         <v/>
       </c>
       <c r="AE146" t="str">
-        <v>footwear-012</v>
+        <v>accessories-002</v>
       </c>
       <c r="AF146" t="str">
         <v/>
       </c>
       <c r="AG146" t="str">
-        <v>Iron Commute Boot</v>
+        <v>Aurora Wrap</v>
       </c>
       <c r="AH146" t="str">
-        <v>580</v>
+        <v>215</v>
       </c>
       <c r="AI146" t="str">
         <v/>
@@ -27385,7 +27385,7 @@
         <v/>
       </c>
       <c r="BB146" t="str">
-        <v>footwear-atelier</v>
+        <v>accessories-atelier</v>
       </c>
       <c r="BC146" t="str">
         <v/>
@@ -27397,16 +27397,16 @@
         <v/>
       </c>
       <c r="BF146" t="str">
-        <v>City Build</v>
+        <v>Essential</v>
       </c>
       <c r="BG146" t="str">
-        <v>Weatherproof Bridle Leather</v>
+        <v>Organic Raw Silk</v>
       </c>
       <c r="BH146" t="str">
-        <v>City-ready leather boot with sturdy outsole and matte finish</v>
+        <v>Artisanal silk scarf draped over a wooden chair</v>
       </c>
       <c r="BI146" t="str">
-        <v>type:Boots|size:42|material:Bridle Leather</v>
+        <v>category:Scarves|material:Raw Silk</v>
       </c>
     </row>
     <row r="147">
@@ -27423,7 +27423,7 @@
         <v/>
       </c>
       <c r="E147" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F147" t="str">
         <v/>
@@ -27486,7 +27486,7 @@
         <v/>
       </c>
       <c r="Z147" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDclyoI7lW_Aez2lBayMz4ES5BVdH-wo43IL4ZwpD4HLQkaJqfV3eDM-qMUs4V8Uyl6BTZ9FSNg7ExFisE6J-TMxcflCy5mFritcP54bDT49eqwGnwGnsOeheOgbCmpdtfGvnHaqpfmRpU4zQvBD7B4tmigGgv7hCDEHWLojIzOlAfe5p-0cCnzLjktClPIw5lG6h2qfT0buVNcsY57FFriSrjdMpV_jPcwn3Dwsz1C-8IS20dhOYE1-Kak6Hi0R-OiEeULdIqMBj2c</v>
       </c>
       <c r="AA147" t="str">
         <v/>
@@ -27501,16 +27501,16 @@
         <v/>
       </c>
       <c r="AE147" t="str">
-        <v>accessories-001</v>
+        <v>accessories-003</v>
       </c>
       <c r="AF147" t="str">
         <v/>
       </c>
       <c r="AG147" t="str">
-        <v>Atelier Tote</v>
+        <v>Cintura Belt</v>
       </c>
       <c r="AH147" t="str">
-        <v>840</v>
+        <v>165</v>
       </c>
       <c r="AI147" t="str">
         <v/>
@@ -27582,16 +27582,16 @@
         <v/>
       </c>
       <c r="BF147" t="str">
-        <v>Limited Edition</v>
+        <v>Leather Detail</v>
       </c>
       <c r="BG147" t="str">
-        <v>Vegetable Tanned Leather</v>
+        <v>Full Grain Saddle Leather</v>
       </c>
       <c r="BH147" t="str">
-        <v>Minimalist leather tote in deep forest green</v>
+        <v>Classic leather belt with brass buckle</v>
       </c>
       <c r="BI147" t="str">
-        <v>category:Bags|material:Vachetta</v>
+        <v>category:Belts|material:Vachetta</v>
       </c>
     </row>
     <row r="148">
@@ -27608,7 +27608,7 @@
         <v/>
       </c>
       <c r="E148" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F148" t="str">
         <v/>
@@ -27671,7 +27671,7 @@
         <v/>
       </c>
       <c r="Z148" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAc-xgefZmjRHW4tYawNPs3ljWfgQ66YMBuFgX39XflOo-rQyjbJ2Ju2V0nLkyj2SVuz2BKsp1ucM74P4Gg2Q-TiJKsqrjsQRpxYORvaVExN0KFMkAU9KQFmWEmtNZHK5dm7iBBb1zYMTsluHO4Em5IwIi3lS3JGSUeU_unqmYgh-Fw65tcUaH2Ywxl8ag7h1znu1rGefQrkuDTARLHNwtQdpiGPKWCCp8JpO_yLO4kKGzLmwj8g3VfRzxs02GzkmBt2St6l1zyFYZU</v>
       </c>
       <c r="AA148" t="str">
         <v/>
@@ -27686,16 +27686,16 @@
         <v/>
       </c>
       <c r="AE148" t="str">
-        <v>accessories-002</v>
+        <v>accessories-004</v>
       </c>
       <c r="AF148" t="str">
         <v/>
       </c>
       <c r="AG148" t="str">
-        <v>Aurora Wrap</v>
+        <v>Vault Clutch</v>
       </c>
       <c r="AH148" t="str">
-        <v>215</v>
+        <v>420</v>
       </c>
       <c r="AI148" t="str">
         <v/>
@@ -27767,16 +27767,16 @@
         <v/>
       </c>
       <c r="BF148" t="str">
-        <v>Essential</v>
+        <v>Leather Detail</v>
       </c>
       <c r="BG148" t="str">
-        <v>Organic Raw Silk</v>
+        <v>Nappa Leather</v>
       </c>
       <c r="BH148" t="str">
-        <v>Artisanal silk scarf draped over a wooden chair</v>
+        <v>Sculptural leather clutch in warm cognac tone</v>
       </c>
       <c r="BI148" t="str">
-        <v>category:Scarves|material:Raw Silk</v>
+        <v>category:Bags|material:Nappa Leather</v>
       </c>
     </row>
     <row r="149">
@@ -27793,7 +27793,7 @@
         <v/>
       </c>
       <c r="E149" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F149" t="str">
         <v/>
@@ -27856,7 +27856,7 @@
         <v/>
       </c>
       <c r="Z149" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDclyoI7lW_Aez2lBayMz4ES5BVdH-wo43IL4ZwpD4HLQkaJqfV3eDM-qMUs4V8Uyl6BTZ9FSNg7ExFisE6J-TMxcflCy5mFritcP54bDT49eqwGnwGnsOeheOgbCmpdtfGvnHaqpfmRpU4zQvBD7B4tmigGgv7hCDEHWLojIzOlAfe5p-0cCnzLjktClPIw5lG6h2qfT0buVNcsY57FFriSrjdMpV_jPcwn3Dwsz1C-8IS20dhOYE1-Kak6Hi0R-OiEeULdIqMBj2c</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDwib-yVKWuTMsi4heheiLMLuw3Aukcrj4t8F5TLsWcUDULrkliTF_b5hFcyekqcaoBOrRCOob6yU3tV5aJCQChHBAggBedojt1THWZ_F-1GiBclBPJw389BrO0MvSA5xrOo1ssievm9rXO2UiIT0Ix_tHvr6rnGAPSAVNt1DYmLJVg_7vuvdan2zI6d3Z7JsuFwAqcipqjdi0FbCpFwqD4d7bZrq5JeL4i4aGx5NsOkOBZScx3UPHkR_rmJldHJi3Cb4MoiZaIoNsN</v>
       </c>
       <c r="AA149" t="str">
         <v/>
@@ -27871,16 +27871,16 @@
         <v/>
       </c>
       <c r="AE149" t="str">
-        <v>accessories-003</v>
+        <v>accessories-005</v>
       </c>
       <c r="AF149" t="str">
         <v/>
       </c>
       <c r="AG149" t="str">
-        <v>Cintura Belt</v>
+        <v>Obsidian Band</v>
       </c>
       <c r="AH149" t="str">
-        <v>165</v>
+        <v>310</v>
       </c>
       <c r="AI149" t="str">
         <v/>
@@ -27952,16 +27952,16 @@
         <v/>
       </c>
       <c r="BF149" t="str">
-        <v>Leather Detail</v>
+        <v>Limited Edition</v>
       </c>
       <c r="BG149" t="str">
-        <v>Full Grain Saddle Leather</v>
+        <v>925 Sterling Silver</v>
       </c>
       <c r="BH149" t="str">
-        <v>Classic leather belt with brass buckle</v>
+        <v>Hand-hammered sterling silver ring on dark stone</v>
       </c>
       <c r="BI149" t="str">
-        <v>category:Belts|material:Vachetta</v>
+        <v>category:Jewelry|material:Sterling Silver</v>
       </c>
     </row>
     <row r="150">
@@ -27978,7 +27978,7 @@
         <v/>
       </c>
       <c r="E150" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F150" t="str">
         <v/>
@@ -28041,7 +28041,7 @@
         <v/>
       </c>
       <c r="Z150" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAc-xgefZmjRHW4tYawNPs3ljWfgQ66YMBuFgX39XflOo-rQyjbJ2Ju2V0nLkyj2SVuz2BKsp1ucM74P4Gg2Q-TiJKsqrjsQRpxYORvaVExN0KFMkAU9KQFmWEmtNZHK5dm7iBBb1zYMTsluHO4Em5IwIi3lS3JGSUeU_unqmYgh-Fw65tcUaH2Ywxl8ag7h1znu1rGefQrkuDTARLHNwtQdpiGPKWCCp8JpO_yLO4kKGzLmwj8g3VfRzxs02GzkmBt2St6l1zyFYZU</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
       </c>
       <c r="AA150" t="str">
         <v/>
@@ -28056,16 +28056,16 @@
         <v/>
       </c>
       <c r="AE150" t="str">
-        <v>accessories-004</v>
+        <v>accessories-006</v>
       </c>
       <c r="AF150" t="str">
         <v/>
       </c>
       <c r="AG150" t="str">
-        <v>Vault Clutch</v>
+        <v>Mist Scarf</v>
       </c>
       <c r="AH150" t="str">
-        <v>420</v>
+        <v>190</v>
       </c>
       <c r="AI150" t="str">
         <v/>
@@ -28137,16 +28137,16 @@
         <v/>
       </c>
       <c r="BF150" t="str">
-        <v>Leather Detail</v>
+        <v>Soft Finish</v>
       </c>
       <c r="BG150" t="str">
-        <v>Nappa Leather</v>
+        <v>Cashmere Blend</v>
       </c>
       <c r="BH150" t="str">
-        <v>Sculptural leather clutch in warm cognac tone</v>
+        <v>Monochromatic scarf with delicate fringe detail</v>
       </c>
       <c r="BI150" t="str">
-        <v>category:Bags|material:Nappa Leather</v>
+        <v>category:Scarves|material:Cashmere</v>
       </c>
     </row>
     <row r="151">
@@ -28163,7 +28163,7 @@
         <v/>
       </c>
       <c r="E151" t="str">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F151" t="str">
         <v/>
@@ -28226,7 +28226,7 @@
         <v/>
       </c>
       <c r="Z151" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDwib-yVKWuTMsi4heheiLMLuw3Aukcrj4t8F5TLsWcUDULrkliTF_b5hFcyekqcaoBOrRCOob6yU3tV5aJCQChHBAggBedojt1THWZ_F-1GiBclBPJw389BrO0MvSA5xrOo1ssievm9rXO2UiIT0Ix_tHvr6rnGAPSAVNt1DYmLJVg_7vuvdan2zI6d3Z7JsuFwAqcipqjdi0FbCpFwqD4d7bZrq5JeL4i4aGx5NsOkOBZScx3UPHkR_rmJldHJi3Cb4MoiZaIoNsN</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
       </c>
       <c r="AA151" t="str">
         <v/>
@@ -28241,16 +28241,16 @@
         <v/>
       </c>
       <c r="AE151" t="str">
-        <v>accessories-005</v>
+        <v>accessories-007</v>
       </c>
       <c r="AF151" t="str">
         <v/>
       </c>
       <c r="AG151" t="str">
-        <v>Obsidian Band</v>
+        <v>Meridian Weekender</v>
       </c>
       <c r="AH151" t="str">
-        <v>310</v>
+        <v>980</v>
       </c>
       <c r="AI151" t="str">
         <v/>
@@ -28322,16 +28322,16 @@
         <v/>
       </c>
       <c r="BF151" t="str">
-        <v>Limited Edition</v>
+        <v>Travel Object</v>
       </c>
       <c r="BG151" t="str">
-        <v>925 Sterling Silver</v>
+        <v>Vachetta Leather</v>
       </c>
       <c r="BH151" t="str">
-        <v>Hand-hammered sterling silver ring on dark stone</v>
+        <v>Leather weekender bag with rolled handles and matte hardware</v>
       </c>
       <c r="BI151" t="str">
-        <v>category:Jewelry|material:Sterling Silver</v>
+        <v>category:Bags|material:Vachetta</v>
       </c>
     </row>
     <row r="152">
@@ -28348,7 +28348,7 @@
         <v/>
       </c>
       <c r="E152" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F152" t="str">
         <v/>
@@ -28411,7 +28411,7 @@
         <v/>
       </c>
       <c r="Z152" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDclyoI7lW_Aez2lBayMz4ES5BVdH-wo43IL4ZwpD4HLQkaJqfV3eDM-qMUs4V8Uyl6BTZ9FSNg7ExFisE6J-TMxcflCy5mFritcP54bDT49eqwGnwGnsOeheOgbCmpdtfGvnHaqpfmRpU4zQvBD7B4tmigGgv7hCDEHWLojIzOlAfe5p-0cCnzLjktClPIw5lG6h2qfT0buVNcsY57FFriSrjdMpV_jPcwn3Dwsz1C-8IS20dhOYE1-Kak6Hi0R-OiEeULdIqMBj2c</v>
       </c>
       <c r="AA152" t="str">
         <v/>
@@ -28426,16 +28426,16 @@
         <v/>
       </c>
       <c r="AE152" t="str">
-        <v>accessories-006</v>
+        <v>accessories-008</v>
       </c>
       <c r="AF152" t="str">
         <v/>
       </c>
       <c r="AG152" t="str">
-        <v>Mist Scarf</v>
+        <v>Sculptor Card Holder</v>
       </c>
       <c r="AH152" t="str">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="AI152" t="str">
         <v/>
@@ -28507,16 +28507,16 @@
         <v/>
       </c>
       <c r="BF152" t="str">
-        <v>Soft Finish</v>
+        <v>Daily Carry</v>
       </c>
       <c r="BG152" t="str">
-        <v>Cashmere Blend</v>
+        <v>Vachetta Leather</v>
       </c>
       <c r="BH152" t="str">
-        <v>Monochromatic scarf with delicate fringe detail</v>
+        <v>Compact leather card holder resting on textured stone</v>
       </c>
       <c r="BI152" t="str">
-        <v>category:Scarves|material:Cashmere</v>
+        <v>category:Bags|material:Vachetta</v>
       </c>
     </row>
     <row r="153">
@@ -28533,7 +28533,7 @@
         <v/>
       </c>
       <c r="E153" t="str">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F153" t="str">
         <v/>
@@ -28596,7 +28596,7 @@
         <v/>
       </c>
       <c r="Z153" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAc-xgefZmjRHW4tYawNPs3ljWfgQ66YMBuFgX39XflOo-rQyjbJ2Ju2V0nLkyj2SVuz2BKsp1ucM74P4Gg2Q-TiJKsqrjsQRpxYORvaVExN0KFMkAU9KQFmWEmtNZHK5dm7iBBb1zYMTsluHO4Em5IwIi3lS3JGSUeU_unqmYgh-Fw65tcUaH2Ywxl8ag7h1znu1rGefQrkuDTARLHNwtQdpiGPKWCCp8JpO_yLO4kKGzLmwj8g3VfRzxs02GzkmBt2St6l1zyFYZU</v>
       </c>
       <c r="AA153" t="str">
         <v/>
@@ -28611,16 +28611,16 @@
         <v/>
       </c>
       <c r="AE153" t="str">
-        <v>accessories-007</v>
+        <v>accessories-009</v>
       </c>
       <c r="AF153" t="str">
         <v/>
       </c>
       <c r="AG153" t="str">
-        <v>Meridian Weekender</v>
+        <v>Studio Key Lanyard</v>
       </c>
       <c r="AH153" t="str">
-        <v>980</v>
+        <v>110</v>
       </c>
       <c r="AI153" t="str">
         <v/>
@@ -28692,16 +28692,16 @@
         <v/>
       </c>
       <c r="BF153" t="str">
-        <v>Travel Object</v>
+        <v>Utility Detail</v>
       </c>
       <c r="BG153" t="str">
-        <v>Vachetta Leather</v>
+        <v>Bridle Leather</v>
       </c>
       <c r="BH153" t="str">
-        <v>Leather weekender bag with rolled handles and matte hardware</v>
+        <v>Leather key lanyard draped across a pale wooden table</v>
       </c>
       <c r="BI153" t="str">
-        <v>category:Bags|material:Vachetta</v>
+        <v>category:All Objects|material:Vachetta</v>
       </c>
     </row>
     <row r="154">
@@ -28718,7 +28718,7 @@
         <v/>
       </c>
       <c r="E154" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F154" t="str">
         <v/>
@@ -28781,7 +28781,7 @@
         <v/>
       </c>
       <c r="Z154" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDclyoI7lW_Aez2lBayMz4ES5BVdH-wo43IL4ZwpD4HLQkaJqfV3eDM-qMUs4V8Uyl6BTZ9FSNg7ExFisE6J-TMxcflCy5mFritcP54bDT49eqwGnwGnsOeheOgbCmpdtfGvnHaqpfmRpU4zQvBD7B4tmigGgv7hCDEHWLojIzOlAfe5p-0cCnzLjktClPIw5lG6h2qfT0buVNcsY57FFriSrjdMpV_jPcwn3Dwsz1C-8IS20dhOYE1-Kak6Hi0R-OiEeULdIqMBj2c</v>
+        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDwib-yVKWuTMsi4heheiLMLuw3Aukcrj4t8F5TLsWcUDULrkliTF_b5hFcyekqcaoBOrRCOob6yU3tV5aJCQChHBAggBedojt1THWZ_F-1GiBclBPJw389BrO0MvSA5xrOo1ssievm9rXO2UiIT0Ix_tHvr6rnGAPSAVNt1DYmLJVg_7vuvdan2zI6d3Z7JsuFwAqcipqjdi0FbCpFwqD4d7bZrq5JeL4i4aGx5NsOkOBZScx3UPHkR_rmJldHJi3Cb4MoiZaIoNsN</v>
       </c>
       <c r="AA154" t="str">
         <v/>
@@ -28796,16 +28796,16 @@
         <v/>
       </c>
       <c r="AE154" t="str">
-        <v>accessories-008</v>
+        <v>accessories-010</v>
       </c>
       <c r="AF154" t="str">
         <v/>
       </c>
       <c r="AG154" t="str">
-        <v>Sculptor Card Holder</v>
+        <v>Veil Silk Neckerchief</v>
       </c>
       <c r="AH154" t="str">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="AI154" t="str">
         <v/>
@@ -28877,761 +28877,21 @@
         <v/>
       </c>
       <c r="BF154" t="str">
-        <v>Daily Carry</v>
+        <v>Silk Accent</v>
       </c>
       <c r="BG154" t="str">
-        <v>Vachetta Leather</v>
+        <v>Printed Raw Silk</v>
       </c>
       <c r="BH154" t="str">
-        <v>Compact leather card holder resting on textured stone</v>
+        <v>Silk neckerchief arranged beside a polished leather bag</v>
       </c>
       <c r="BI154" t="str">
-        <v>category:Bags|material:Vachetta</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="str">
-        <v>category_page_product</v>
-      </c>
-      <c r="B155" t="str">
-        <v/>
-      </c>
-      <c r="C155" t="str">
-        <v/>
-      </c>
-      <c r="D155" t="str">
-        <v/>
-      </c>
-      <c r="E155" t="str">
-        <v>9</v>
-      </c>
-      <c r="F155" t="str">
-        <v/>
-      </c>
-      <c r="G155" t="str">
-        <v/>
-      </c>
-      <c r="H155" t="str">
-        <v>/categories/Accessories</v>
-      </c>
-      <c r="I155" t="str">
-        <v/>
-      </c>
-      <c r="J155" t="str">
-        <v/>
-      </c>
-      <c r="K155" t="str">
-        <v/>
-      </c>
-      <c r="L155" t="str">
-        <v/>
-      </c>
-      <c r="M155" t="str">
-        <v/>
-      </c>
-      <c r="N155" t="str">
-        <v/>
-      </c>
-      <c r="O155" t="str">
-        <v/>
-      </c>
-      <c r="P155" t="str">
-        <v/>
-      </c>
-      <c r="Q155" t="str">
-        <v/>
-      </c>
-      <c r="R155" t="str">
-        <v/>
-      </c>
-      <c r="S155" t="str">
-        <v/>
-      </c>
-      <c r="T155" t="str">
-        <v/>
-      </c>
-      <c r="U155" t="str">
-        <v/>
-      </c>
-      <c r="V155" t="str">
-        <v/>
-      </c>
-      <c r="W155" t="str">
-        <v/>
-      </c>
-      <c r="X155" t="str">
-        <v/>
-      </c>
-      <c r="Y155" t="str">
-        <v/>
-      </c>
-      <c r="Z155" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuAc-xgefZmjRHW4tYawNPs3ljWfgQ66YMBuFgX39XflOo-rQyjbJ2Ju2V0nLkyj2SVuz2BKsp1ucM74P4Gg2Q-TiJKsqrjsQRpxYORvaVExN0KFMkAU9KQFmWEmtNZHK5dm7iBBb1zYMTsluHO4Em5IwIi3lS3JGSUeU_unqmYgh-Fw65tcUaH2Ywxl8ag7h1znu1rGefQrkuDTARLHNwtQdpiGPKWCCp8JpO_yLO4kKGzLmwj8g3VfRzxs02GzkmBt2St6l1zyFYZU</v>
-      </c>
-      <c r="AA155" t="str">
-        <v/>
-      </c>
-      <c r="AB155" t="str">
-        <v/>
-      </c>
-      <c r="AC155" t="str">
-        <v/>
-      </c>
-      <c r="AD155" t="str">
-        <v/>
-      </c>
-      <c r="AE155" t="str">
-        <v>accessories-009</v>
-      </c>
-      <c r="AF155" t="str">
-        <v/>
-      </c>
-      <c r="AG155" t="str">
-        <v>Studio Key Lanyard</v>
-      </c>
-      <c r="AH155" t="str">
-        <v>110</v>
-      </c>
-      <c r="AI155" t="str">
-        <v/>
-      </c>
-      <c r="AJ155" t="str">
-        <v/>
-      </c>
-      <c r="AK155" t="str">
-        <v/>
-      </c>
-      <c r="AL155" t="str">
-        <v/>
-      </c>
-      <c r="AM155" t="str">
-        <v/>
-      </c>
-      <c r="AN155" t="str">
-        <v/>
-      </c>
-      <c r="AO155" t="str">
-        <v/>
-      </c>
-      <c r="AP155" t="str">
-        <v/>
-      </c>
-      <c r="AQ155" t="str">
-        <v/>
-      </c>
-      <c r="AR155" t="str">
-        <v/>
-      </c>
-      <c r="AS155" t="str">
-        <v/>
-      </c>
-      <c r="AT155" t="str">
-        <v/>
-      </c>
-      <c r="AU155" t="str">
-        <v/>
-      </c>
-      <c r="AV155" t="str">
-        <v/>
-      </c>
-      <c r="AW155" t="str">
-        <v/>
-      </c>
-      <c r="AX155" t="str">
-        <v/>
-      </c>
-      <c r="AY155" t="str">
-        <v/>
-      </c>
-      <c r="AZ155" t="str">
-        <v/>
-      </c>
-      <c r="BA155" t="str">
-        <v/>
-      </c>
-      <c r="BB155" t="str">
-        <v>accessories-atelier</v>
-      </c>
-      <c r="BC155" t="str">
-        <v/>
-      </c>
-      <c r="BD155" t="str">
-        <v/>
-      </c>
-      <c r="BE155" t="str">
-        <v/>
-      </c>
-      <c r="BF155" t="str">
-        <v>Utility Detail</v>
-      </c>
-      <c r="BG155" t="str">
-        <v>Bridle Leather</v>
-      </c>
-      <c r="BH155" t="str">
-        <v>Leather key lanyard draped across a pale wooden table</v>
-      </c>
-      <c r="BI155" t="str">
-        <v>category:All Objects|material:Vachetta</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="str">
-        <v>category_page_product</v>
-      </c>
-      <c r="B156" t="str">
-        <v/>
-      </c>
-      <c r="C156" t="str">
-        <v/>
-      </c>
-      <c r="D156" t="str">
-        <v/>
-      </c>
-      <c r="E156" t="str">
-        <v>10</v>
-      </c>
-      <c r="F156" t="str">
-        <v/>
-      </c>
-      <c r="G156" t="str">
-        <v/>
-      </c>
-      <c r="H156" t="str">
-        <v>/categories/Accessories</v>
-      </c>
-      <c r="I156" t="str">
-        <v/>
-      </c>
-      <c r="J156" t="str">
-        <v/>
-      </c>
-      <c r="K156" t="str">
-        <v/>
-      </c>
-      <c r="L156" t="str">
-        <v/>
-      </c>
-      <c r="M156" t="str">
-        <v/>
-      </c>
-      <c r="N156" t="str">
-        <v/>
-      </c>
-      <c r="O156" t="str">
-        <v/>
-      </c>
-      <c r="P156" t="str">
-        <v/>
-      </c>
-      <c r="Q156" t="str">
-        <v/>
-      </c>
-      <c r="R156" t="str">
-        <v/>
-      </c>
-      <c r="S156" t="str">
-        <v/>
-      </c>
-      <c r="T156" t="str">
-        <v/>
-      </c>
-      <c r="U156" t="str">
-        <v/>
-      </c>
-      <c r="V156" t="str">
-        <v/>
-      </c>
-      <c r="W156" t="str">
-        <v/>
-      </c>
-      <c r="X156" t="str">
-        <v/>
-      </c>
-      <c r="Y156" t="str">
-        <v/>
-      </c>
-      <c r="Z156" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuDwib-yVKWuTMsi4heheiLMLuw3Aukcrj4t8F5TLsWcUDULrkliTF_b5hFcyekqcaoBOrRCOob6yU3tV5aJCQChHBAggBedojt1THWZ_F-1GiBclBPJw389BrO0MvSA5xrOo1ssievm9rXO2UiIT0Ix_tHvr6rnGAPSAVNt1DYmLJVg_7vuvdan2zI6d3Z7JsuFwAqcipqjdi0FbCpFwqD4d7bZrq5JeL4i4aGx5NsOkOBZScx3UPHkR_rmJldHJi3Cb4MoiZaIoNsN</v>
-      </c>
-      <c r="AA156" t="str">
-        <v/>
-      </c>
-      <c r="AB156" t="str">
-        <v/>
-      </c>
-      <c r="AC156" t="str">
-        <v/>
-      </c>
-      <c r="AD156" t="str">
-        <v/>
-      </c>
-      <c r="AE156" t="str">
-        <v>accessories-010</v>
-      </c>
-      <c r="AF156" t="str">
-        <v/>
-      </c>
-      <c r="AG156" t="str">
-        <v>Veil Silk Neckerchief</v>
-      </c>
-      <c r="AH156" t="str">
-        <v>175</v>
-      </c>
-      <c r="AI156" t="str">
-        <v/>
-      </c>
-      <c r="AJ156" t="str">
-        <v/>
-      </c>
-      <c r="AK156" t="str">
-        <v/>
-      </c>
-      <c r="AL156" t="str">
-        <v/>
-      </c>
-      <c r="AM156" t="str">
-        <v/>
-      </c>
-      <c r="AN156" t="str">
-        <v/>
-      </c>
-      <c r="AO156" t="str">
-        <v/>
-      </c>
-      <c r="AP156" t="str">
-        <v/>
-      </c>
-      <c r="AQ156" t="str">
-        <v/>
-      </c>
-      <c r="AR156" t="str">
-        <v/>
-      </c>
-      <c r="AS156" t="str">
-        <v/>
-      </c>
-      <c r="AT156" t="str">
-        <v/>
-      </c>
-      <c r="AU156" t="str">
-        <v/>
-      </c>
-      <c r="AV156" t="str">
-        <v/>
-      </c>
-      <c r="AW156" t="str">
-        <v/>
-      </c>
-      <c r="AX156" t="str">
-        <v/>
-      </c>
-      <c r="AY156" t="str">
-        <v/>
-      </c>
-      <c r="AZ156" t="str">
-        <v/>
-      </c>
-      <c r="BA156" t="str">
-        <v/>
-      </c>
-      <c r="BB156" t="str">
-        <v>accessories-atelier</v>
-      </c>
-      <c r="BC156" t="str">
-        <v/>
-      </c>
-      <c r="BD156" t="str">
-        <v/>
-      </c>
-      <c r="BE156" t="str">
-        <v/>
-      </c>
-      <c r="BF156" t="str">
-        <v>Silk Accent</v>
-      </c>
-      <c r="BG156" t="str">
-        <v>Printed Raw Silk</v>
-      </c>
-      <c r="BH156" t="str">
-        <v>Silk neckerchief arranged beside a polished leather bag</v>
-      </c>
-      <c r="BI156" t="str">
         <v>category:Scarves|material:Raw Silk</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="str">
-        <v>category_page_product</v>
-      </c>
-      <c r="B157" t="str">
-        <v/>
-      </c>
-      <c r="C157" t="str">
-        <v/>
-      </c>
-      <c r="D157" t="str">
-        <v/>
-      </c>
-      <c r="E157" t="str">
-        <v>11</v>
-      </c>
-      <c r="F157" t="str">
-        <v/>
-      </c>
-      <c r="G157" t="str">
-        <v/>
-      </c>
-      <c r="H157" t="str">
-        <v>/categories/Accessories</v>
-      </c>
-      <c r="I157" t="str">
-        <v/>
-      </c>
-      <c r="J157" t="str">
-        <v/>
-      </c>
-      <c r="K157" t="str">
-        <v/>
-      </c>
-      <c r="L157" t="str">
-        <v/>
-      </c>
-      <c r="M157" t="str">
-        <v/>
-      </c>
-      <c r="N157" t="str">
-        <v/>
-      </c>
-      <c r="O157" t="str">
-        <v/>
-      </c>
-      <c r="P157" t="str">
-        <v/>
-      </c>
-      <c r="Q157" t="str">
-        <v/>
-      </c>
-      <c r="R157" t="str">
-        <v/>
-      </c>
-      <c r="S157" t="str">
-        <v/>
-      </c>
-      <c r="T157" t="str">
-        <v/>
-      </c>
-      <c r="U157" t="str">
-        <v/>
-      </c>
-      <c r="V157" t="str">
-        <v/>
-      </c>
-      <c r="W157" t="str">
-        <v/>
-      </c>
-      <c r="X157" t="str">
-        <v/>
-      </c>
-      <c r="Y157" t="str">
-        <v/>
-      </c>
-      <c r="Z157" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</v>
-      </c>
-      <c r="AA157" t="str">
-        <v/>
-      </c>
-      <c r="AB157" t="str">
-        <v/>
-      </c>
-      <c r="AC157" t="str">
-        <v/>
-      </c>
-      <c r="AD157" t="str">
-        <v/>
-      </c>
-      <c r="AE157" t="str">
-        <v>accessories-011</v>
-      </c>
-      <c r="AF157" t="str">
-        <v/>
-      </c>
-      <c r="AG157" t="str">
-        <v>Hinge Cuff</v>
-      </c>
-      <c r="AH157" t="str">
-        <v>265</v>
-      </c>
-      <c r="AI157" t="str">
-        <v/>
-      </c>
-      <c r="AJ157" t="str">
-        <v/>
-      </c>
-      <c r="AK157" t="str">
-        <v/>
-      </c>
-      <c r="AL157" t="str">
-        <v/>
-      </c>
-      <c r="AM157" t="str">
-        <v/>
-      </c>
-      <c r="AN157" t="str">
-        <v/>
-      </c>
-      <c r="AO157" t="str">
-        <v/>
-      </c>
-      <c r="AP157" t="str">
-        <v/>
-      </c>
-      <c r="AQ157" t="str">
-        <v/>
-      </c>
-      <c r="AR157" t="str">
-        <v/>
-      </c>
-      <c r="AS157" t="str">
-        <v/>
-      </c>
-      <c r="AT157" t="str">
-        <v/>
-      </c>
-      <c r="AU157" t="str">
-        <v/>
-      </c>
-      <c r="AV157" t="str">
-        <v/>
-      </c>
-      <c r="AW157" t="str">
-        <v/>
-      </c>
-      <c r="AX157" t="str">
-        <v/>
-      </c>
-      <c r="AY157" t="str">
-        <v/>
-      </c>
-      <c r="AZ157" t="str">
-        <v/>
-      </c>
-      <c r="BA157" t="str">
-        <v/>
-      </c>
-      <c r="BB157" t="str">
-        <v>accessories-atelier</v>
-      </c>
-      <c r="BC157" t="str">
-        <v/>
-      </c>
-      <c r="BD157" t="str">
-        <v/>
-      </c>
-      <c r="BE157" t="str">
-        <v/>
-      </c>
-      <c r="BF157" t="str">
-        <v>Metal Form</v>
-      </c>
-      <c r="BG157" t="str">
-        <v>Sterling Silver</v>
-      </c>
-      <c r="BH157" t="str">
-        <v>Sterling silver cuff displayed on matte black stone</v>
-      </c>
-      <c r="BI157" t="str">
-        <v>category:Jewelry|material:Sterling Silver</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="str">
-        <v>category_page_product</v>
-      </c>
-      <c r="B158" t="str">
-        <v/>
-      </c>
-      <c r="C158" t="str">
-        <v/>
-      </c>
-      <c r="D158" t="str">
-        <v/>
-      </c>
-      <c r="E158" t="str">
-        <v>12</v>
-      </c>
-      <c r="F158" t="str">
-        <v/>
-      </c>
-      <c r="G158" t="str">
-        <v/>
-      </c>
-      <c r="H158" t="str">
-        <v>/categories/Accessories</v>
-      </c>
-      <c r="I158" t="str">
-        <v/>
-      </c>
-      <c r="J158" t="str">
-        <v/>
-      </c>
-      <c r="K158" t="str">
-        <v/>
-      </c>
-      <c r="L158" t="str">
-        <v/>
-      </c>
-      <c r="M158" t="str">
-        <v/>
-      </c>
-      <c r="N158" t="str">
-        <v/>
-      </c>
-      <c r="O158" t="str">
-        <v/>
-      </c>
-      <c r="P158" t="str">
-        <v/>
-      </c>
-      <c r="Q158" t="str">
-        <v/>
-      </c>
-      <c r="R158" t="str">
-        <v/>
-      </c>
-      <c r="S158" t="str">
-        <v/>
-      </c>
-      <c r="T158" t="str">
-        <v/>
-      </c>
-      <c r="U158" t="str">
-        <v/>
-      </c>
-      <c r="V158" t="str">
-        <v/>
-      </c>
-      <c r="W158" t="str">
-        <v/>
-      </c>
-      <c r="X158" t="str">
-        <v/>
-      </c>
-      <c r="Y158" t="str">
-        <v/>
-      </c>
-      <c r="Z158" t="str">
-        <v>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</v>
-      </c>
-      <c r="AA158" t="str">
-        <v/>
-      </c>
-      <c r="AB158" t="str">
-        <v/>
-      </c>
-      <c r="AC158" t="str">
-        <v/>
-      </c>
-      <c r="AD158" t="str">
-        <v/>
-      </c>
-      <c r="AE158" t="str">
-        <v>accessories-012</v>
-      </c>
-      <c r="AF158" t="str">
-        <v/>
-      </c>
-      <c r="AG158" t="str">
-        <v>Atelier Bucket Pouch</v>
-      </c>
-      <c r="AH158" t="str">
-        <v>390</v>
-      </c>
-      <c r="AI158" t="str">
-        <v/>
-      </c>
-      <c r="AJ158" t="str">
-        <v/>
-      </c>
-      <c r="AK158" t="str">
-        <v/>
-      </c>
-      <c r="AL158" t="str">
-        <v/>
-      </c>
-      <c r="AM158" t="str">
-        <v/>
-      </c>
-      <c r="AN158" t="str">
-        <v/>
-      </c>
-      <c r="AO158" t="str">
-        <v/>
-      </c>
-      <c r="AP158" t="str">
-        <v/>
-      </c>
-      <c r="AQ158" t="str">
-        <v/>
-      </c>
-      <c r="AR158" t="str">
-        <v/>
-      </c>
-      <c r="AS158" t="str">
-        <v/>
-      </c>
-      <c r="AT158" t="str">
-        <v/>
-      </c>
-      <c r="AU158" t="str">
-        <v/>
-      </c>
-      <c r="AV158" t="str">
-        <v/>
-      </c>
-      <c r="AW158" t="str">
-        <v/>
-      </c>
-      <c r="AX158" t="str">
-        <v/>
-      </c>
-      <c r="AY158" t="str">
-        <v/>
-      </c>
-      <c r="AZ158" t="str">
-        <v/>
-      </c>
-      <c r="BA158" t="str">
-        <v/>
-      </c>
-      <c r="BB158" t="str">
-        <v>accessories-atelier</v>
-      </c>
-      <c r="BC158" t="str">
-        <v/>
-      </c>
-      <c r="BD158" t="str">
-        <v/>
-      </c>
-      <c r="BE158" t="str">
-        <v/>
-      </c>
-      <c r="BF158" t="str">
-        <v>Compact Bag</v>
-      </c>
-      <c r="BG158" t="str">
-        <v>Nappa Leather</v>
-      </c>
-      <c r="BH158" t="str">
-        <v>Drawstring leather pouch with minimal hardware</v>
-      </c>
-      <c r="BI158" t="str">
-        <v>category:Bags|material:Nappa Leather</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:BI158"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:BI154"/>
   </ignoredErrors>
 </worksheet>
 </file>